--- a/docs/DropDownAccessMethods.xlsx
+++ b/docs/DropDownAccessMethods.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robin\spCoin\SPCOIN-PROJECT-MODULES\spcoin-nextjs-front-end\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C1944B2-9276-44E7-8459-5E2283C00C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB77FB3-F313-4EC0-9056-688F7E04B5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="13403" windowWidth="21795" windowHeight="12975" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Methods" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2023" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2030" uniqueCount="277">
   <si>
     <t>Panel</t>
   </si>
@@ -859,6 +859,9 @@
   </si>
   <si>
     <t>getInitialTotalSupply</t>
+  </si>
+  <si>
+    <t>getAccountList</t>
   </si>
 </sst>
 </file>
@@ -4409,7 +4412,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.1328125" customWidth="1"/>
@@ -4498,10 +4501,10 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4521,19 +4524,19 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>274</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
@@ -4544,7 +4547,7 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>274</v>
@@ -4556,7 +4559,7 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
@@ -4564,10 +4567,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>274</v>
@@ -4579,7 +4582,7 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
@@ -4587,22 +4590,22 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>271</v>
+        <v>31</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>274</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
@@ -4613,19 +4616,19 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>271</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
@@ -4633,22 +4636,22 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>271</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
@@ -4656,22 +4659,22 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>111</v>
+        <v>33</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>271</v>
       </c>
       <c r="E11" t="s">
-        <v>112</v>
+        <v>27</v>
       </c>
       <c r="F11" t="s">
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>113</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
@@ -4682,19 +4685,19 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>271</v>
       </c>
       <c r="E12" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="F12" t="s">
         <v>9</v>
       </c>
       <c r="G12" t="s">
-        <v>67</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
@@ -4705,19 +4708,19 @@
         <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>274</v>
+        <v>65</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="F13" t="s">
         <v>9</v>
       </c>
       <c r="G13" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
@@ -4725,22 +4728,22 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>271</v>
+        <v>72</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>274</v>
       </c>
       <c r="E14" t="s">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
         <v>9</v>
       </c>
       <c r="G14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
@@ -4748,22 +4751,22 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>271</v>
       </c>
       <c r="E15" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="F15" t="s">
         <v>9</v>
       </c>
       <c r="G15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
@@ -4774,19 +4777,19 @@
         <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>271</v>
       </c>
       <c r="E16" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="F16" t="s">
         <v>9</v>
       </c>
       <c r="G16" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
@@ -4797,19 +4800,19 @@
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>271</v>
       </c>
       <c r="E17" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="F17" t="s">
         <v>9</v>
       </c>
       <c r="G17" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
@@ -4817,10 +4820,10 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>271</v>
@@ -4832,7 +4835,7 @@
         <v>9</v>
       </c>
       <c r="G18" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
@@ -4840,22 +4843,22 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>271</v>
       </c>
       <c r="E19" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="F19" t="s">
         <v>9</v>
       </c>
       <c r="G19" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
@@ -4866,19 +4869,19 @@
         <v>6</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>271</v>
       </c>
       <c r="E20" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="F20" t="s">
         <v>9</v>
       </c>
       <c r="G20" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
@@ -4889,19 +4892,19 @@
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>271</v>
       </c>
       <c r="E21" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="F21" t="s">
         <v>9</v>
       </c>
       <c r="G21" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
@@ -4912,19 +4915,19 @@
         <v>6</v>
       </c>
       <c r="C22" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>274</v>
+        <v>79</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="F22" t="s">
         <v>9</v>
       </c>
       <c r="G22" t="s">
-        <v>10</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
@@ -4935,7 +4938,7 @@
         <v>6</v>
       </c>
       <c r="C23" t="s">
-        <v>275</v>
+        <v>7</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>274</v>
@@ -4947,7 +4950,7 @@
         <v>9</v>
       </c>
       <c r="G23" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
@@ -4958,7 +4961,7 @@
         <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>68</v>
+        <v>275</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>274</v>
@@ -4970,7 +4973,7 @@
         <v>9</v>
       </c>
       <c r="G24" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
@@ -4981,7 +4984,7 @@
         <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>274</v>
@@ -4993,7 +4996,7 @@
         <v>9</v>
       </c>
       <c r="G25" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
@@ -5004,19 +5007,19 @@
         <v>6</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>274</v>
       </c>
       <c r="E26" t="s">
-        <v>103</v>
+        <v>8</v>
       </c>
       <c r="F26" t="s">
         <v>9</v>
       </c>
       <c r="G26" t="s">
-        <v>104</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
@@ -5027,19 +5030,19 @@
         <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>102</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>274</v>
       </c>
       <c r="E27" t="s">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="F27" t="s">
         <v>9</v>
       </c>
       <c r="G27" t="s">
-        <v>17</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
@@ -5050,19 +5053,19 @@
         <v>6</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>271</v>
+        <v>16</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>274</v>
       </c>
       <c r="E28" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="F28" t="s">
         <v>9</v>
       </c>
       <c r="G28" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
@@ -5073,19 +5076,19 @@
         <v>6</v>
       </c>
       <c r="C29" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>271</v>
       </c>
       <c r="E29" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F29" t="s">
         <v>9</v>
       </c>
       <c r="G29" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
@@ -5096,19 +5099,19 @@
         <v>6</v>
       </c>
       <c r="C30" t="s">
-        <v>58</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>274</v>
+        <v>44</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="E30" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F30" t="s">
         <v>9</v>
       </c>
       <c r="G30" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
@@ -5116,22 +5119,22 @@
         <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C31" t="s">
-        <v>47</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>271</v>
+        <v>58</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>274</v>
       </c>
       <c r="E31" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="F31" t="s">
         <v>9</v>
       </c>
       <c r="G31" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
@@ -5139,22 +5142,22 @@
         <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C32" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>271</v>
       </c>
       <c r="E32" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F32" t="s">
         <v>9</v>
       </c>
       <c r="G32" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
@@ -5165,19 +5168,19 @@
         <v>6</v>
       </c>
       <c r="C33" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>271</v>
       </c>
       <c r="E33" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F33" t="s">
         <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
@@ -5185,22 +5188,22 @@
         <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C34" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>271</v>
       </c>
       <c r="E34" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F34" t="s">
         <v>9</v>
       </c>
       <c r="G34" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
@@ -5208,22 +5211,22 @@
         <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C35" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>271</v>
       </c>
       <c r="E35" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="F35" t="s">
         <v>9</v>
       </c>
       <c r="G35" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
@@ -5231,22 +5234,22 @@
         <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C36" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>271</v>
       </c>
       <c r="E36" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="F36" t="s">
         <v>9</v>
       </c>
       <c r="G36" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
@@ -5254,22 +5257,22 @@
         <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C37" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>271</v>
       </c>
       <c r="E37" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F37" t="s">
         <v>9</v>
       </c>
       <c r="G37" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
@@ -5280,19 +5283,19 @@
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>105</v>
+        <v>24</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>271</v>
       </c>
       <c r="E38" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="F38" t="s">
         <v>9</v>
       </c>
       <c r="G38" t="s">
-        <v>107</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
@@ -5303,19 +5306,19 @@
         <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>70</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>274</v>
+        <v>105</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="E39" t="s">
-        <v>8</v>
+        <v>106</v>
       </c>
       <c r="F39" t="s">
         <v>9</v>
       </c>
       <c r="G39" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
@@ -5326,7 +5329,7 @@
         <v>6</v>
       </c>
       <c r="C40" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>274</v>
@@ -5338,7 +5341,7 @@
         <v>9</v>
       </c>
       <c r="G40" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
@@ -5349,7 +5352,7 @@
         <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>274</v>
@@ -5361,7 +5364,7 @@
         <v>9</v>
       </c>
       <c r="G41" t="s">
-        <v>121</v>
+        <v>57</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
@@ -5372,19 +5375,19 @@
         <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>100</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>271</v>
+        <v>120</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>274</v>
       </c>
       <c r="E42" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F42" t="s">
         <v>9</v>
       </c>
       <c r="G42" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
@@ -5395,19 +5398,19 @@
         <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>97</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>274</v>
+        <v>100</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="E43" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="F43" t="s">
         <v>9</v>
       </c>
       <c r="G43" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
@@ -5418,19 +5421,19 @@
         <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>114</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>271</v>
+        <v>97</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>274</v>
       </c>
       <c r="E44" t="s">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="F44" t="s">
         <v>9</v>
       </c>
       <c r="G44" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
@@ -5441,7 +5444,7 @@
         <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>271</v>
@@ -5453,7 +5456,7 @@
         <v>9</v>
       </c>
       <c r="G45" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.45">
@@ -5464,7 +5467,7 @@
         <v>6</v>
       </c>
       <c r="C46" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>271</v>
@@ -5476,13 +5479,36 @@
         <v>9</v>
       </c>
       <c r="G46" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" t="s">
+        <v>118</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E47" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" t="s">
+        <v>9</v>
+      </c>
+      <c r="G47" t="s">
         <v>119</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G46" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G46">
-      <sortCondition ref="C1:C46"/>
+  <autoFilter ref="A1:G47" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G47">
+      <sortCondition ref="C1:C47"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/DropDownAccessMethods.xlsx
+++ b/docs/DropDownAccessMethods.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robin\spCoin\SPCOIN-PROJECT-MODULES\spcoin-nextjs-front-end\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB77FB3-F313-4EC0-9056-688F7E04B5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30EE1390-4264-4B6C-9A6E-0C498D7A8B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Methods" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2030" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2016" uniqueCount="287">
   <si>
     <t>Panel</t>
   </si>
@@ -402,7 +402,7 @@
     <t>SpCoin Write</t>
   </si>
   <si>
-    <t>addSponsorRecipientBranch</t>
+    <t>addSponsorRecipient</t>
   </si>
   <si>
     <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/addRecipient.ts</t>
@@ -432,19 +432,13 @@
     <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/addRecipients.ts</t>
   </si>
   <si>
-    <t>addRecipientAgentBranch</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/addRecipientAgentBranch.ts</t>
-  </si>
-  <si>
-    <t>addAgentRateTransaction</t>
+    <t>addAgentTransaction</t>
   </si>
   <si>
     <t>Sponsor Key, Recipient Key, Recipient Rate Key, Agent Key, Agent Rate Key, Transaction Quantity</t>
   </si>
   <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/addAgentRateTransaction.ts</t>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/addAgentTransaction.ts</t>
   </si>
   <si>
     <t>addAgents</t>
@@ -474,10 +468,409 @@
     <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteSponsorTree.ts</t>
   </si>
   <si>
-    <t>deleteSponsorRecipientBranch</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteSponsorRecipientBranch.ts</t>
+    <t>deleteSponsorRecipient</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteSponsorRecipient.ts</t>
+  </si>
+  <si>
+    <t>deleteRecipientAgent</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteRecipientAgent.ts</t>
+  </si>
+  <si>
+    <t>deleteAgentRateBranch</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteAgentRateBranch.ts</t>
+  </si>
+  <si>
+    <t>deleteRecipientSponsorships</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteRecipientSponsorships.ts</t>
+  </si>
+  <si>
+    <t>deleteRecipientSponsorshipTree</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteRecipientSponsorshipTree.ts</t>
+  </si>
+  <si>
+    <t>deleteAgentSponsorships</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteAgentSponsorships.ts</t>
+  </si>
+  <si>
+    <t>deleteRecipientSponsorRate</t>
+  </si>
+  <si>
+    <t>Recipient Key, Recipient Rate Key</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteRecipientRate.ts</t>
+  </si>
+  <si>
+    <t>deleteAgent</t>
+  </si>
+  <si>
+    <t>Recipient Key, Recipient Rate Key, Agent Key</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteAgent.ts</t>
+  </si>
+  <si>
+    <t>unSponsorAgent</t>
+  </si>
+  <si>
+    <t>Recipient Key, Recipient Rate Key, Agent Key, Agent Rate Key</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteAgentSponsorship.ts</t>
+  </si>
+  <si>
+    <t>Owner Admin</t>
+  </si>
+  <si>
+    <t>addBackDatedRecipientRateAmount</t>
+  </si>
+  <si>
+    <t>Sponsor Key, Recipient Key, Recipient Rate Key, Transaction Quantity, Transaction Back Date</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/addBackDatedRecipientRateAmount.ts</t>
+  </si>
+  <si>
+    <t>addBackDatedRecipientAgentRateAmount</t>
+  </si>
+  <si>
+    <t>Sponsor Key, Recipient Key, Recipient Rate Key, Agent Key, Agent Rate Key, Transaction Quantity, Transaction Back Date</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/addBackDatedRecipientAgentRateAmount.ts</t>
+  </si>
+  <si>
+    <t>backDateRecipientTransactionDate</t>
+  </si>
+  <si>
+    <t>Sponsor Key, Recipient Key, Recipient Rate Key, Transaction Row Id, Transaction Back Date</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/backDateRecipientTransactionDate.ts</t>
+  </si>
+  <si>
+    <t>backDateAgentTransactionDate</t>
+  </si>
+  <si>
+    <t>Sponsor Key, Recipient Key, Recipient Rate Key, Agent Key, Agent Rate Key, Transaction Row Id, Transaction Back Date</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/backDateAgentTransactionDate.ts</t>
+  </si>
+  <si>
+    <t>deleteRecipientSponsorship</t>
+  </si>
+  <si>
+    <t>Recipient Key</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/delRecipient.ts</t>
+  </si>
+  <si>
+    <t>deleteAccountRecord</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteAccountRecord.ts</t>
+  </si>
+  <si>
+    <t>Todo</t>
+  </si>
+  <si>
+    <t>deleteAccountRecords</t>
+  </si>
+  <si>
+    <t>Account List Keys</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteAccountRecords.ts</t>
+  </si>
+  <si>
+    <t>updateAccountStakingRewards</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/updateAccountStakingRewards.ts</t>
+  </si>
+  <si>
+    <t>updateMasterStakingRewards</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/updateMasterStakingRewards.ts</t>
+  </si>
+  <si>
+    <t>World Write</t>
+  </si>
+  <si>
+    <t>depositSponsorStakingRewards</t>
+  </si>
+  <si>
+    <t>Sponsor Account, Recipient Account, Recipient Rate, Amount</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/depositSponsorStakingRewards.ts</t>
+  </si>
+  <si>
+    <t>depositRecipientStakingRewards</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/depositRecipientStakingRewards.ts</t>
+  </si>
+  <si>
+    <t>depositAgentStakingRewards</t>
+  </si>
+  <si>
+    <t>Sponsor Account, Recipient Account, Recipient Rate, Agent Account, Agent Rate, Amount</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/depositAgentStakingRewards.ts</t>
+  </si>
+  <si>
+    <t>setInflationRate</t>
+  </si>
+  <si>
+    <t>New Inflation Rate</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/setInflationRate.ts</t>
+  </si>
+  <si>
+    <t>setLowerRecipientRate</t>
+  </si>
+  <si>
+    <t>New Lower Recipient Rate</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/setLowerRecipient.ts</t>
+  </si>
+  <si>
+    <t>setUpperRecipientRate</t>
+  </si>
+  <si>
+    <t>New Upper Recipient Rate</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/setUpperRecipient.ts</t>
+  </si>
+  <si>
+    <t>setRecipientRateRange</t>
+  </si>
+  <si>
+    <t>New Lower Recipient Rate, New Upper Recipient Rate</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/setRecipientRateRange.ts</t>
+  </si>
+  <si>
+    <t>setLowerAgentRate</t>
+  </si>
+  <si>
+    <t>New Lower Agent Rate</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/setLowerAgent.ts</t>
+  </si>
+  <si>
+    <t>setUpperAgentRate</t>
+  </si>
+  <si>
+    <t>New Upper Agent Rate</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/setUpperAgent.ts</t>
+  </si>
+  <si>
+    <t>setAgentRateRange</t>
+  </si>
+  <si>
+    <t>New Lower Agent Rate, New Upper Agent Rate</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/setAgentRateRange.ts</t>
+  </si>
+  <si>
+    <t>setVersion</t>
+  </si>
+  <si>
+    <t>New Version</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/setVersion.ts</t>
+  </si>
+  <si>
+    <t>ERC20 Read</t>
+  </si>
+  <si>
+    <t>allowance</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/erc20/read/methods/allowance.ts</t>
+  </si>
+  <si>
+    <t>balanceOf</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/erc20/read/methods/balanceOf.ts</t>
+  </si>
+  <si>
+    <t>decimals</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/erc20/read/methods/decimals.ts</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/erc20/read/methods/name.ts</t>
+  </si>
+  <si>
+    <t>symbol</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/erc20/read/methods/symbol.ts</t>
+  </si>
+  <si>
+    <t>totalSupply</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/erc20/read/methods/totalSupply.ts</t>
+  </si>
+  <si>
+    <t>ERC20 Write</t>
+  </si>
+  <si>
+    <t>approve</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/erc20/write/methods/approve.ts</t>
+  </si>
+  <si>
+    <t>transfer</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/erc20/write/methods/transfer.ts</t>
+  </si>
+  <si>
+    <t>transferFrom</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/erc20/write/methods/transferFrom.ts</t>
+  </si>
+  <si>
+    <t>Serialization / Utilities</t>
+  </si>
+  <si>
+    <t>Serialization Test</t>
+  </si>
+  <si>
+    <t>external_getSerializedSPCoinHeader</t>
+  </si>
+  <si>
+    <t>visible unless hidden by utility filter</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/serializationTests/index.ts</t>
+  </si>
+  <si>
+    <t>external_getSerializedAccountRecord</t>
+  </si>
+  <si>
+    <t>external_getSerializedAccountRewards</t>
+  </si>
+  <si>
+    <t>external_getSerializedRecipientRecordList</t>
+  </si>
+  <si>
+    <t>external_getSerializedRecipientRateList</t>
+  </si>
+  <si>
+    <t>external_serializeAgentRateRecordStr</t>
+  </si>
+  <si>
+    <t>external_getSerializedRateTransactionList</t>
+  </si>
+  <si>
+    <t>Read Admin</t>
+  </si>
+  <si>
+    <t>compareSpCoinContractSize</t>
+  </si>
+  <si>
+    <t>Previous Release Directory, Latest Release Directory</t>
+  </si>
+  <si>
+    <t>getSponsorAccounts</t>
+  </si>
+  <si>
+    <t>getMasterSponsorList</t>
+  </si>
+  <si>
+    <t>getMasterSponsorList_BAK</t>
+  </si>
+  <si>
+    <t>hhFundAccounts</t>
+  </si>
+  <si>
+    <t>Total Token Amount</t>
+  </si>
+  <si>
+    <t>deleteMasterSponsorships</t>
+  </si>
+  <si>
+    <t>ToDo</t>
+  </si>
+  <si>
+    <t>Test Status</t>
+  </si>
+  <si>
+    <t>Test Status</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>getInitialTotalSupply</t>
+  </si>
+  <si>
+    <t>addSponsorRecipient</t>
+  </si>
+  <si>
+    <t>addRecipientAgent</t>
+  </si>
+  <si>
+    <t>deleteSponsorRecipient</t>
+  </si>
+  <si>
+    <t>deleteRecipientAgent</t>
+  </si>
+  <si>
+    <t>deleteRecipientTransaction</t>
+  </si>
+  <si>
+    <t>addAgentTransaction</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/addRecipientAgent.ts</t>
+  </si>
+  <si>
+    <t>deleteRecipientSponsorRate</t>
+  </si>
+  <si>
+    <t>deleteRecipientSponsorRate</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteRecipientRate.ts</t>
   </si>
   <si>
     <t>deleteRecipientRateBranch</t>
@@ -486,382 +879,19 @@
     <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteRecipientRateBranch.ts</t>
   </si>
   <si>
-    <t>deleteRecipientAgentBranch</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteRecipientAgentBranch.ts</t>
-  </si>
-  <si>
-    <t>deleteAgentRateBranch</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteAgentRateBranch.ts</t>
-  </si>
-  <si>
-    <t>deleteRecipientSponsorships</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteRecipientSponsorships.ts</t>
-  </si>
-  <si>
-    <t>deleteRecipientSponsorshipTree</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteRecipientSponsorshipTree.ts</t>
-  </si>
-  <si>
-    <t>deleteAgentSponsorships</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteAgentSponsorships.ts</t>
-  </si>
-  <si>
-    <t>deleteRecipientRateSponsorship</t>
-  </si>
-  <si>
-    <t>Recipient Key, Recipient Rate Key</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteRecipientRate.ts</t>
-  </si>
-  <si>
-    <t>deleteRecipientRateAmount</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteRecipientRateAmount.ts</t>
-  </si>
-  <si>
-    <t>deleteAgent</t>
-  </si>
-  <si>
-    <t>Recipient Key, Recipient Rate Key, Agent Key</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteAgent.ts</t>
-  </si>
-  <si>
-    <t>unSponsorAgent</t>
-  </si>
-  <si>
-    <t>Recipient Key, Recipient Rate Key, Agent Key, Agent Rate Key</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteAgentSponsorship.ts</t>
-  </si>
-  <si>
-    <t>Owner Admin</t>
-  </si>
-  <si>
-    <t>addBackDatedRecipientRateTransaction</t>
-  </si>
-  <si>
-    <t>Sponsor Key, Recipient Key, Recipient Rate Key, Transaction Quantity, Transaction Back Date</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/addBackDatedRecipientRateTransaction.ts</t>
-  </si>
-  <si>
-    <t>addBackDatedAgentRateTransaction</t>
-  </si>
-  <si>
-    <t>Sponsor Key, Recipient Key, Recipient Rate Key, Agent Key, Agent Rate Key, Transaction Quantity, Transaction Back Date</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/addBackDatedAgentRateTransaction.ts</t>
-  </si>
-  <si>
-    <t>backDateRecipientTransactionDate</t>
-  </si>
-  <si>
-    <t>Sponsor Key, Recipient Key, Recipient Rate Key, Transaction Row Id, Transaction Back Date</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/backDateRecipientTransactionDate.ts</t>
-  </si>
-  <si>
-    <t>backDateAgentTransactionDate</t>
-  </si>
-  <si>
-    <t>Sponsor Key, Recipient Key, Recipient Rate Key, Agent Key, Agent Rate Key, Transaction Row Id, Transaction Back Date</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/backDateAgentTransactionDate.ts</t>
-  </si>
-  <si>
-    <t>deleteRecipientSponsorship</t>
-  </si>
-  <si>
-    <t>Recipient Key</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/delRecipient.ts</t>
-  </si>
-  <si>
-    <t>deleteAccountRecord</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteAccountRecord.ts</t>
-  </si>
-  <si>
-    <t>Todo</t>
-  </si>
-  <si>
-    <t>deleteAccountRecords</t>
-  </si>
-  <si>
-    <t>Account List Keys</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteAccountRecords.ts</t>
-  </si>
-  <si>
-    <t>updateAccountStakingRewards</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/updateAccountStakingRewards.ts</t>
-  </si>
-  <si>
-    <t>updateMasterStakingRewards</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/updateMasterStakingRewards.ts</t>
-  </si>
-  <si>
-    <t>World Write</t>
-  </si>
-  <si>
-    <t>depositSponsorStakingRewards</t>
-  </si>
-  <si>
-    <t>Sponsor Account, Recipient Account, Recipient Rate, Amount</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/depositSponsorStakingRewards.ts</t>
-  </si>
-  <si>
-    <t>depositRecipientStakingRewards</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/depositRecipientStakingRewards.ts</t>
-  </si>
-  <si>
-    <t>depositAgentStakingRewards</t>
-  </si>
-  <si>
-    <t>Sponsor Account, Recipient Account, Recipient Rate, Agent Account, Agent Rate, Amount</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/depositAgentStakingRewards.ts</t>
-  </si>
-  <si>
-    <t>setInflationRate</t>
-  </si>
-  <si>
-    <t>New Inflation Rate</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/setInflationRate.ts</t>
-  </si>
-  <si>
-    <t>setLowerRecipientRate</t>
-  </si>
-  <si>
-    <t>New Lower Recipient Rate</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/setLowerRecipient.ts</t>
-  </si>
-  <si>
-    <t>setUpperRecipientRate</t>
-  </si>
-  <si>
-    <t>New Upper Recipient Rate</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/setUpperRecipient.ts</t>
-  </si>
-  <si>
-    <t>setRecipientRateRange</t>
-  </si>
-  <si>
-    <t>New Lower Recipient Rate, New Upper Recipient Rate</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/setRecipientRateRange.ts</t>
-  </si>
-  <si>
-    <t>setLowerAgentRate</t>
-  </si>
-  <si>
-    <t>New Lower Agent Rate</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/setLowerAgent.ts</t>
-  </si>
-  <si>
-    <t>setUpperAgentRate</t>
-  </si>
-  <si>
-    <t>New Upper Agent Rate</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/setUpperAgent.ts</t>
-  </si>
-  <si>
-    <t>setAgentRateRange</t>
-  </si>
-  <si>
-    <t>New Lower Agent Rate, New Upper Agent Rate</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/setAgentRateRange.ts</t>
-  </si>
-  <si>
-    <t>setVersion</t>
-  </si>
-  <si>
-    <t>New Version</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/setVersion.ts</t>
-  </si>
-  <si>
-    <t>ERC20 Read</t>
-  </si>
-  <si>
-    <t>allowance</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/erc20/read/methods/allowance.ts</t>
-  </si>
-  <si>
-    <t>balanceOf</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/erc20/read/methods/balanceOf.ts</t>
-  </si>
-  <si>
-    <t>decimals</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/erc20/read/methods/decimals.ts</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/erc20/read/methods/name.ts</t>
-  </si>
-  <si>
-    <t>symbol</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/erc20/read/methods/symbol.ts</t>
-  </si>
-  <si>
-    <t>totalSupply</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/erc20/read/methods/totalSupply.ts</t>
-  </si>
-  <si>
-    <t>ERC20 Write</t>
-  </si>
-  <si>
-    <t>approve</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/erc20/write/methods/approve.ts</t>
-  </si>
-  <si>
-    <t>transfer</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/erc20/write/methods/transfer.ts</t>
-  </si>
-  <si>
-    <t>transferFrom</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/erc20/write/methods/transferFrom.ts</t>
-  </si>
-  <si>
-    <t>Serialization / Utilities</t>
-  </si>
-  <si>
-    <t>Serialization Test</t>
-  </si>
-  <si>
-    <t>external_getSerializedSPCoinHeader</t>
-  </si>
-  <si>
-    <t>visible unless hidden by utility filter</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/serializationTests/index.ts</t>
-  </si>
-  <si>
-    <t>external_getSerializedAccountRecord</t>
-  </si>
-  <si>
-    <t>external_getSerializedAccountRewards</t>
-  </si>
-  <si>
-    <t>external_getSerializedRecipientRecordList</t>
-  </si>
-  <si>
-    <t>external_getSerializedRecipientRateList</t>
-  </si>
-  <si>
-    <t>external_serializeAgentRateRecordStr</t>
-  </si>
-  <si>
-    <t>external_getSerializedRateTransactionList</t>
-  </si>
-  <si>
-    <t>Read Admin</t>
-  </si>
-  <si>
-    <t>compareSpCoinContractSize</t>
-  </si>
-  <si>
-    <t>Previous Release Directory, Latest Release Directory</t>
-  </si>
-  <si>
-    <t>getSponsorAccounts</t>
-  </si>
-  <si>
-    <t>getMasterSponsorList</t>
-  </si>
-  <si>
-    <t>getMasterSponsorList_BAK</t>
-  </si>
-  <si>
-    <t>hhFundAccounts</t>
-  </si>
-  <si>
-    <t>Total Token Amount</t>
-  </si>
-  <si>
-    <t>deleteMasterSponsorships</t>
-  </si>
-  <si>
-    <t>ToDo</t>
-  </si>
-  <si>
-    <t>Test Ststus</t>
-  </si>
-  <si>
-    <t>Test Status</t>
-  </si>
-  <si>
-    <t>Pass</t>
-  </si>
-  <si>
-    <t>getInitialTotalSupply</t>
-  </si>
-  <si>
-    <t>getAccountList</t>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteRecipientTransaction.ts</t>
+  </si>
+  <si>
+    <t>addBackDatedAgentTransaction</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/addBackDatedAgentTransaction.ts</t>
+  </si>
+  <si>
+    <t>addBackDatedRecipientTransaction</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/addBackDatedRecipientTransaction.ts</t>
   </si>
 </sst>
 </file>
@@ -1278,9 +1308,9 @@
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
-    <col min="4" max="4" width="72" customWidth="1"/>
-    <col min="5" max="5" width="12" style="4" customWidth="1"/>
+    <col min="3" max="3" width="34.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" style="4" customWidth="1"/>
+    <col min="5" max="5" width="72" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
     <col min="7" max="7" width="96" customWidth="1"/>
   </cols>
@@ -1295,11 +1325,11 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>272</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -1318,11 +1348,11 @@
       <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E2" t="s">
         <v>8</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
@@ -1341,11 +1371,11 @@
       <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E3" t="s">
         <v>12</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
@@ -1364,11 +1394,11 @@
       <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E4" t="s">
         <v>8</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
@@ -1387,11 +1417,11 @@
       <c r="C5" t="s">
         <v>16</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E5" t="s">
         <v>8</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
@@ -1410,11 +1440,11 @@
       <c r="C6" t="s">
         <v>18</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E6" t="s">
         <v>8</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
@@ -1433,11 +1463,11 @@
       <c r="C7" t="s">
         <v>21</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E7" t="s">
         <v>22</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
@@ -1456,11 +1486,11 @@
       <c r="C8" t="s">
         <v>24</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E8" t="s">
         <v>8</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -1479,11 +1509,11 @@
       <c r="C9" t="s">
         <v>26</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E9" t="s">
         <v>27</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
@@ -1502,11 +1532,11 @@
       <c r="C10" t="s">
         <v>29</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E10" t="s">
         <v>27</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
@@ -1525,11 +1555,11 @@
       <c r="C11" t="s">
         <v>31</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E11" t="s">
         <v>27</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F11" t="s">
         <v>9</v>
@@ -1548,11 +1578,11 @@
       <c r="C12" t="s">
         <v>33</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E12" t="s">
         <v>27</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F12" t="s">
         <v>9</v>
@@ -1571,11 +1601,11 @@
       <c r="C13" t="s">
         <v>35</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E13" t="s">
         <v>36</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F13" t="s">
         <v>9</v>
@@ -1594,11 +1624,11 @@
       <c r="C14" t="s">
         <v>38</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E14" t="s">
         <v>39</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F14" t="s">
         <v>9</v>
@@ -1617,11 +1647,11 @@
       <c r="C15" t="s">
         <v>41</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E15" t="s">
         <v>42</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F15" t="s">
         <v>9</v>
@@ -1640,11 +1670,11 @@
       <c r="C16" t="s">
         <v>44</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E16" t="s">
         <v>45</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F16" t="s">
         <v>9</v>
@@ -1663,11 +1693,11 @@
       <c r="C17" t="s">
         <v>47</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E17" t="s">
         <v>48</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F17" t="s">
         <v>9</v>
@@ -1686,11 +1716,11 @@
       <c r="C18" t="s">
         <v>50</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E18" t="s">
         <v>45</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F18" t="s">
         <v>9</v>
@@ -1709,11 +1739,11 @@
       <c r="C19" t="s">
         <v>52</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E19" t="s">
         <v>48</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F19" t="s">
         <v>9</v>
@@ -1732,11 +1762,11 @@
       <c r="C20" t="s">
         <v>54</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E20" t="s">
         <v>8</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F20" t="s">
         <v>9</v>
@@ -1755,11 +1785,11 @@
       <c r="C21" t="s">
         <v>56</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E21" t="s">
         <v>8</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F21" t="s">
         <v>9</v>
@@ -1778,11 +1808,11 @@
       <c r="C22" t="s">
         <v>58</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E22" t="s">
         <v>8</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F22" t="s">
         <v>9</v>
@@ -1801,11 +1831,11 @@
       <c r="C23" t="s">
         <v>60</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E23" t="s">
         <v>45</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F23" t="s">
         <v>9</v>
@@ -1824,11 +1854,11 @@
       <c r="C24" t="s">
         <v>62</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E24" t="s">
         <v>63</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F24" t="s">
         <v>9</v>
@@ -1847,11 +1877,11 @@
       <c r="C25" t="s">
         <v>65</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E25" t="s">
         <v>66</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F25" t="s">
         <v>9</v>
@@ -1870,11 +1900,11 @@
       <c r="C26" t="s">
         <v>68</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E26" t="s">
         <v>8</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F26" t="s">
         <v>9</v>
@@ -1893,11 +1923,11 @@
       <c r="C27" t="s">
         <v>70</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E27" t="s">
         <v>8</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F27" t="s">
         <v>9</v>
@@ -1916,11 +1946,11 @@
       <c r="C28" t="s">
         <v>72</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E28" t="s">
         <v>8</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F28" t="s">
         <v>9</v>
@@ -1939,11 +1969,11 @@
       <c r="C29" t="s">
         <v>74</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E29" t="s">
         <v>75</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F29" t="s">
         <v>9</v>
@@ -1962,11 +1992,11 @@
       <c r="C30" t="s">
         <v>77</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E30" t="s">
         <v>66</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F30" t="s">
         <v>9</v>
@@ -1985,11 +2015,11 @@
       <c r="C31" t="s">
         <v>79</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E31" t="s">
         <v>66</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F31" t="s">
         <v>9</v>
@@ -2008,11 +2038,11 @@
       <c r="C32" t="s">
         <v>81</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E32" t="s">
         <v>48</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F32" t="s">
         <v>9</v>
@@ -2031,11 +2061,11 @@
       <c r="C33" t="s">
         <v>83</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E33" t="s">
         <v>75</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F33" t="s">
         <v>9</v>
@@ -2054,11 +2084,11 @@
       <c r="C34" t="s">
         <v>85</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E34" t="s">
         <v>86</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F34" t="s">
         <v>9</v>
@@ -2077,11 +2107,11 @@
       <c r="C35" t="s">
         <v>88</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E35" t="s">
         <v>75</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F35" t="s">
         <v>9</v>
@@ -2100,11 +2130,11 @@
       <c r="C36" t="s">
         <v>90</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E36" t="s">
         <v>66</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F36" t="s">
         <v>9</v>
@@ -2123,11 +2153,11 @@
       <c r="C37" t="s">
         <v>92</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E37" t="s">
         <v>93</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F37" t="s">
         <v>9</v>
@@ -2146,11 +2176,11 @@
       <c r="C38" t="s">
         <v>95</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E38" t="s">
         <v>8</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F38" t="s">
         <v>9</v>
@@ -2169,11 +2199,11 @@
       <c r="C39" t="s">
         <v>97</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E39" t="s">
         <v>98</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F39" t="s">
         <v>9</v>
@@ -2192,11 +2222,11 @@
       <c r="C40" t="s">
         <v>100</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E40" t="s">
         <v>27</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F40" t="s">
         <v>9</v>
@@ -2215,11 +2245,11 @@
       <c r="C41" t="s">
         <v>102</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E41" t="s">
         <v>103</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F41" t="s">
         <v>9</v>
@@ -2238,11 +2268,11 @@
       <c r="C42" t="s">
         <v>105</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E42" t="s">
         <v>106</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F42" t="s">
         <v>9</v>
@@ -2261,11 +2291,11 @@
       <c r="C43" t="s">
         <v>108</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E43" t="s">
         <v>109</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F43" t="s">
         <v>9</v>
@@ -2284,11 +2314,11 @@
       <c r="C44" t="s">
         <v>111</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E44" t="s">
         <v>112</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F44" t="s">
         <v>9</v>
@@ -2307,11 +2337,11 @@
       <c r="C45" t="s">
         <v>114</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E45" t="s">
         <v>8</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F45" t="s">
         <v>9</v>
@@ -2330,11 +2360,11 @@
       <c r="C46" t="s">
         <v>116</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E46" t="s">
         <v>8</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F46" t="s">
         <v>9</v>
@@ -2353,11 +2383,11 @@
       <c r="C47" t="s">
         <v>118</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E47" t="s">
         <v>8</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F47" t="s">
         <v>9</v>
@@ -2376,11 +2406,11 @@
       <c r="C48" t="s">
         <v>120</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E48" t="s">
         <v>8</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F48" t="s">
         <v>9</v>
@@ -2399,11 +2429,11 @@
       <c r="C49" t="s">
         <v>123</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E49" t="s">
         <v>45</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F49" t="s">
         <v>9</v>
@@ -2422,11 +2452,11 @@
       <c r="C50" t="s">
         <v>125</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E50" t="s">
         <v>126</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F50" t="s">
         <v>9</v>
@@ -2445,11 +2475,11 @@
       <c r="C51" t="s">
         <v>129</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E51" t="s">
         <v>130</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F51" t="s">
         <v>131</v>
@@ -2466,19 +2496,19 @@
         <v>122</v>
       </c>
       <c r="C52" t="s">
-        <v>133</v>
-      </c>
-      <c r="D52" t="s">
+        <v>271</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E52" t="s">
         <v>66</v>
       </c>
-      <c r="E52" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F52" t="s">
         <v>9</v>
       </c>
       <c r="G52" t="s">
-        <v>134</v>
+        <v>276</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.45">
@@ -2489,19 +2519,19 @@
         <v>122</v>
       </c>
       <c r="C53" t="s">
+        <v>133</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E53" t="s">
+        <v>134</v>
+      </c>
+      <c r="F53" t="s">
+        <v>9</v>
+      </c>
+      <c r="G53" t="s">
         <v>135</v>
-      </c>
-      <c r="D53" t="s">
-        <v>136</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="F53" t="s">
-        <v>9</v>
-      </c>
-      <c r="G53" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.45">
@@ -2512,19 +2542,19 @@
         <v>128</v>
       </c>
       <c r="C54" t="s">
-        <v>138</v>
-      </c>
-      <c r="D54" t="s">
+        <v>136</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E54" t="s">
         <v>93</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F54" t="s">
         <v>131</v>
       </c>
       <c r="G54" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.45">
@@ -2535,19 +2565,19 @@
         <v>122</v>
       </c>
       <c r="C55" t="s">
+        <v>138</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E55" t="s">
+        <v>139</v>
+      </c>
+      <c r="F55" t="s">
         <v>140</v>
       </c>
-      <c r="D55" t="s">
+      <c r="G55" t="s">
         <v>141</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="F55" t="s">
-        <v>142</v>
-      </c>
-      <c r="G55" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.45">
@@ -2555,22 +2585,22 @@
         <v>122</v>
       </c>
       <c r="B56" t="s">
+        <v>142</v>
+      </c>
+      <c r="C56" t="s">
+        <v>143</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E56" t="s">
+        <v>139</v>
+      </c>
+      <c r="F56" t="s">
+        <v>9</v>
+      </c>
+      <c r="G56" t="s">
         <v>144</v>
-      </c>
-      <c r="C56" t="s">
-        <v>145</v>
-      </c>
-      <c r="D56" t="s">
-        <v>141</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="F56" t="s">
-        <v>9</v>
-      </c>
-      <c r="G56" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.45">
@@ -2578,22 +2608,22 @@
         <v>122</v>
       </c>
       <c r="B57" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C57" t="s">
-        <v>147</v>
-      </c>
-      <c r="D57" t="s">
+        <v>145</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E57" t="s">
         <v>45</v>
       </c>
-      <c r="E57" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F57" t="s">
         <v>9</v>
       </c>
       <c r="G57" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.45">
@@ -2601,22 +2631,22 @@
         <v>122</v>
       </c>
       <c r="B58" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C58" t="s">
-        <v>149</v>
-      </c>
-      <c r="D58" t="s">
+        <v>278</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E58" t="s">
         <v>48</v>
       </c>
-      <c r="E58" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F58" t="s">
         <v>9</v>
       </c>
       <c r="G58" t="s">
-        <v>150</v>
+        <v>279</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.45">
@@ -2624,22 +2654,22 @@
         <v>122</v>
       </c>
       <c r="B59" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C59" t="s">
-        <v>151</v>
-      </c>
-      <c r="D59" t="s">
+        <v>147</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E59" t="s">
         <v>66</v>
       </c>
-      <c r="E59" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F59" t="s">
         <v>9</v>
       </c>
       <c r="G59" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.45">
@@ -2647,22 +2677,22 @@
         <v>122</v>
       </c>
       <c r="B60" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C60" t="s">
-        <v>153</v>
-      </c>
-      <c r="D60" t="s">
+        <v>149</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E60" t="s">
         <v>75</v>
       </c>
-      <c r="E60" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F60" t="s">
         <v>9</v>
       </c>
       <c r="G60" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.45">
@@ -2673,19 +2703,19 @@
         <v>122</v>
       </c>
       <c r="C61" t="s">
-        <v>155</v>
-      </c>
-      <c r="D61" t="s">
+        <v>151</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E61" t="s">
         <v>45</v>
       </c>
-      <c r="E61" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F61" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G61" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.45">
@@ -2696,19 +2726,19 @@
         <v>122</v>
       </c>
       <c r="C62" t="s">
-        <v>157</v>
-      </c>
-      <c r="D62" t="s">
+        <v>153</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E62" t="s">
         <v>48</v>
       </c>
-      <c r="E62" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F62" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G62" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.45">
@@ -2719,19 +2749,19 @@
         <v>122</v>
       </c>
       <c r="C63" t="s">
-        <v>159</v>
-      </c>
-      <c r="D63" t="s">
+        <v>155</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E63" t="s">
         <v>66</v>
       </c>
-      <c r="E63" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F63" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G63" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.45">
@@ -2742,19 +2772,19 @@
         <v>122</v>
       </c>
       <c r="C64" t="s">
-        <v>161</v>
-      </c>
-      <c r="D64" t="s">
-        <v>162</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>271</v>
+        <v>157</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E64" t="s">
+        <v>158</v>
       </c>
       <c r="F64" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G64" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.45">
@@ -2765,19 +2795,19 @@
         <v>122</v>
       </c>
       <c r="C65" t="s">
-        <v>164</v>
-      </c>
-      <c r="D65" t="s">
-        <v>162</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>271</v>
+        <v>274</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E65" t="s">
+        <v>158</v>
       </c>
       <c r="F65" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G65" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.45">
@@ -2788,19 +2818,19 @@
         <v>122</v>
       </c>
       <c r="C66" t="s">
-        <v>166</v>
-      </c>
-      <c r="D66" t="s">
-        <v>167</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>271</v>
+        <v>160</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E66" t="s">
+        <v>161</v>
       </c>
       <c r="F66" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G66" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.45">
@@ -2811,19 +2841,19 @@
         <v>122</v>
       </c>
       <c r="C67" t="s">
-        <v>169</v>
-      </c>
-      <c r="D67" t="s">
-        <v>170</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>271</v>
+        <v>163</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E67" t="s">
+        <v>164</v>
       </c>
       <c r="F67" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G67" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.45">
@@ -2831,22 +2861,22 @@
         <v>122</v>
       </c>
       <c r="B68" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C68" t="s">
-        <v>173</v>
-      </c>
-      <c r="D68" t="s">
-        <v>174</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>271</v>
+        <v>167</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E68" t="s">
+        <v>168</v>
       </c>
       <c r="F68" t="s">
         <v>9</v>
       </c>
       <c r="G68" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.45">
@@ -2854,22 +2884,22 @@
         <v>122</v>
       </c>
       <c r="B69" t="s">
+        <v>166</v>
+      </c>
+      <c r="C69" t="s">
+        <v>170</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E69" t="s">
+        <v>171</v>
+      </c>
+      <c r="F69" t="s">
+        <v>9</v>
+      </c>
+      <c r="G69" t="s">
         <v>172</v>
-      </c>
-      <c r="C69" t="s">
-        <v>176</v>
-      </c>
-      <c r="D69" t="s">
-        <v>177</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="F69" t="s">
-        <v>9</v>
-      </c>
-      <c r="G69" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.45">
@@ -2877,22 +2907,22 @@
         <v>122</v>
       </c>
       <c r="B70" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C70" t="s">
-        <v>179</v>
-      </c>
-      <c r="D70" t="s">
-        <v>180</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>271</v>
+        <v>173</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E70" t="s">
+        <v>174</v>
       </c>
       <c r="F70" t="s">
         <v>9</v>
       </c>
       <c r="G70" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.45">
@@ -2900,22 +2930,22 @@
         <v>122</v>
       </c>
       <c r="B71" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C71" t="s">
-        <v>182</v>
-      </c>
-      <c r="D71" t="s">
-        <v>183</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>271</v>
+        <v>176</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E71" t="s">
+        <v>177</v>
       </c>
       <c r="F71" t="s">
         <v>9</v>
       </c>
       <c r="G71" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.45">
@@ -2926,19 +2956,19 @@
         <v>122</v>
       </c>
       <c r="C72" t="s">
-        <v>185</v>
-      </c>
-      <c r="D72" t="s">
-        <v>186</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>271</v>
+        <v>179</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E72" t="s">
+        <v>180</v>
       </c>
       <c r="F72" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G72" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.45">
@@ -2949,19 +2979,19 @@
         <v>122</v>
       </c>
       <c r="C73" t="s">
-        <v>188</v>
-      </c>
-      <c r="D73" t="s">
+        <v>182</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E73" t="s">
         <v>27</v>
       </c>
-      <c r="E73" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F73" t="s">
         <v>9</v>
       </c>
       <c r="G73" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.45">
@@ -2969,22 +2999,22 @@
         <v>122</v>
       </c>
       <c r="B74" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C74" t="s">
-        <v>191</v>
-      </c>
-      <c r="D74" t="s">
-        <v>192</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>271</v>
+        <v>185</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E74" t="s">
+        <v>186</v>
       </c>
       <c r="F74" t="s">
         <v>131</v>
       </c>
       <c r="G74" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.45">
@@ -2995,19 +3025,19 @@
         <v>122</v>
       </c>
       <c r="C75" t="s">
-        <v>194</v>
-      </c>
-      <c r="D75" t="s">
+        <v>188</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E75" t="s">
         <v>27</v>
       </c>
-      <c r="E75" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F75" t="s">
         <v>9</v>
       </c>
       <c r="G75" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.45">
@@ -3015,22 +3045,22 @@
         <v>122</v>
       </c>
       <c r="B76" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C76" t="s">
-        <v>196</v>
-      </c>
-      <c r="D76" t="s">
+        <v>190</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E76" t="s">
         <v>8</v>
       </c>
-      <c r="E76" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F76" t="s">
         <v>9</v>
       </c>
       <c r="G76" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.45">
@@ -3038,22 +3068,22 @@
         <v>122</v>
       </c>
       <c r="B77" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C77" t="s">
-        <v>199</v>
-      </c>
-      <c r="D77" t="s">
-        <v>200</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>271</v>
+        <v>193</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E77" t="s">
+        <v>194</v>
       </c>
       <c r="F77" t="s">
         <v>9</v>
       </c>
       <c r="G77" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.45">
@@ -3061,22 +3091,22 @@
         <v>122</v>
       </c>
       <c r="B78" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C78" t="s">
-        <v>202</v>
-      </c>
-      <c r="D78" t="s">
-        <v>200</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>271</v>
+        <v>196</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E78" t="s">
+        <v>194</v>
       </c>
       <c r="F78" t="s">
         <v>9</v>
       </c>
       <c r="G78" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.45">
@@ -3084,22 +3114,22 @@
         <v>122</v>
       </c>
       <c r="B79" t="s">
+        <v>192</v>
+      </c>
+      <c r="C79" t="s">
         <v>198</v>
       </c>
-      <c r="C79" t="s">
-        <v>204</v>
-      </c>
-      <c r="D79" t="s">
-        <v>205</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>271</v>
+      <c r="D79" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E79" t="s">
+        <v>199</v>
       </c>
       <c r="F79" t="s">
         <v>9</v>
       </c>
       <c r="G79" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.45">
@@ -3107,22 +3137,22 @@
         <v>122</v>
       </c>
       <c r="B80" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C80" t="s">
-        <v>207</v>
-      </c>
-      <c r="D80" t="s">
-        <v>208</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>271</v>
+        <v>201</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E80" t="s">
+        <v>202</v>
       </c>
       <c r="F80" t="s">
         <v>9</v>
       </c>
       <c r="G80" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.45">
@@ -3130,22 +3160,22 @@
         <v>122</v>
       </c>
       <c r="B81" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C81" t="s">
-        <v>210</v>
-      </c>
-      <c r="D81" t="s">
-        <v>211</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>271</v>
+        <v>204</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E81" t="s">
+        <v>205</v>
       </c>
       <c r="F81" t="s">
         <v>9</v>
       </c>
       <c r="G81" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.45">
@@ -3153,22 +3183,22 @@
         <v>122</v>
       </c>
       <c r="B82" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C82" t="s">
-        <v>213</v>
-      </c>
-      <c r="D82" t="s">
-        <v>214</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>271</v>
+        <v>207</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E82" t="s">
+        <v>208</v>
       </c>
       <c r="F82" t="s">
         <v>9</v>
       </c>
       <c r="G82" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.45">
@@ -3176,22 +3206,22 @@
         <v>122</v>
       </c>
       <c r="B83" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C83" t="s">
-        <v>216</v>
-      </c>
-      <c r="D83" t="s">
-        <v>217</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>271</v>
+        <v>210</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E83" t="s">
+        <v>211</v>
       </c>
       <c r="F83" t="s">
         <v>9</v>
       </c>
       <c r="G83" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.45">
@@ -3199,22 +3229,22 @@
         <v>122</v>
       </c>
       <c r="B84" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C84" t="s">
-        <v>219</v>
-      </c>
-      <c r="D84" t="s">
-        <v>220</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>271</v>
+        <v>213</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E84" t="s">
+        <v>214</v>
       </c>
       <c r="F84" t="s">
         <v>9</v>
       </c>
       <c r="G84" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.45">
@@ -3222,22 +3252,22 @@
         <v>122</v>
       </c>
       <c r="B85" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C85" t="s">
-        <v>222</v>
-      </c>
-      <c r="D85" t="s">
-        <v>223</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>271</v>
+        <v>216</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E85" t="s">
+        <v>217</v>
       </c>
       <c r="F85" t="s">
         <v>9</v>
       </c>
       <c r="G85" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.45">
@@ -3245,22 +3275,22 @@
         <v>122</v>
       </c>
       <c r="B86" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C86" t="s">
-        <v>225</v>
-      </c>
-      <c r="D86" t="s">
-        <v>226</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>271</v>
+        <v>219</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E86" t="s">
+        <v>220</v>
       </c>
       <c r="F86" t="s">
         <v>9</v>
       </c>
       <c r="G86" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.45">
@@ -3268,712 +3298,712 @@
         <v>122</v>
       </c>
       <c r="B87" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C87" t="s">
-        <v>228</v>
-      </c>
-      <c r="D87" t="s">
-        <v>229</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>271</v>
+        <v>222</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E87" t="s">
+        <v>223</v>
       </c>
       <c r="F87" t="s">
         <v>9</v>
       </c>
       <c r="G87" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B88" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C88" t="s">
-        <v>232</v>
-      </c>
-      <c r="D88" t="s">
+        <v>226</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E88" t="s">
         <v>8</v>
       </c>
-      <c r="E88" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F88" t="s">
         <v>9</v>
       </c>
       <c r="G88" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B89" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C89" t="s">
-        <v>234</v>
-      </c>
-      <c r="D89" t="s">
+        <v>228</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E89" t="s">
         <v>8</v>
       </c>
-      <c r="E89" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F89" t="s">
         <v>9</v>
       </c>
       <c r="G89" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
+        <v>225</v>
+      </c>
+      <c r="B90" t="s">
+        <v>225</v>
+      </c>
+      <c r="C90" t="s">
+        <v>230</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E90" t="s">
+        <v>8</v>
+      </c>
+      <c r="F90" t="s">
+        <v>9</v>
+      </c>
+      <c r="G90" t="s">
         <v>231</v>
-      </c>
-      <c r="B90" t="s">
-        <v>231</v>
-      </c>
-      <c r="C90" t="s">
-        <v>236</v>
-      </c>
-      <c r="D90" t="s">
-        <v>8</v>
-      </c>
-      <c r="E90" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="F90" t="s">
-        <v>9</v>
-      </c>
-      <c r="G90" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B91" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C91" t="s">
-        <v>238</v>
-      </c>
-      <c r="D91" t="s">
+        <v>232</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E91" t="s">
         <v>8</v>
       </c>
-      <c r="E91" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F91" t="s">
         <v>9</v>
       </c>
       <c r="G91" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B92" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C92" t="s">
-        <v>240</v>
-      </c>
-      <c r="D92" t="s">
+        <v>234</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E92" t="s">
         <v>8</v>
       </c>
-      <c r="E92" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F92" t="s">
         <v>9</v>
       </c>
       <c r="G92" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B93" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C93" t="s">
-        <v>242</v>
-      </c>
-      <c r="D93" t="s">
+        <v>236</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E93" t="s">
         <v>8</v>
       </c>
-      <c r="E93" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F93" t="s">
         <v>9</v>
       </c>
       <c r="G93" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B94" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C94" t="s">
-        <v>245</v>
-      </c>
-      <c r="D94" t="s">
+        <v>239</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E94" t="s">
         <v>8</v>
       </c>
-      <c r="E94" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F94" t="s">
         <v>9</v>
       </c>
       <c r="G94" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B95" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C95" t="s">
-        <v>247</v>
-      </c>
-      <c r="D95" t="s">
+        <v>241</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E95" t="s">
         <v>8</v>
       </c>
-      <c r="E95" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F95" t="s">
         <v>9</v>
       </c>
       <c r="G95" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
+        <v>238</v>
+      </c>
+      <c r="B96" t="s">
+        <v>238</v>
+      </c>
+      <c r="C96" t="s">
+        <v>243</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E96" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" t="s">
+        <v>9</v>
+      </c>
+      <c r="G96" t="s">
         <v>244</v>
-      </c>
-      <c r="B96" t="s">
-        <v>244</v>
-      </c>
-      <c r="C96" t="s">
-        <v>249</v>
-      </c>
-      <c r="D96" t="s">
-        <v>8</v>
-      </c>
-      <c r="E96" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="F96" t="s">
-        <v>9</v>
-      </c>
-      <c r="G96" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B97" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C97" t="s">
-        <v>253</v>
-      </c>
-      <c r="D97" t="s">
+        <v>247</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E97" t="s">
         <v>8</v>
       </c>
-      <c r="E97" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F97" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G97" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B98" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C98" t="s">
-        <v>256</v>
-      </c>
-      <c r="D98" t="s">
+        <v>250</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E98" t="s">
         <v>27</v>
       </c>
-      <c r="E98" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F98" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G98" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
+        <v>245</v>
+      </c>
+      <c r="B99" t="s">
+        <v>246</v>
+      </c>
+      <c r="C99" t="s">
         <v>251</v>
       </c>
-      <c r="B99" t="s">
-        <v>252</v>
-      </c>
-      <c r="C99" t="s">
-        <v>257</v>
-      </c>
-      <c r="D99" t="s">
+      <c r="D99" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E99" t="s">
         <v>27</v>
       </c>
-      <c r="E99" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F99" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G99" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B100" t="s">
+        <v>246</v>
+      </c>
+      <c r="C100" t="s">
         <v>252</v>
       </c>
-      <c r="C100" t="s">
-        <v>258</v>
-      </c>
-      <c r="D100" t="s">
+      <c r="D100" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E100" t="s">
         <v>45</v>
       </c>
-      <c r="E100" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F100" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G100" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B101" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C101" t="s">
-        <v>259</v>
-      </c>
-      <c r="D101" t="s">
+        <v>253</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E101" t="s">
         <v>48</v>
       </c>
-      <c r="E101" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F101" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G101" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B102" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C102" t="s">
-        <v>260</v>
-      </c>
-      <c r="D102" t="s">
+        <v>254</v>
+      </c>
+      <c r="D102" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E102" t="s">
         <v>75</v>
       </c>
-      <c r="E102" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F102" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G102" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B103" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C103" t="s">
-        <v>261</v>
-      </c>
-      <c r="D103" t="s">
+        <v>255</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E103" t="s">
         <v>75</v>
       </c>
-      <c r="E103" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F103" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G103" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B104" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C104" t="s">
-        <v>263</v>
-      </c>
-      <c r="D104" t="s">
-        <v>264</v>
-      </c>
-      <c r="E104" s="5" t="s">
-        <v>271</v>
+        <v>257</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E104" t="s">
+        <v>258</v>
       </c>
       <c r="F104" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G104" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B105" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C105" t="s">
-        <v>265</v>
-      </c>
-      <c r="D105" t="s">
+        <v>259</v>
+      </c>
+      <c r="D105" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E105" t="s">
         <v>8</v>
       </c>
-      <c r="E105" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F105" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G105" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B106" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C106" t="s">
-        <v>266</v>
-      </c>
-      <c r="D106" t="s">
+        <v>260</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E106" t="s">
         <v>8</v>
       </c>
-      <c r="E106" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F106" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G106" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B107" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C107" t="s">
-        <v>267</v>
-      </c>
-      <c r="D107" t="s">
+        <v>261</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E107" t="s">
         <v>8</v>
       </c>
-      <c r="E107" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F107" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G107" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B108" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C108" t="s">
-        <v>268</v>
-      </c>
-      <c r="D108" t="s">
-        <v>269</v>
-      </c>
-      <c r="E108" s="5" t="s">
-        <v>271</v>
+        <v>262</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E108" t="s">
+        <v>263</v>
       </c>
       <c r="F108" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G108" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B109" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C109" t="s">
-        <v>270</v>
-      </c>
-      <c r="D109" t="s">
+        <v>264</v>
+      </c>
+      <c r="D109" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E109" t="s">
         <v>8</v>
       </c>
-      <c r="E109" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F109" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G109" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B110" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C110" t="s">
-        <v>145</v>
-      </c>
-      <c r="D110" t="s">
-        <v>141</v>
-      </c>
-      <c r="E110" s="5" t="s">
-        <v>271</v>
+        <v>143</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E110" t="s">
+        <v>139</v>
       </c>
       <c r="F110" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G110" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B111" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C111" t="s">
-        <v>147</v>
-      </c>
-      <c r="D111" t="s">
+        <v>145</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E111" t="s">
         <v>45</v>
       </c>
-      <c r="E111" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F111" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G111" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B112" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C112" t="s">
-        <v>149</v>
-      </c>
-      <c r="D112" t="s">
+        <v>278</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E112" t="s">
         <v>48</v>
       </c>
-      <c r="E112" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F112" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G112" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B113" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C113" t="s">
-        <v>151</v>
-      </c>
-      <c r="D113" t="s">
+        <v>147</v>
+      </c>
+      <c r="D113" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E113" t="s">
         <v>66</v>
       </c>
-      <c r="E113" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F113" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G113" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B114" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C114" t="s">
-        <v>153</v>
-      </c>
-      <c r="D114" t="s">
+        <v>149</v>
+      </c>
+      <c r="D114" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E114" t="s">
         <v>75</v>
       </c>
-      <c r="E114" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F114" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G114" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B115" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C115" t="s">
-        <v>155</v>
-      </c>
-      <c r="D115" t="s">
+        <v>151</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E115" t="s">
         <v>45</v>
       </c>
-      <c r="E115" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F115" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G115" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B116" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C116" t="s">
-        <v>157</v>
-      </c>
-      <c r="D116" t="s">
+        <v>153</v>
+      </c>
+      <c r="D116" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E116" t="s">
         <v>48</v>
       </c>
-      <c r="E116" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F116" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G116" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B117" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C117" t="s">
-        <v>159</v>
-      </c>
-      <c r="D117" t="s">
+        <v>155</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E117" t="s">
         <v>66</v>
       </c>
-      <c r="E117" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F117" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G117" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -3989,9 +4019,9 @@
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
-    <col min="4" max="4" width="72" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="3" max="3" width="23.06640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.73046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="60" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
     <col min="7" max="7" width="96" customWidth="1"/>
   </cols>
@@ -4006,11 +4036,11 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>272</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -4029,11 +4059,11 @@
       <c r="C2" t="s">
         <v>129</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E2" t="s">
         <v>130</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F2" t="s">
         <v>131</v>
@@ -4050,19 +4080,19 @@
         <v>128</v>
       </c>
       <c r="C3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E3" t="s">
         <v>93</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F3" t="s">
         <v>131</v>
       </c>
       <c r="G3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
@@ -4070,22 +4100,22 @@
         <v>122</v>
       </c>
       <c r="B4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" t="s">
         <v>144</v>
-      </c>
-      <c r="C4" t="s">
-        <v>145</v>
-      </c>
-      <c r="D4" t="s">
-        <v>141</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
@@ -4093,22 +4123,22 @@
         <v>122</v>
       </c>
       <c r="B5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E5" t="s">
         <v>45</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
@@ -4116,22 +4146,22 @@
         <v>122</v>
       </c>
       <c r="B6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E6" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F6" t="s">
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>150</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
@@ -4139,22 +4169,22 @@
         <v>122</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C7" t="s">
-        <v>151</v>
-      </c>
-      <c r="D7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E7" t="s">
         <v>66</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
@@ -4162,22 +4192,22 @@
         <v>122</v>
       </c>
       <c r="B8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C8" t="s">
-        <v>153</v>
-      </c>
-      <c r="D8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E8" t="s">
         <v>75</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -4214,7 +4244,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -4237,7 +4267,7 @@
         <v>130</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="F2" t="s">
         <v>131</v>
@@ -4254,19 +4284,19 @@
         <v>128</v>
       </c>
       <c r="C3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D3" t="s">
         <v>93</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="F3" t="s">
         <v>131</v>
       </c>
       <c r="G3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
@@ -4274,22 +4304,22 @@
         <v>122</v>
       </c>
       <c r="B4" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C4" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D4" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="F4" t="s">
         <v>131</v>
       </c>
       <c r="G4" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -4326,7 +4356,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -4340,22 +4370,22 @@
         <v>122</v>
       </c>
       <c r="B2" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C2" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D2" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
@@ -4363,22 +4393,22 @@
         <v>122</v>
       </c>
       <c r="B3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
@@ -4386,22 +4416,22 @@
         <v>122</v>
       </c>
       <c r="B4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C4" t="s">
         <v>198</v>
       </c>
-      <c r="C4" t="s">
-        <v>204</v>
-      </c>
       <c r="D4" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -4412,7 +4442,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.1328125" customWidth="1"/>
@@ -4435,7 +4465,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -4458,7 +4488,7 @@
         <v>11</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -4481,7 +4511,7 @@
         <v>14</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4501,10 +4531,10 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>276</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>271</v>
+        <v>18</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4524,19 +4554,19 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
@@ -4547,10 +4577,10 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="E6" t="s">
         <v>27</v>
@@ -4559,7 +4589,7 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
@@ -4567,13 +4597,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="E7" t="s">
         <v>27</v>
@@ -4582,7 +4612,7 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
@@ -4590,22 +4620,22 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>274</v>
+        <v>35</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
@@ -4616,19 +4646,19 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
@@ -4636,22 +4666,22 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
@@ -4659,22 +4689,22 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>111</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E11" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="F11" t="s">
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>34</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
@@ -4685,19 +4715,19 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>111</v>
+        <v>65</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E12" t="s">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="F12" t="s">
         <v>9</v>
       </c>
       <c r="G12" t="s">
-        <v>113</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
@@ -4708,19 +4738,19 @@
         <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>271</v>
+        <v>72</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="E13" t="s">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
         <v>9</v>
       </c>
       <c r="G13" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
@@ -4728,22 +4758,22 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>274</v>
+        <v>74</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="F14" t="s">
         <v>9</v>
       </c>
       <c r="G14" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
@@ -4751,22 +4781,22 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E15" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F15" t="s">
         <v>9</v>
       </c>
       <c r="G15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
@@ -4777,19 +4807,19 @@
         <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E16" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="F16" t="s">
         <v>9</v>
       </c>
       <c r="G16" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
@@ -4800,19 +4830,19 @@
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E17" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="F17" t="s">
         <v>9</v>
       </c>
       <c r="G17" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
@@ -4820,13 +4850,13 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E18" t="s">
         <v>75</v>
@@ -4835,7 +4865,7 @@
         <v>9</v>
       </c>
       <c r="G18" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
@@ -4843,22 +4873,22 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E19" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F19" t="s">
         <v>9</v>
       </c>
       <c r="G19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
@@ -4869,19 +4899,19 @@
         <v>6</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E20" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="F20" t="s">
         <v>9</v>
       </c>
       <c r="G20" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
@@ -4892,19 +4922,19 @@
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E21" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="F21" t="s">
         <v>9</v>
       </c>
       <c r="G21" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
@@ -4915,19 +4945,19 @@
         <v>6</v>
       </c>
       <c r="C22" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>271</v>
+        <v>7</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="E22" t="s">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
         <v>9</v>
       </c>
       <c r="G22" t="s">
-        <v>80</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
@@ -4938,10 +4968,10 @@
         <v>6</v>
       </c>
       <c r="C23" t="s">
-        <v>7</v>
+        <v>269</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -4950,7 +4980,7 @@
         <v>9</v>
       </c>
       <c r="G23" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
@@ -4961,10 +4991,10 @@
         <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>275</v>
+        <v>68</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -4973,7 +5003,7 @@
         <v>9</v>
       </c>
       <c r="G24" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
@@ -4984,10 +5014,10 @@
         <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -4996,7 +5026,7 @@
         <v>9</v>
       </c>
       <c r="G25" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
@@ -5007,19 +5037,19 @@
         <v>6</v>
       </c>
       <c r="C26" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="F26" t="s">
         <v>9</v>
       </c>
       <c r="G26" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
@@ -5030,19 +5060,19 @@
         <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>102</v>
+        <v>16</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="E27" t="s">
-        <v>103</v>
+        <v>8</v>
       </c>
       <c r="F27" t="s">
         <v>9</v>
       </c>
       <c r="G27" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
@@ -5053,19 +5083,19 @@
         <v>6</v>
       </c>
       <c r="C28" t="s">
-        <v>16</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>274</v>
+        <v>52</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="E28" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="F28" t="s">
         <v>9</v>
       </c>
       <c r="G28" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
@@ -5076,19 +5106,19 @@
         <v>6</v>
       </c>
       <c r="C29" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E29" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F29" t="s">
         <v>9</v>
       </c>
       <c r="G29" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
@@ -5099,19 +5129,19 @@
         <v>6</v>
       </c>
       <c r="C30" t="s">
-        <v>44</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>271</v>
+        <v>58</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="E30" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F30" t="s">
         <v>9</v>
       </c>
       <c r="G30" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
@@ -5119,22 +5149,22 @@
         <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C31" t="s">
-        <v>58</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>274</v>
+        <v>47</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="E31" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="F31" t="s">
         <v>9</v>
       </c>
       <c r="G31" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
@@ -5142,22 +5172,22 @@
         <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C32" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E32" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F32" t="s">
         <v>9</v>
       </c>
       <c r="G32" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
@@ -5168,19 +5198,19 @@
         <v>6</v>
       </c>
       <c r="C33" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E33" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F33" t="s">
         <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
@@ -5188,22 +5218,22 @@
         <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C34" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E34" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F34" t="s">
         <v>9</v>
       </c>
       <c r="G34" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
@@ -5211,22 +5241,22 @@
         <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E35" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="F35" t="s">
         <v>9</v>
       </c>
       <c r="G35" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
@@ -5237,19 +5267,19 @@
         <v>6</v>
       </c>
       <c r="C36" t="s">
-        <v>62</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>271</v>
+        <v>24</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="E36" t="s">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="F36" t="s">
         <v>9</v>
       </c>
       <c r="G36" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
@@ -5257,22 +5287,22 @@
         <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C37" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E37" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="F37" t="s">
         <v>9</v>
       </c>
       <c r="G37" t="s">
-        <v>23</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
@@ -5283,10 +5313,10 @@
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>24</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>271</v>
+        <v>70</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -5295,7 +5325,7 @@
         <v>9</v>
       </c>
       <c r="G38" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
@@ -5306,19 +5336,19 @@
         <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>105</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>271</v>
+        <v>56</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="E39" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="F39" t="s">
         <v>9</v>
       </c>
       <c r="G39" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
@@ -5329,10 +5359,10 @@
         <v>6</v>
       </c>
       <c r="C40" t="s">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -5341,7 +5371,7 @@
         <v>9</v>
       </c>
       <c r="G40" t="s">
-        <v>71</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
@@ -5352,19 +5382,19 @@
         <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="E41" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F41" t="s">
         <v>9</v>
       </c>
       <c r="G41" t="s">
-        <v>57</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
@@ -5375,19 +5405,19 @@
         <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="E42" t="s">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="F42" t="s">
         <v>9</v>
       </c>
       <c r="G42" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
@@ -5398,19 +5428,19 @@
         <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E43" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F43" t="s">
         <v>9</v>
       </c>
       <c r="G43" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
@@ -5421,19 +5451,19 @@
         <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>97</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>274</v>
+        <v>116</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="E44" t="s">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="F44" t="s">
         <v>9</v>
       </c>
       <c r="G44" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
@@ -5444,10 +5474,10 @@
         <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -5456,59 +5486,13 @@
         <v>9</v>
       </c>
       <c r="G45" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A46" t="s">
-        <v>6</v>
-      </c>
-      <c r="B46" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" t="s">
-        <v>116</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="E46" t="s">
-        <v>8</v>
-      </c>
-      <c r="F46" t="s">
-        <v>9</v>
-      </c>
-      <c r="G46" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A47" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" t="s">
-        <v>118</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="E47" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" t="s">
-        <v>9</v>
-      </c>
-      <c r="G47" t="s">
         <v>119</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G47" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G47">
-      <sortCondition ref="C1:C47"/>
+  <autoFilter ref="A1:G45" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G45">
+      <sortCondition ref="C1:C45"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5521,10 +5505,10 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
-    <col min="4" max="4" width="72" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="2" max="2" width="24.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.6640625" customWidth="1"/>
+    <col min="4" max="4" width="13.53125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="96.46484375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
     <col min="7" max="7" width="96" customWidth="1"/>
   </cols>
@@ -5539,11 +5523,11 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>272</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -5560,19 +5544,19 @@
         <v>122</v>
       </c>
       <c r="C2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D2" t="s">
-        <v>45</v>
+        <v>275</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="E2" t="s">
-        <v>271</v>
+        <v>134</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
@@ -5580,22 +5564,22 @@
         <v>122</v>
       </c>
       <c r="B3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D3" t="s">
-        <v>126</v>
+        <v>136</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="E3" t="s">
-        <v>271</v>
+        <v>93</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>131</v>
       </c>
       <c r="G3" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
@@ -5603,22 +5587,22 @@
         <v>122</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D4" t="s">
-        <v>130</v>
+        <v>283</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="E4" t="s">
-        <v>271</v>
+        <v>171</v>
       </c>
       <c r="F4" t="s">
-        <v>131</v>
+        <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>132</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
@@ -5626,22 +5610,22 @@
         <v>122</v>
       </c>
       <c r="B5" t="s">
-        <v>122</v>
+        <v>166</v>
       </c>
       <c r="C5" t="s">
-        <v>133</v>
-      </c>
-      <c r="D5" t="s">
-        <v>66</v>
+        <v>285</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="E5" t="s">
-        <v>271</v>
+        <v>168</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>134</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
@@ -5652,19 +5636,19 @@
         <v>122</v>
       </c>
       <c r="C6" t="s">
-        <v>135</v>
-      </c>
-      <c r="D6" t="s">
-        <v>136</v>
+        <v>271</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="E6" t="s">
-        <v>271</v>
+        <v>66</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>137</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
@@ -5672,22 +5656,22 @@
         <v>122</v>
       </c>
       <c r="B7" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C7" t="s">
-        <v>138</v>
-      </c>
-      <c r="D7" t="s">
-        <v>93</v>
+        <v>125</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="E7" t="s">
-        <v>271</v>
+        <v>126</v>
       </c>
       <c r="F7" t="s">
-        <v>131</v>
+        <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
@@ -5695,22 +5679,22 @@
         <v>122</v>
       </c>
       <c r="B8" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C8" t="s">
-        <v>140</v>
-      </c>
-      <c r="D8" t="s">
-        <v>141</v>
+        <v>129</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="E8" t="s">
-        <v>271</v>
+        <v>130</v>
       </c>
       <c r="F8" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="G8" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
@@ -5718,22 +5702,22 @@
         <v>122</v>
       </c>
       <c r="B9" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="C9" t="s">
-        <v>145</v>
-      </c>
-      <c r="D9" t="s">
-        <v>141</v>
+        <v>270</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="E9" t="s">
-        <v>271</v>
+        <v>45</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
@@ -5741,22 +5725,22 @@
         <v>122</v>
       </c>
       <c r="B10" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="C10" t="s">
-        <v>147</v>
-      </c>
-      <c r="D10" t="s">
-        <v>45</v>
+        <v>176</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="E10" t="s">
-        <v>271</v>
+        <v>177</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
@@ -5764,22 +5748,22 @@
         <v>122</v>
       </c>
       <c r="B11" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="C11" t="s">
-        <v>149</v>
-      </c>
-      <c r="D11" t="s">
-        <v>48</v>
+        <v>173</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="E11" t="s">
-        <v>271</v>
+        <v>174</v>
       </c>
       <c r="F11" t="s">
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
@@ -5787,22 +5771,22 @@
         <v>122</v>
       </c>
       <c r="B12" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="C12" t="s">
-        <v>151</v>
-      </c>
-      <c r="D12" t="s">
-        <v>66</v>
+        <v>182</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="E12" t="s">
-        <v>271</v>
+        <v>27</v>
       </c>
       <c r="F12" t="s">
         <v>9</v>
       </c>
       <c r="G12" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
@@ -5810,22 +5794,22 @@
         <v>122</v>
       </c>
       <c r="B13" t="s">
-        <v>144</v>
+        <v>184</v>
       </c>
       <c r="C13" t="s">
-        <v>153</v>
-      </c>
-      <c r="D13" t="s">
-        <v>75</v>
+        <v>185</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="E13" t="s">
-        <v>271</v>
+        <v>186</v>
       </c>
       <c r="F13" t="s">
-        <v>9</v>
+        <v>131</v>
       </c>
       <c r="G13" t="s">
-        <v>154</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
@@ -5836,19 +5820,19 @@
         <v>122</v>
       </c>
       <c r="C14" t="s">
-        <v>155</v>
-      </c>
-      <c r="D14" t="s">
-        <v>45</v>
+        <v>160</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="E14" t="s">
-        <v>271</v>
+        <v>161</v>
       </c>
       <c r="F14" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G14" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
@@ -5856,22 +5840,22 @@
         <v>122</v>
       </c>
       <c r="B15" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="C15" t="s">
-        <v>157</v>
-      </c>
-      <c r="D15" t="s">
-        <v>48</v>
+        <v>149</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="E15" t="s">
-        <v>271</v>
+        <v>75</v>
       </c>
       <c r="F15" t="s">
-        <v>142</v>
+        <v>9</v>
       </c>
       <c r="G15" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
@@ -5882,19 +5866,19 @@
         <v>122</v>
       </c>
       <c r="C16" t="s">
-        <v>159</v>
-      </c>
-      <c r="D16" t="s">
+        <v>155</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E16" t="s">
         <v>66</v>
       </c>
-      <c r="E16" t="s">
-        <v>271</v>
-      </c>
       <c r="F16" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G16" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
@@ -5902,22 +5886,22 @@
         <v>122</v>
       </c>
       <c r="B17" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="C17" t="s">
-        <v>161</v>
-      </c>
-      <c r="D17" t="s">
-        <v>162</v>
+        <v>273</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="E17" t="s">
-        <v>271</v>
+        <v>66</v>
       </c>
       <c r="F17" t="s">
-        <v>142</v>
+        <v>9</v>
       </c>
       <c r="G17" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
@@ -5928,19 +5912,19 @@
         <v>122</v>
       </c>
       <c r="C18" t="s">
-        <v>164</v>
-      </c>
-      <c r="D18" t="s">
-        <v>162</v>
+        <v>277</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="E18" t="s">
-        <v>271</v>
+        <v>158</v>
       </c>
       <c r="F18" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G18" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
@@ -5948,22 +5932,22 @@
         <v>122</v>
       </c>
       <c r="B19" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="C19" t="s">
-        <v>166</v>
-      </c>
-      <c r="D19" t="s">
-        <v>167</v>
+        <v>280</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="E19" t="s">
-        <v>271</v>
+        <v>48</v>
       </c>
       <c r="F19" t="s">
-        <v>142</v>
+        <v>9</v>
       </c>
       <c r="G19" t="s">
-        <v>168</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
@@ -5974,19 +5958,19 @@
         <v>122</v>
       </c>
       <c r="C20" t="s">
-        <v>169</v>
-      </c>
-      <c r="D20" t="s">
-        <v>170</v>
+        <v>274</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="E20" t="s">
-        <v>271</v>
+        <v>158</v>
       </c>
       <c r="F20" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G20" t="s">
-        <v>171</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
@@ -5994,22 +5978,22 @@
         <v>122</v>
       </c>
       <c r="B21" t="s">
-        <v>172</v>
+        <v>122</v>
       </c>
       <c r="C21" t="s">
-        <v>173</v>
-      </c>
-      <c r="D21" t="s">
-        <v>174</v>
+        <v>179</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="E21" t="s">
-        <v>271</v>
+        <v>180</v>
       </c>
       <c r="F21" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="G21" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
@@ -6017,22 +6001,22 @@
         <v>122</v>
       </c>
       <c r="B22" t="s">
-        <v>172</v>
+        <v>122</v>
       </c>
       <c r="C22" t="s">
-        <v>176</v>
-      </c>
-      <c r="D22" t="s">
-        <v>177</v>
+        <v>151</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="E22" t="s">
-        <v>271</v>
+        <v>45</v>
       </c>
       <c r="F22" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="G22" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
@@ -6040,22 +6024,22 @@
         <v>122</v>
       </c>
       <c r="B23" t="s">
-        <v>172</v>
+        <v>122</v>
       </c>
       <c r="C23" t="s">
-        <v>179</v>
-      </c>
-      <c r="D23" t="s">
-        <v>180</v>
+        <v>153</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="E23" t="s">
-        <v>271</v>
+        <v>48</v>
       </c>
       <c r="F23" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="G23" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
@@ -6063,22 +6047,22 @@
         <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>172</v>
+        <v>122</v>
       </c>
       <c r="C24" t="s">
-        <v>182</v>
-      </c>
-      <c r="D24" t="s">
-        <v>183</v>
+        <v>138</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="E24" t="s">
-        <v>271</v>
+        <v>139</v>
       </c>
       <c r="F24" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="G24" t="s">
-        <v>184</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
@@ -6086,22 +6070,22 @@
         <v>122</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="C25" t="s">
-        <v>185</v>
-      </c>
-      <c r="D25" t="s">
-        <v>186</v>
+        <v>272</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="E25" t="s">
-        <v>271</v>
+        <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>142</v>
+        <v>9</v>
       </c>
       <c r="G25" t="s">
-        <v>187</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
@@ -6109,22 +6093,22 @@
         <v>122</v>
       </c>
       <c r="B26" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="C26" t="s">
-        <v>188</v>
-      </c>
-      <c r="D26" t="s">
-        <v>27</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>271</v>
+        <v>143</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E26" t="s">
+        <v>139</v>
       </c>
       <c r="F26" t="s">
         <v>9</v>
       </c>
       <c r="G26" t="s">
-        <v>189</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
@@ -6132,22 +6116,22 @@
         <v>122</v>
       </c>
       <c r="B27" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C27" t="s">
-        <v>191</v>
-      </c>
-      <c r="D27" t="s">
-        <v>192</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>271</v>
+        <v>198</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E27" t="s">
+        <v>199</v>
       </c>
       <c r="F27" t="s">
-        <v>131</v>
+        <v>9</v>
       </c>
       <c r="G27" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
@@ -6155,22 +6139,22 @@
         <v>122</v>
       </c>
       <c r="B28" t="s">
-        <v>122</v>
+        <v>192</v>
       </c>
       <c r="C28" t="s">
+        <v>196</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E28" t="s">
         <v>194</v>
       </c>
-      <c r="D28" t="s">
-        <v>27</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F28" t="s">
         <v>9</v>
       </c>
       <c r="G28" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
@@ -6178,22 +6162,22 @@
         <v>122</v>
       </c>
       <c r="B29" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="C29" t="s">
-        <v>196</v>
-      </c>
-      <c r="D29" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>271</v>
+        <v>193</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E29" t="s">
+        <v>194</v>
       </c>
       <c r="F29" t="s">
         <v>9</v>
       </c>
       <c r="G29" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
@@ -6201,22 +6185,22 @@
         <v>122</v>
       </c>
       <c r="B30" t="s">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="C30" t="s">
-        <v>199</v>
-      </c>
-      <c r="D30" t="s">
-        <v>200</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>271</v>
+        <v>219</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E30" t="s">
+        <v>220</v>
       </c>
       <c r="F30" t="s">
         <v>9</v>
       </c>
       <c r="G30" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
@@ -6224,16 +6208,16 @@
         <v>122</v>
       </c>
       <c r="B31" t="s">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="C31" t="s">
+        <v>201</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E31" t="s">
         <v>202</v>
-      </c>
-      <c r="D31" t="s">
-        <v>200</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F31" t="s">
         <v>9</v>
@@ -6247,22 +6231,22 @@
         <v>122</v>
       </c>
       <c r="B32" t="s">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="C32" t="s">
-        <v>204</v>
-      </c>
-      <c r="D32" t="s">
-        <v>205</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>271</v>
+        <v>213</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E32" t="s">
+        <v>214</v>
       </c>
       <c r="F32" t="s">
         <v>9</v>
       </c>
       <c r="G32" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
@@ -6270,22 +6254,22 @@
         <v>122</v>
       </c>
       <c r="B33" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C33" t="s">
-        <v>207</v>
-      </c>
-      <c r="D33" t="s">
-        <v>208</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>271</v>
+        <v>204</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E33" t="s">
+        <v>205</v>
       </c>
       <c r="F33" t="s">
         <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
@@ -6293,16 +6277,16 @@
         <v>122</v>
       </c>
       <c r="B34" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C34" t="s">
         <v>210</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E34" t="s">
         <v>211</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F34" t="s">
         <v>9</v>
@@ -6316,22 +6300,22 @@
         <v>122</v>
       </c>
       <c r="B35" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C35" t="s">
-        <v>213</v>
-      </c>
-      <c r="D35" t="s">
-        <v>214</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>271</v>
+        <v>216</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E35" t="s">
+        <v>217</v>
       </c>
       <c r="F35" t="s">
         <v>9</v>
       </c>
       <c r="G35" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
@@ -6339,22 +6323,22 @@
         <v>122</v>
       </c>
       <c r="B36" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C36" t="s">
-        <v>216</v>
-      </c>
-      <c r="D36" t="s">
-        <v>217</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>271</v>
+        <v>207</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E36" t="s">
+        <v>208</v>
       </c>
       <c r="F36" t="s">
         <v>9</v>
       </c>
       <c r="G36" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
@@ -6362,22 +6346,22 @@
         <v>122</v>
       </c>
       <c r="B37" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C37" t="s">
-        <v>219</v>
-      </c>
-      <c r="D37" t="s">
-        <v>220</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>271</v>
+        <v>222</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E37" t="s">
+        <v>223</v>
       </c>
       <c r="F37" t="s">
         <v>9</v>
       </c>
       <c r="G37" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
@@ -6385,22 +6369,22 @@
         <v>122</v>
       </c>
       <c r="B38" t="s">
-        <v>172</v>
+        <v>122</v>
       </c>
       <c r="C38" t="s">
-        <v>222</v>
-      </c>
-      <c r="D38" t="s">
-        <v>223</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>271</v>
+        <v>163</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E38" t="s">
+        <v>164</v>
       </c>
       <c r="F38" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="G38" t="s">
-        <v>224</v>
+        <v>165</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
@@ -6408,22 +6392,22 @@
         <v>122</v>
       </c>
       <c r="B39" t="s">
-        <v>172</v>
+        <v>122</v>
       </c>
       <c r="C39" t="s">
-        <v>225</v>
-      </c>
-      <c r="D39" t="s">
-        <v>226</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>271</v>
+        <v>188</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E39" t="s">
+        <v>27</v>
       </c>
       <c r="F39" t="s">
         <v>9</v>
       </c>
       <c r="G39" t="s">
-        <v>227</v>
+        <v>189</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
@@ -6431,26 +6415,30 @@
         <v>122</v>
       </c>
       <c r="B40" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C40" t="s">
-        <v>228</v>
-      </c>
-      <c r="D40" t="s">
-        <v>229</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>271</v>
+        <v>190</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
       </c>
       <c r="F40" t="s">
         <v>9</v>
       </c>
       <c r="G40" t="s">
-        <v>230</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G40" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:G40" xr:uid="{00000000-0009-0000-0000-000002000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G40">
+      <sortCondition ref="C1:C40"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6460,12 +6448,12 @@
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
-    <col min="4" max="4" width="11.9296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="1" max="1" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.73046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.9296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.9296875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="96" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6479,11 +6467,11 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>272</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -6494,140 +6482,140 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B2" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B3" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C3" t="s">
-        <v>234</v>
-      </c>
-      <c r="D3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="E3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C4" t="s">
+        <v>230</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" t="s">
         <v>231</v>
-      </c>
-      <c r="B4" t="s">
-        <v>231</v>
-      </c>
-      <c r="C4" t="s">
-        <v>236</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B5" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C5" t="s">
-        <v>238</v>
-      </c>
-      <c r="D5" t="s">
+        <v>232</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E5" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B6" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C6" t="s">
-        <v>240</v>
-      </c>
-      <c r="D6" t="s">
+        <v>234</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E6" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F6" t="s">
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B7" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C7" t="s">
-        <v>242</v>
-      </c>
-      <c r="D7" t="s">
+        <v>236</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E7" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -6644,8 +6632,8 @@
     <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.59765625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.9296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" style="4" customWidth="1"/>
+    <col min="4" max="4" width="12" style="4" customWidth="1"/>
+    <col min="5" max="5" width="11.9296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.9296875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="96" customWidth="1"/>
   </cols>
@@ -6660,11 +6648,11 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>272</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -6675,71 +6663,71 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B2" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C2" t="s">
-        <v>245</v>
-      </c>
-      <c r="D2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B3" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C3" t="s">
-        <v>247</v>
-      </c>
-      <c r="D3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C4" t="s">
+        <v>243</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" t="s">
         <v>244</v>
-      </c>
-      <c r="B4" t="s">
-        <v>244</v>
-      </c>
-      <c r="C4" t="s">
-        <v>249</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" t="s">
-        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -6756,8 +6744,8 @@
     <col min="1" max="1" width="18.265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.59765625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="72" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="60" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
     <col min="7" max="7" width="96" customWidth="1"/>
   </cols>
@@ -6772,11 +6760,11 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>272</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -6787,485 +6775,485 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B2" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F2" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B3" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C3" t="s">
-        <v>256</v>
-      </c>
-      <c r="D3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E3" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F3" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" t="s">
         <v>251</v>
       </c>
-      <c r="B4" t="s">
-        <v>252</v>
-      </c>
-      <c r="C4" t="s">
-        <v>257</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="D4" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E4" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F4" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G4" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C5" t="s">
         <v>252</v>
       </c>
-      <c r="C5" t="s">
-        <v>258</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="D5" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E5" t="s">
         <v>45</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F5" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G5" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B6" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C6" t="s">
-        <v>259</v>
-      </c>
-      <c r="D6" t="s">
+        <v>253</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E6" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F6" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G6" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B7" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C7" t="s">
-        <v>260</v>
-      </c>
-      <c r="D7" t="s">
+        <v>254</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E7" t="s">
         <v>75</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F7" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G7" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B8" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C8" t="s">
-        <v>261</v>
-      </c>
-      <c r="D8" t="s">
+        <v>255</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E8" t="s">
         <v>75</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F8" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G8" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B9" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C9" t="s">
-        <v>263</v>
-      </c>
-      <c r="D9" t="s">
-        <v>264</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>271</v>
+        <v>257</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E9" t="s">
+        <v>258</v>
       </c>
       <c r="F9" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G9" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B10" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C10" t="s">
-        <v>265</v>
-      </c>
-      <c r="D10" t="s">
+        <v>259</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E10" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F10" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G10" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B11" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C11" t="s">
-        <v>266</v>
-      </c>
-      <c r="D11" t="s">
+        <v>260</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E11" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F11" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G11" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B12" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C12" t="s">
-        <v>267</v>
-      </c>
-      <c r="D12" t="s">
+        <v>261</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E12" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F12" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G12" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B13" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C13" t="s">
-        <v>268</v>
-      </c>
-      <c r="D13" t="s">
-        <v>269</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>271</v>
+        <v>262</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E13" t="s">
+        <v>263</v>
       </c>
       <c r="F13" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G13" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B14" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C14" t="s">
-        <v>270</v>
-      </c>
-      <c r="D14" t="s">
+        <v>264</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E14" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F14" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G14" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B15" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D15" t="s">
-        <v>141</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>271</v>
+        <v>143</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E15" t="s">
+        <v>139</v>
       </c>
       <c r="F15" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G15" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B16" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C16" t="s">
-        <v>147</v>
-      </c>
-      <c r="D16" t="s">
+        <v>145</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E16" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F16" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G16" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B17" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C17" t="s">
-        <v>149</v>
-      </c>
-      <c r="D17" t="s">
+        <v>278</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E17" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F17" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G17" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B18" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C18" t="s">
-        <v>151</v>
-      </c>
-      <c r="D18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E18" t="s">
         <v>66</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F18" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G18" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B19" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C19" t="s">
-        <v>153</v>
-      </c>
-      <c r="D19" t="s">
+        <v>149</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E19" t="s">
         <v>75</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F19" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G19" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B20" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C20" t="s">
-        <v>155</v>
-      </c>
-      <c r="D20" t="s">
+        <v>151</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E20" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F20" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G20" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B21" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C21" t="s">
-        <v>157</v>
-      </c>
-      <c r="D21" t="s">
+        <v>153</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E21" t="s">
         <v>48</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F21" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G21" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B22" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C22" t="s">
-        <v>159</v>
-      </c>
-      <c r="D22" t="s">
+        <v>155</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E22" t="s">
         <v>66</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F22" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G22" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -7282,8 +7270,8 @@
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
-    <col min="4" max="4" width="72" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="96.46484375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
     <col min="7" max="7" width="96" customWidth="1"/>
   </cols>
@@ -7298,11 +7286,11 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>272</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -7316,22 +7304,22 @@
         <v>122</v>
       </c>
       <c r="B2" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>271</v>
+        <v>285</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E2" t="s">
+        <v>168</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>175</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
@@ -7339,22 +7327,22 @@
         <v>122</v>
       </c>
       <c r="B3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>271</v>
+        <v>283</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E3" t="s">
+        <v>171</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>178</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
@@ -7362,22 +7350,22 @@
         <v>122</v>
       </c>
       <c r="B4" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
-        <v>179</v>
-      </c>
-      <c r="D4" t="s">
-        <v>180</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>271</v>
+        <v>173</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E4" t="s">
+        <v>174</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
@@ -7385,22 +7373,22 @@
         <v>122</v>
       </c>
       <c r="B5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D5" t="s">
-        <v>183</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>271</v>
+        <v>176</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E5" t="s">
+        <v>177</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
@@ -7408,22 +7396,22 @@
         <v>122</v>
       </c>
       <c r="B6" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C6" t="s">
-        <v>196</v>
-      </c>
-      <c r="D6" t="s">
+        <v>190</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E6" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F6" t="s">
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
@@ -7431,22 +7419,22 @@
         <v>122</v>
       </c>
       <c r="B7" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C7" t="s">
-        <v>207</v>
-      </c>
-      <c r="D7" t="s">
-        <v>208</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>271</v>
+        <v>201</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E7" t="s">
+        <v>202</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
@@ -7454,22 +7442,22 @@
         <v>122</v>
       </c>
       <c r="B8" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C8" t="s">
-        <v>210</v>
-      </c>
-      <c r="D8" t="s">
-        <v>211</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>271</v>
+        <v>204</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E8" t="s">
+        <v>205</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
@@ -7477,22 +7465,22 @@
         <v>122</v>
       </c>
       <c r="B9" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C9" t="s">
-        <v>213</v>
-      </c>
-      <c r="D9" t="s">
-        <v>214</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>271</v>
+        <v>207</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E9" t="s">
+        <v>208</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
@@ -7500,22 +7488,22 @@
         <v>122</v>
       </c>
       <c r="B10" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C10" t="s">
-        <v>216</v>
-      </c>
-      <c r="D10" t="s">
-        <v>217</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>271</v>
+        <v>210</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E10" t="s">
+        <v>211</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
@@ -7523,22 +7511,22 @@
         <v>122</v>
       </c>
       <c r="B11" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C11" t="s">
-        <v>219</v>
-      </c>
-      <c r="D11" t="s">
-        <v>220</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>271</v>
+        <v>213</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E11" t="s">
+        <v>214</v>
       </c>
       <c r="F11" t="s">
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
@@ -7546,22 +7534,22 @@
         <v>122</v>
       </c>
       <c r="B12" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C12" t="s">
-        <v>222</v>
-      </c>
-      <c r="D12" t="s">
-        <v>223</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>271</v>
+        <v>216</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E12" t="s">
+        <v>217</v>
       </c>
       <c r="F12" t="s">
         <v>9</v>
       </c>
       <c r="G12" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
@@ -7569,22 +7557,22 @@
         <v>122</v>
       </c>
       <c r="B13" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C13" t="s">
-        <v>225</v>
-      </c>
-      <c r="D13" t="s">
-        <v>226</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>271</v>
+        <v>219</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E13" t="s">
+        <v>220</v>
       </c>
       <c r="F13" t="s">
         <v>9</v>
       </c>
       <c r="G13" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
@@ -7592,252 +7580,252 @@
         <v>122</v>
       </c>
       <c r="B14" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C14" t="s">
-        <v>228</v>
-      </c>
-      <c r="D14" t="s">
-        <v>229</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>271</v>
+        <v>222</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E14" t="s">
+        <v>223</v>
       </c>
       <c r="F14" t="s">
         <v>9</v>
       </c>
       <c r="G14" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B15" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C15" t="s">
-        <v>268</v>
-      </c>
-      <c r="D15" t="s">
-        <v>269</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>271</v>
+        <v>262</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E15" t="s">
+        <v>263</v>
       </c>
       <c r="F15" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G15" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B16" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C16" t="s">
-        <v>270</v>
-      </c>
-      <c r="D16" t="s">
+        <v>264</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E16" t="s">
         <v>8</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F16" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G16" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B17" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C17" t="s">
-        <v>145</v>
-      </c>
-      <c r="D17" t="s">
-        <v>141</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>271</v>
+        <v>143</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E17" t="s">
+        <v>139</v>
       </c>
       <c r="F17" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G17" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B18" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C18" t="s">
-        <v>147</v>
-      </c>
-      <c r="D18" t="s">
+        <v>145</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E18" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F18" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G18" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B19" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C19" t="s">
-        <v>149</v>
-      </c>
-      <c r="D19" t="s">
+        <v>278</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E19" t="s">
         <v>48</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F19" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G19" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B20" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C20" t="s">
-        <v>151</v>
-      </c>
-      <c r="D20" t="s">
+        <v>147</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E20" t="s">
         <v>66</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F20" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G20" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B21" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C21" t="s">
-        <v>153</v>
-      </c>
-      <c r="D21" t="s">
+        <v>149</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E21" t="s">
         <v>75</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F21" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G21" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B22" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C22" t="s">
-        <v>155</v>
-      </c>
-      <c r="D22" t="s">
+        <v>151</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E22" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F22" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G22" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B23" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C23" t="s">
-        <v>157</v>
-      </c>
-      <c r="D23" t="s">
+        <v>153</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E23" t="s">
         <v>48</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F23" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G23" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C24" t="s">
-        <v>159</v>
-      </c>
-      <c r="D24" t="s">
+        <v>155</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E24" t="s">
         <v>66</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F24" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G24" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -7854,9 +7842,9 @@
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
-    <col min="4" max="4" width="72" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="42" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.796875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="96" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7870,11 +7858,11 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>272</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -7885,94 +7873,94 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B2" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>271</v>
+        <v>257</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E2" t="s">
+        <v>258</v>
       </c>
       <c r="F2" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B3" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C3" t="s">
-        <v>265</v>
-      </c>
-      <c r="D3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F3" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B4" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C4" t="s">
-        <v>266</v>
-      </c>
-      <c r="D4" t="s">
+        <v>260</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E4" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F4" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G4" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B5" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C5" t="s">
-        <v>267</v>
-      </c>
-      <c r="D5" t="s">
+        <v>261</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E5" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F5" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G5" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -7989,8 +7977,8 @@
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
-    <col min="4" max="4" width="72" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="72" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
     <col min="7" max="7" width="96" customWidth="1"/>
   </cols>
@@ -8005,11 +7993,11 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>272</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -8028,11 +8016,11 @@
       <c r="C2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E2" t="s">
         <v>22</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
@@ -8051,11 +8039,11 @@
       <c r="C3" t="s">
         <v>31</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E3" t="s">
         <v>27</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
@@ -8074,11 +8062,11 @@
       <c r="C4" t="s">
         <v>33</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E4" t="s">
         <v>27</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
@@ -8097,11 +8085,11 @@
       <c r="C5" t="s">
         <v>47</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E5" t="s">
         <v>48</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
@@ -8120,11 +8108,11 @@
       <c r="C6" t="s">
         <v>60</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E6" t="s">
         <v>45</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
@@ -8143,11 +8131,11 @@
       <c r="C7" t="s">
         <v>74</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E7" t="s">
         <v>75</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
@@ -8166,11 +8154,11 @@
       <c r="C8" t="s">
         <v>88</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E8" t="s">
         <v>75</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>

--- a/docs/DropDownAccessMethods.xlsx
+++ b/docs/DropDownAccessMethods.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robin\spCoin\SPCOIN-PROJECT-MODULES\spcoin-nextjs-front-end\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30EE1390-4264-4B6C-9A6E-0C498D7A8B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797364A7-8A36-408E-AE3A-023054E16581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Methods" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2016" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2009" uniqueCount="289">
   <si>
     <t>Panel</t>
   </si>
@@ -81,12 +81,6 @@
     <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/creationTime.ts</t>
   </si>
   <si>
-    <t>getMasterAccountList</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getMasterAccountList.ts</t>
-  </si>
-  <si>
     <t>getAccountListSize</t>
   </si>
   <si>
@@ -165,15 +159,9 @@
     <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getRateTransactionList.ts</t>
   </si>
   <si>
-    <t>getRecipientRateList</t>
-  </si>
-  <si>
     <t>Sponsor Key, Recipient Key</t>
   </si>
   <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getRecipientRateList.ts</t>
-  </si>
-  <si>
     <t>getRecipientRateRecord</t>
   </si>
   <si>
@@ -189,12 +177,6 @@
     <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getRecipientRateRecordList.ts</t>
   </si>
   <si>
-    <t>getRecipientRateAgentList</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getRecipientRateAgentList.ts</t>
-  </si>
-  <si>
     <t>getLowerRecipientRate</t>
   </si>
   <si>
@@ -228,15 +210,9 @@
     <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getRecipientRecordList.ts</t>
   </si>
   <si>
-    <t>getAgentRateList</t>
-  </si>
-  <si>
     <t>Sponsor Key, Recipient Key, Recipient Rate Key, Agent Key</t>
   </si>
   <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getAgentRateList.ts</t>
-  </si>
-  <si>
     <t>getLowerAgentRate</t>
   </si>
   <si>
@@ -339,15 +315,9 @@
     <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/isAccountInserted.ts</t>
   </si>
   <si>
-    <t>getMasterAccountElement</t>
-  </si>
-  <si>
     <t>Index</t>
   </si>
   <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getMasterAccountElement.ts</t>
-  </si>
-  <si>
     <t>getStakingRewards</t>
   </si>
   <si>
@@ -366,21 +336,9 @@
     <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getTimeMultiplier.ts</t>
   </si>
   <si>
-    <t>getAccountTimeInSecondeSinceUpdate</t>
-  </si>
-  <si>
     <t>Token Last Update</t>
   </si>
   <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getAccountTimeInSecondeSinceUpdate.ts</t>
-  </si>
-  <si>
-    <t>totalBalanceOf</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/totalBalanceOf.ts</t>
-  </si>
-  <si>
     <t>totalStakedSPCoins</t>
   </si>
   <si>
@@ -892,6 +850,54 @@
   </si>
   <si>
     <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/addBackDatedRecipientTransaction.ts</t>
+  </si>
+  <si>
+    <t>calcDataTimeDiff</t>
+  </si>
+  <si>
+    <t>getMasterAccountKeyAt</t>
+  </si>
+  <si>
+    <t>getMasterAccountKeys</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getMasterAccountKeys.ts</t>
+  </si>
+  <si>
+    <t>getRecipientRateAgentKeys</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getRecipientRateAgentKeys.ts</t>
+  </si>
+  <si>
+    <t>getRecipientRateKeys</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getRecipientRateKeys.ts</t>
+  </si>
+  <si>
+    <t>totalUnstakedSpCoins</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/totalUnstakedSpCoins.ts</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/calcDataTimeDiff.ts</t>
+  </si>
+  <si>
+    <t>getAgentRateKeys</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getAgentRateKeys.ts</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getMasterAccountKeyAt.ts</t>
+  </si>
+  <si>
+    <t>ggetMasterAccountKeys</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/ggetMasterAccountKeys.ts</t>
   </si>
 </sst>
 </file>
@@ -1326,7 +1332,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -1349,7 +1355,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1372,7 +1378,7 @@
         <v>11</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1395,7 +1401,7 @@
         <v>14</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1415,10 +1421,10 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>287</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1427,7 +1433,7 @@
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
@@ -1438,10 +1444,10 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1450,7 +1456,7 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
@@ -1458,22 +1464,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E7" t="s">
         <v>20</v>
       </c>
-      <c r="C7" t="s">
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" t="s">
         <v>21</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="E7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
@@ -1484,10 +1490,10 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1496,7 +1502,7 @@
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
@@ -1507,19 +1513,19 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" t="s">
         <v>26</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="E9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
@@ -1530,19 +1536,19 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
@@ -1550,22 +1556,22 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F11" t="s">
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
@@ -1573,22 +1579,22 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F12" t="s">
         <v>9</v>
       </c>
       <c r="G12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
@@ -1599,19 +1605,19 @@
         <v>6</v>
       </c>
       <c r="C13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13" t="s">
         <v>35</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="E13" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G13" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
@@ -1622,19 +1628,19 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14" t="s">
         <v>38</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="E14" t="s">
-        <v>39</v>
-      </c>
-      <c r="F14" t="s">
-        <v>9</v>
-      </c>
-      <c r="G14" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
@@ -1645,19 +1651,19 @@
         <v>6</v>
       </c>
       <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" t="s">
         <v>41</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="E15" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" t="s">
-        <v>9</v>
-      </c>
-      <c r="G15" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
@@ -1668,19 +1674,19 @@
         <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>279</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E16" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F16" t="s">
         <v>9</v>
       </c>
       <c r="G16" t="s">
-        <v>46</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
@@ -1688,22 +1694,22 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E17" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
         <v>9</v>
       </c>
       <c r="G17" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
@@ -1714,19 +1720,19 @@
         <v>6</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E18" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F18" t="s">
         <v>9</v>
       </c>
       <c r="G18" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
@@ -1737,19 +1743,19 @@
         <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>277</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F19" t="s">
         <v>9</v>
       </c>
       <c r="G19" t="s">
-        <v>53</v>
+        <v>278</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
@@ -1760,10 +1766,10 @@
         <v>6</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1772,7 +1778,7 @@
         <v>9</v>
       </c>
       <c r="G20" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
@@ -1783,10 +1789,10 @@
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1795,7 +1801,7 @@
         <v>9</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
@@ -1806,10 +1812,10 @@
         <v>6</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1818,7 +1824,7 @@
         <v>9</v>
       </c>
       <c r="G22" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
@@ -1826,22 +1832,22 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F23" t="s">
         <v>9</v>
       </c>
       <c r="G23" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
@@ -1852,19 +1858,19 @@
         <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E24" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F24" t="s">
         <v>9</v>
       </c>
       <c r="G24" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
@@ -1875,19 +1881,19 @@
         <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>284</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E25" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F25" t="s">
         <v>9</v>
       </c>
       <c r="G25" t="s">
-        <v>67</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
@@ -1898,10 +1904,10 @@
         <v>6</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1910,7 +1916,7 @@
         <v>9</v>
       </c>
       <c r="G26" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
@@ -1921,10 +1927,10 @@
         <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -1933,7 +1939,7 @@
         <v>9</v>
       </c>
       <c r="G27" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
@@ -1944,10 +1950,10 @@
         <v>6</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -1956,7 +1962,7 @@
         <v>9</v>
       </c>
       <c r="G28" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
@@ -1964,22 +1970,22 @@
         <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E29" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F29" t="s">
         <v>9</v>
       </c>
       <c r="G29" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
@@ -1990,19 +1996,19 @@
         <v>6</v>
       </c>
       <c r="C30" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E30" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F30" t="s">
         <v>9</v>
       </c>
       <c r="G30" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
@@ -2013,19 +2019,19 @@
         <v>6</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E31" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F31" t="s">
         <v>9</v>
       </c>
       <c r="G31" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
@@ -2036,19 +2042,19 @@
         <v>6</v>
       </c>
       <c r="C32" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E32" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F32" t="s">
         <v>9</v>
       </c>
       <c r="G32" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
@@ -2059,19 +2065,19 @@
         <v>6</v>
       </c>
       <c r="C33" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E33" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F33" t="s">
         <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
@@ -2082,19 +2088,19 @@
         <v>6</v>
       </c>
       <c r="C34" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E34" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F34" t="s">
         <v>9</v>
       </c>
       <c r="G34" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
@@ -2102,22 +2108,22 @@
         <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C35" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E35" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F35" t="s">
         <v>9</v>
       </c>
       <c r="G35" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
@@ -2128,19 +2134,19 @@
         <v>6</v>
       </c>
       <c r="C36" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E36" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F36" t="s">
         <v>9</v>
       </c>
       <c r="G36" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
@@ -2151,19 +2157,19 @@
         <v>6</v>
       </c>
       <c r="C37" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E37" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F37" t="s">
         <v>9</v>
       </c>
       <c r="G37" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
@@ -2174,10 +2180,10 @@
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -2186,7 +2192,7 @@
         <v>9</v>
       </c>
       <c r="G38" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
@@ -2197,19 +2203,19 @@
         <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E39" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F39" t="s">
         <v>9</v>
       </c>
       <c r="G39" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
@@ -2220,19 +2226,19 @@
         <v>6</v>
       </c>
       <c r="C40" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E40" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F40" t="s">
         <v>9</v>
       </c>
       <c r="G40" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
@@ -2243,19 +2249,19 @@
         <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>102</v>
+        <v>274</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E41" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="F41" t="s">
         <v>9</v>
       </c>
       <c r="G41" t="s">
-        <v>104</v>
+        <v>286</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
@@ -2266,19 +2272,19 @@
         <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E42" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="F42" t="s">
         <v>9</v>
       </c>
       <c r="G42" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
@@ -2289,19 +2295,19 @@
         <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E43" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="F43" t="s">
         <v>9</v>
       </c>
       <c r="G43" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
@@ -2312,19 +2318,19 @@
         <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>111</v>
+        <v>273</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E44" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="F44" t="s">
         <v>9</v>
       </c>
       <c r="G44" t="s">
-        <v>113</v>
+        <v>283</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
@@ -2335,10 +2341,10 @@
         <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>114</v>
+        <v>281</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -2347,7 +2353,7 @@
         <v>9</v>
       </c>
       <c r="G45" t="s">
-        <v>115</v>
+        <v>282</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.45">
@@ -2358,10 +2364,10 @@
         <v>6</v>
       </c>
       <c r="C46" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -2370,7 +2376,7 @@
         <v>9</v>
       </c>
       <c r="G46" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.45">
@@ -2381,10 +2387,10 @@
         <v>6</v>
       </c>
       <c r="C47" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -2393,7 +2399,7 @@
         <v>9</v>
       </c>
       <c r="G47" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.45">
@@ -2404,10 +2410,10 @@
         <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -2416,642 +2422,642 @@
         <v>9</v>
       </c>
       <c r="G48" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B49" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C49" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E49" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F49" t="s">
         <v>9</v>
       </c>
       <c r="G49" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B50" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C50" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E50" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="F50" t="s">
         <v>9</v>
       </c>
       <c r="G50" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B51" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C51" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E51" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="F51" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="G51" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B52" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C52" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E52" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F52" t="s">
         <v>9</v>
       </c>
       <c r="G52" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B53" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C53" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E53" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="F53" t="s">
         <v>9</v>
       </c>
       <c r="G53" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
+        <v>108</v>
+      </c>
+      <c r="B54" t="s">
+        <v>114</v>
+      </c>
+      <c r="C54" t="s">
         <v>122</v>
       </c>
-      <c r="B54" t="s">
-        <v>128</v>
-      </c>
-      <c r="C54" t="s">
-        <v>136</v>
-      </c>
       <c r="D54" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E54" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F54" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="G54" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B55" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C55" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E55" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="F55" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="G55" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B56" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C56" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E56" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="F56" t="s">
         <v>9</v>
       </c>
       <c r="G56" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B57" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C57" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E57" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F57" t="s">
         <v>9</v>
       </c>
       <c r="G57" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B58" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C58" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="D58" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E58" t="s">
+        <v>44</v>
+      </c>
+      <c r="F58" t="s">
+        <v>9</v>
+      </c>
+      <c r="G58" t="s">
         <v>265</v>
-      </c>
-      <c r="E58" t="s">
-        <v>48</v>
-      </c>
-      <c r="F58" t="s">
-        <v>9</v>
-      </c>
-      <c r="G58" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B59" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C59" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E59" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F59" t="s">
         <v>9</v>
       </c>
       <c r="G59" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B60" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C60" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E60" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F60" t="s">
         <v>9</v>
       </c>
       <c r="G60" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B61" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C61" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E61" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F61" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="G61" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B62" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C62" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E62" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F62" t="s">
+        <v>126</v>
+      </c>
+      <c r="G62" t="s">
         <v>140</v>
-      </c>
-      <c r="G62" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B63" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C63" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E63" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F63" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="G63" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B64" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C64" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E64" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="F64" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="G64" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B65" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C65" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E65" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="F65" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="G65" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B66" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C66" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E66" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="F66" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="G66" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B67" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C67" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E67" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="F67" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="G67" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B68" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C68" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E68" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="F68" t="s">
         <v>9</v>
       </c>
       <c r="G68" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B69" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C69" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E69" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="F69" t="s">
         <v>9</v>
       </c>
       <c r="G69" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B70" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C70" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E70" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="F70" t="s">
         <v>9</v>
       </c>
       <c r="G70" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B71" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C71" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E71" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F71" t="s">
         <v>9</v>
       </c>
       <c r="G71" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B72" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C72" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E72" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="F72" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="G72" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B73" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C73" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E73" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F73" t="s">
         <v>9</v>
       </c>
       <c r="G73" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B74" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="C74" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E74" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="F74" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="G74" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B75" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C75" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E75" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F75" t="s">
         <v>9</v>
       </c>
       <c r="G75" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B76" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C76" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
@@ -3060,274 +3066,274 @@
         <v>9</v>
       </c>
       <c r="G76" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B77" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="C77" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E77" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="F77" t="s">
         <v>9</v>
       </c>
       <c r="G77" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B78" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="C78" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E78" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="F78" t="s">
         <v>9</v>
       </c>
       <c r="G78" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B79" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="C79" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E79" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="F79" t="s">
         <v>9</v>
       </c>
       <c r="G79" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B80" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C80" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E80" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="F80" t="s">
         <v>9</v>
       </c>
       <c r="G80" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B81" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C81" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E81" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="F81" t="s">
         <v>9</v>
       </c>
       <c r="G81" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B82" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C82" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E82" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="F82" t="s">
         <v>9</v>
       </c>
       <c r="G82" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B83" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C83" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E83" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="F83" t="s">
         <v>9</v>
       </c>
       <c r="G83" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B84" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C84" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E84" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="F84" t="s">
         <v>9</v>
       </c>
       <c r="G84" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B85" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C85" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E85" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="F85" t="s">
         <v>9</v>
       </c>
       <c r="G85" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B86" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C86" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E86" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="F86" t="s">
         <v>9</v>
       </c>
       <c r="G86" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B87" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C87" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E87" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="F87" t="s">
         <v>9</v>
       </c>
       <c r="G87" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="B88" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="C88" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -3336,21 +3342,21 @@
         <v>9</v>
       </c>
       <c r="G88" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="B89" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="C89" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
@@ -3359,21 +3365,21 @@
         <v>9</v>
       </c>
       <c r="G89" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="B90" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="C90" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
@@ -3382,21 +3388,21 @@
         <v>9</v>
       </c>
       <c r="G90" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="B91" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="C91" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -3405,21 +3411,21 @@
         <v>9</v>
       </c>
       <c r="G91" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="B92" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="C92" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -3428,21 +3434,21 @@
         <v>9</v>
       </c>
       <c r="G92" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="B93" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="C93" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
@@ -3451,21 +3457,21 @@
         <v>9</v>
       </c>
       <c r="G93" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="B94" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="C94" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
@@ -3474,21 +3480,21 @@
         <v>9</v>
       </c>
       <c r="G94" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="B95" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="C95" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
@@ -3497,21 +3503,21 @@
         <v>9</v>
       </c>
       <c r="G95" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="B96" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="C96" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
@@ -3520,490 +3526,490 @@
         <v>9</v>
       </c>
       <c r="G96" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B97" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="C97" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E97" t="s">
         <v>8</v>
       </c>
       <c r="F97" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G97" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B98" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="C98" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E98" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F98" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G98" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B99" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="C99" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E99" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F99" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G99" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B100" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="C100" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E100" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F100" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G100" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B101" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="C101" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E101" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F101" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G101" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B102" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="C102" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E102" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F102" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G102" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B103" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="C103" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E103" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F103" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G103" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B104" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="C104" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E104" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="F104" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G104" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
+        <v>231</v>
+      </c>
+      <c r="B105" t="s">
+        <v>242</v>
+      </c>
+      <c r="C105" t="s">
         <v>245</v>
       </c>
-      <c r="B105" t="s">
-        <v>256</v>
-      </c>
-      <c r="C105" t="s">
-        <v>259</v>
-      </c>
       <c r="D105" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E105" t="s">
         <v>8</v>
       </c>
       <c r="F105" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G105" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B106" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="C106" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
       </c>
       <c r="F106" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G106" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B107" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="C107" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
       </c>
       <c r="F107" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G107" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B108" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C108" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E108" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="F108" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G108" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B109" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C109" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E109" t="s">
         <v>8</v>
       </c>
       <c r="F109" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G109" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B110" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C110" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E110" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="F110" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G110" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B111" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C111" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E111" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F111" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G111" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B112" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C112" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E112" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F112" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G112" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B113" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C113" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E113" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F113" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G113" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B114" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C114" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E114" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F114" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G114" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B115" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C115" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E115" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F115" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G115" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B116" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C116" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E116" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F116" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G116" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B117" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C117" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E117" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F117" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G117" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -4037,7 +4043,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -4051,163 +4057,163 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B2" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C2" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E2" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="F2" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="G2" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" t="s">
         <v>122</v>
       </c>
-      <c r="B3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C3" t="s">
-        <v>136</v>
-      </c>
       <c r="D3" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F3" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="G3" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B4" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C4" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E4" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B5" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C5" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C6" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" t="s">
         <v>265</v>
-      </c>
-      <c r="E6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B7" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C7" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E7" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B8" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E8" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -4244,7 +4250,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -4255,71 +4261,71 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B2" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C2" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="F2" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="G2" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" t="s">
         <v>122</v>
       </c>
-      <c r="B3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C3" t="s">
-        <v>136</v>
-      </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="F3" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="G3" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B4" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="C4" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="D4" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="F4" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="G4" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -4356,7 +4362,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -4367,71 +4373,71 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B2" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="C2" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="D2" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B3" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="C3" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="D3" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B4" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="C4" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="D4" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -4442,7 +4448,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.1328125" customWidth="1"/>
@@ -4465,7 +4471,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -4485,19 +4491,19 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
@@ -4505,22 +4511,22 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
@@ -4531,65 +4537,19 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>268</v>
+        <v>36</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="E5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="E6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
@@ -4597,22 +4557,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
@@ -4623,19 +4583,19 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>265</v>
+        <v>24</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
@@ -4646,157 +4606,51 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>265</v>
+        <v>27</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="E10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" t="s">
-        <v>111</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="E11" t="s">
-        <v>112</v>
-      </c>
-      <c r="F11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" t="s">
-        <v>113</v>
-      </c>
+      <c r="D11" s="3"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="E12" t="s">
-        <v>66</v>
-      </c>
-      <c r="F12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" t="s">
-        <v>67</v>
-      </c>
+      <c r="D12" s="3"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G13" t="s">
-        <v>73</v>
-      </c>
+      <c r="D13" s="3"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E14" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="F14" t="s">
         <v>9</v>
       </c>
       <c r="G14" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="E15" t="s">
-        <v>66</v>
-      </c>
-      <c r="F15" t="s">
-        <v>9</v>
-      </c>
-      <c r="G15" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
@@ -4804,22 +4658,22 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E16" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="F16" t="s">
         <v>9</v>
       </c>
       <c r="G16" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
@@ -4830,19 +4684,19 @@
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>273</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E17" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="F17" t="s">
         <v>9</v>
       </c>
       <c r="G17" t="s">
-        <v>84</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
@@ -4850,22 +4704,22 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>284</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E18" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="F18" t="s">
         <v>9</v>
       </c>
       <c r="G18" t="s">
-        <v>89</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
@@ -4876,19 +4730,19 @@
         <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>265</v>
+        <v>64</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E19" t="s">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
         <v>9</v>
       </c>
       <c r="G19" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
@@ -4896,22 +4750,22 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E20" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="F20" t="s">
         <v>9</v>
       </c>
       <c r="G20" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
@@ -4922,19 +4776,19 @@
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E21" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F21" t="s">
         <v>9</v>
       </c>
       <c r="G21" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
@@ -4945,19 +4799,19 @@
         <v>6</v>
       </c>
       <c r="C22" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>268</v>
+        <v>77</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>78</v>
       </c>
       <c r="F22" t="s">
         <v>9</v>
       </c>
       <c r="G22" t="s">
-        <v>10</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
@@ -4968,19 +4822,19 @@
         <v>6</v>
       </c>
       <c r="C23" t="s">
-        <v>269</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>268</v>
+        <v>75</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="F23" t="s">
         <v>9</v>
       </c>
       <c r="G23" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
@@ -4988,22 +4842,22 @@
         <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>68</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>268</v>
+        <v>80</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="F24" t="s">
         <v>9</v>
       </c>
       <c r="G24" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
@@ -5014,19 +4868,19 @@
         <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>54</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>268</v>
+        <v>82</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="F25" t="s">
         <v>9</v>
       </c>
       <c r="G25" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
@@ -5037,19 +4891,19 @@
         <v>6</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>268</v>
+        <v>84</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E26" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F26" t="s">
         <v>9</v>
       </c>
       <c r="G26" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
@@ -5060,19 +4914,19 @@
         <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>268</v>
+        <v>71</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E27" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="F27" t="s">
         <v>9</v>
       </c>
       <c r="G27" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
@@ -5083,19 +4937,19 @@
         <v>6</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>265</v>
+        <v>7</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E28" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="F28" t="s">
         <v>9</v>
       </c>
       <c r="G28" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
@@ -5106,19 +4960,19 @@
         <v>6</v>
       </c>
       <c r="C29" t="s">
-        <v>44</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>265</v>
+        <v>255</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E29" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F29" t="s">
         <v>9</v>
       </c>
       <c r="G29" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
@@ -5129,10 +4983,10 @@
         <v>6</v>
       </c>
       <c r="C30" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -5141,7 +4995,7 @@
         <v>9</v>
       </c>
       <c r="G30" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
@@ -5149,16 +5003,16 @@
         <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C31" t="s">
-        <v>47</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>265</v>
+        <v>48</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E31" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="F31" t="s">
         <v>9</v>
@@ -5175,19 +5029,19 @@
         <v>6</v>
       </c>
       <c r="C32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>265</v>
+        <v>274</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E32" t="s">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="F32" t="s">
         <v>9</v>
       </c>
       <c r="G32" t="s">
-        <v>51</v>
+        <v>286</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
@@ -5198,19 +5052,19 @@
         <v>6</v>
       </c>
       <c r="C33" t="s">
-        <v>81</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>265</v>
+        <v>275</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E33" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="F33" t="s">
         <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>82</v>
+        <v>276</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
@@ -5218,22 +5072,22 @@
         <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C34" t="s">
-        <v>60</v>
+        <v>277</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F34" t="s">
         <v>9</v>
       </c>
       <c r="G34" t="s">
-        <v>61</v>
+        <v>278</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
@@ -5244,19 +5098,19 @@
         <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>62</v>
+        <v>279</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E35" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="F35" t="s">
         <v>9</v>
       </c>
       <c r="G35" t="s">
-        <v>64</v>
+        <v>280</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
@@ -5267,10 +5121,10 @@
         <v>6</v>
       </c>
       <c r="C36" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -5279,7 +5133,7 @@
         <v>9</v>
       </c>
       <c r="G36" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
@@ -5287,22 +5141,22 @@
         <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C37" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E37" t="s">
-        <v>106</v>
+        <v>44</v>
       </c>
       <c r="F37" t="s">
         <v>9</v>
       </c>
       <c r="G37" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
@@ -5313,19 +5167,19 @@
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>70</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>268</v>
+        <v>46</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E38" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F38" t="s">
         <v>9</v>
       </c>
       <c r="G38" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
@@ -5336,19 +5190,19 @@
         <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>56</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>268</v>
+        <v>73</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E39" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="F39" t="s">
         <v>9</v>
       </c>
       <c r="G39" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
@@ -5356,22 +5210,22 @@
         <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C40" t="s">
-        <v>120</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>268</v>
+        <v>54</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E40" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F40" t="s">
         <v>9</v>
       </c>
       <c r="G40" t="s">
-        <v>121</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
@@ -5382,19 +5236,19 @@
         <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>100</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>268</v>
+        <v>56</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E41" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="F41" t="s">
         <v>9</v>
       </c>
       <c r="G41" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
@@ -5405,19 +5259,19 @@
         <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="E42" t="s">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="F42" t="s">
         <v>9</v>
       </c>
       <c r="G42" t="s">
-        <v>99</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
@@ -5428,19 +5282,19 @@
         <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E43" t="s">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="F43" t="s">
         <v>9</v>
       </c>
       <c r="G43" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
@@ -5451,10 +5305,10 @@
         <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>116</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>265</v>
+        <v>62</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -5463,7 +5317,7 @@
         <v>9</v>
       </c>
       <c r="G44" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
@@ -5474,10 +5328,10 @@
         <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>118</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>265</v>
+        <v>50</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -5486,13 +5340,151 @@
         <v>9</v>
       </c>
       <c r="G45" t="s">
-        <v>119</v>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" t="s">
+        <v>106</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E46" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" t="s">
+        <v>9</v>
+      </c>
+      <c r="G46" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" t="s">
+        <v>92</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E47" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" t="s">
+        <v>9</v>
+      </c>
+      <c r="G47" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" t="s">
+        <v>89</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E48" t="s">
+        <v>90</v>
+      </c>
+      <c r="F48" t="s">
+        <v>9</v>
+      </c>
+      <c r="G48" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" t="s">
+        <v>281</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E49" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G49" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>6</v>
+      </c>
+      <c r="B50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" t="s">
+        <v>102</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E50" t="s">
+        <v>8</v>
+      </c>
+      <c r="F50" t="s">
+        <v>9</v>
+      </c>
+      <c r="G50" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>6</v>
+      </c>
+      <c r="B51" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" t="s">
+        <v>104</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E51" t="s">
+        <v>8</v>
+      </c>
+      <c r="F51" t="s">
+        <v>9</v>
+      </c>
+      <c r="G51" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G45" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G45">
-      <sortCondition ref="C1:C45"/>
+  <autoFilter ref="A1:G51" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G51">
+      <sortCondition ref="C1:C51"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5524,7 +5516,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -5538,890 +5530,890 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C2" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E2" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" t="s">
         <v>122</v>
       </c>
-      <c r="B3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C3" t="s">
-        <v>136</v>
-      </c>
       <c r="D3" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F3" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="G3" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B4" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C4" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E4" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B5" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C5" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E5" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E6" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B7" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C7" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E7" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B8" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C8" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E8" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="F8" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="G8" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C9" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C10" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E10" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B11" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C11" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E11" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="F11" t="s">
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B12" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C12" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F12" t="s">
         <v>9</v>
       </c>
       <c r="G12" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B13" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="C13" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E13" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="F13" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="G13" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B14" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C14" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E14" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="F14" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="G14" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B15" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C15" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E15" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F15" t="s">
         <v>9</v>
       </c>
       <c r="G15" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B16" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C16" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E16" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F16" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="G16" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B17" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C17" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E17" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F17" t="s">
         <v>9</v>
       </c>
       <c r="G17" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B18" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C18" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E18" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="F18" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="G18" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B19" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C19" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F19" t="s">
         <v>9</v>
       </c>
       <c r="G19" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B20" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C20" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E20" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="F20" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="G20" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B21" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C21" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E21" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="F21" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="G21" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C22" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F22" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="G22" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C23" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E23" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F23" t="s">
+        <v>126</v>
+      </c>
+      <c r="G23" t="s">
         <v>140</v>
-      </c>
-      <c r="G23" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B24" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C24" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E24" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="F24" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="G24" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B25" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C25" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E25" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F25" t="s">
         <v>9</v>
       </c>
       <c r="G25" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B26" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C26" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E26" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="F26" t="s">
         <v>9</v>
       </c>
       <c r="G26" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B27" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="C27" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E27" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="F27" t="s">
         <v>9</v>
       </c>
       <c r="G27" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B28" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="C28" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E28" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="F28" t="s">
         <v>9</v>
       </c>
       <c r="G28" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B29" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="C29" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E29" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="F29" t="s">
         <v>9</v>
       </c>
       <c r="G29" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B30" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C30" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E30" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="F30" t="s">
         <v>9</v>
       </c>
       <c r="G30" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B31" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C31" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E31" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="F31" t="s">
         <v>9</v>
       </c>
       <c r="G31" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B32" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C32" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E32" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="F32" t="s">
         <v>9</v>
       </c>
       <c r="G32" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B33" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C33" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E33" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="F33" t="s">
         <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B34" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C34" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E34" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="F34" t="s">
         <v>9</v>
       </c>
       <c r="G34" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B35" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C35" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E35" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="F35" t="s">
         <v>9</v>
       </c>
       <c r="G35" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B36" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C36" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E36" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="F36" t="s">
         <v>9</v>
       </c>
       <c r="G36" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B37" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C37" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E37" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="F37" t="s">
         <v>9</v>
       </c>
       <c r="G37" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B38" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C38" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E38" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="F38" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="G38" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B39" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C39" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E39" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F39" t="s">
         <v>9</v>
       </c>
       <c r="G39" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B40" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C40" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -6430,7 +6422,7 @@
         <v>9</v>
       </c>
       <c r="G40" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -6468,7 +6460,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -6482,16 +6474,16 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="B2" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="C2" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -6500,21 +6492,21 @@
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="B3" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="C3" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -6523,21 +6515,21 @@
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="B4" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="C4" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -6546,21 +6538,21 @@
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="B5" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="C5" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -6569,21 +6561,21 @@
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="B6" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="C6" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -6592,21 +6584,21 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="B7" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="C7" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -6615,7 +6607,7 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -6649,7 +6641,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -6663,16 +6655,16 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="B2" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="C2" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -6681,21 +6673,21 @@
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="B3" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="C3" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -6704,21 +6696,21 @@
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="B4" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="C4" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -6727,7 +6719,7 @@
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -6761,7 +6753,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -6775,485 +6767,485 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B2" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="C2" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G2" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B3" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="C3" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G3" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B4" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="C4" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G4" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B5" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="C5" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F5" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G5" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B6" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="C6" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F6" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G6" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B7" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="C7" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E7" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F7" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G7" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B8" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="C8" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E8" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F8" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G8" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B9" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="C9" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E9" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="F9" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G9" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
+        <v>231</v>
+      </c>
+      <c r="B10" t="s">
+        <v>242</v>
+      </c>
+      <c r="C10" t="s">
         <v>245</v>
       </c>
-      <c r="B10" t="s">
-        <v>256</v>
-      </c>
-      <c r="C10" t="s">
-        <v>259</v>
-      </c>
       <c r="D10" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G10" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B11" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="C11" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G11" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B12" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="C12" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G12" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B13" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C13" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E13" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="F13" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G13" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B14" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C14" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G14" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B15" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C15" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E15" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="F15" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G15" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B16" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C16" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E16" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F16" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G16" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B17" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C17" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E17" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G17" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B18" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C18" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E18" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F18" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G18" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B19" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C19" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E19" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F19" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G19" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B20" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C20" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F20" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G20" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C21" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E21" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F21" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G21" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C22" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E22" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F22" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G22" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -7287,7 +7279,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -7301,108 +7293,108 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B2" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C2" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E2" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B3" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C3" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E3" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B4" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C4" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E4" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B5" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C5" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E5" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C6" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -7411,421 +7403,421 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B7" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C7" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E7" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B8" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C8" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E8" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B9" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C9" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E9" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C10" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E10" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B11" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C11" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E11" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="F11" t="s">
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B12" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C12" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E12" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="F12" t="s">
         <v>9</v>
       </c>
       <c r="G12" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B13" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C13" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E13" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="F13" t="s">
         <v>9</v>
       </c>
       <c r="G13" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B14" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C14" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E14" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="F14" t="s">
         <v>9</v>
       </c>
       <c r="G14" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B15" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C15" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E15" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="F15" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G15" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B16" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C16" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G16" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B17" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C17" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E17" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="F17" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G17" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B18" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C18" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E18" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F18" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G18" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B19" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C19" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F19" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G19" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B20" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C20" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E20" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F20" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G20" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C21" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E21" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F21" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G21" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C22" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F22" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G22" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C23" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E23" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F23" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G23" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B24" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C24" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E24" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F24" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G24" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -7859,7 +7851,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -7873,94 +7865,94 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B2" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="C2" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E2" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="F2" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G2" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C3" t="s">
         <v>245</v>
       </c>
-      <c r="B3" t="s">
-        <v>256</v>
-      </c>
-      <c r="C3" t="s">
-        <v>259</v>
-      </c>
       <c r="D3" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G3" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B4" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G4" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B5" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="C5" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G5" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -7994,7 +7986,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -8011,22 +8003,22 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E2" t="s">
         <v>20</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
         <v>21</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
@@ -8034,22 +8026,22 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
@@ -8057,22 +8049,22 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
@@ -8080,22 +8072,22 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
@@ -8103,22 +8095,22 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
@@ -8126,22 +8118,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E7" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
@@ -8149,22 +8141,22 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E8" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/docs/DropDownAccessMethods.xlsx
+++ b/docs/DropDownAccessMethods.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robin\spCoin\SPCOIN-PROJECT-MODULES\spcoin-nextjs-front-end\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797364A7-8A36-408E-AE3A-023054E16581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC273C88-5394-46A2-92E4-DAB9C600DA24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="10965" windowHeight="12863" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Methods" sheetId="1" r:id="rId1"/>
@@ -855,9 +855,6 @@
     <t>calcDataTimeDiff</t>
   </si>
   <si>
-    <t>getMasterAccountKeyAt</t>
-  </si>
-  <si>
     <t>getMasterAccountKeys</t>
   </si>
   <si>
@@ -891,13 +888,16 @@
     <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getAgentRateKeys.ts</t>
   </si>
   <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getMasterAccountKeyAt.ts</t>
-  </si>
-  <si>
     <t>ggetMasterAccountKeys</t>
   </si>
   <si>
     <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/ggetMasterAccountKeys.ts</t>
+  </si>
+  <si>
+    <t>getMasterAccountElement</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getMasterAccountElement.ts</t>
   </si>
 </sst>
 </file>
@@ -1421,7 +1421,7 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>251</v>
@@ -1433,7 +1433,7 @@
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
@@ -1674,7 +1674,7 @@
         <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>251</v>
@@ -1686,7 +1686,7 @@
         <v>9</v>
       </c>
       <c r="G16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
@@ -1743,7 +1743,7 @@
         <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>251</v>
@@ -1755,7 +1755,7 @@
         <v>9</v>
       </c>
       <c r="G19" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
@@ -1881,7 +1881,7 @@
         <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>251</v>
@@ -1893,7 +1893,7 @@
         <v>9</v>
       </c>
       <c r="G25" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
@@ -2249,7 +2249,7 @@
         <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>251</v>
@@ -2261,7 +2261,7 @@
         <v>9</v>
       </c>
       <c r="G41" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
@@ -2330,7 +2330,7 @@
         <v>9</v>
       </c>
       <c r="G44" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
@@ -2341,7 +2341,7 @@
         <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>251</v>
@@ -2353,7 +2353,7 @@
         <v>9</v>
       </c>
       <c r="G45" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.45">
@@ -4448,7 +4448,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.1328125" customWidth="1"/>
@@ -4507,128 +4507,71 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="D9" s="3"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C10" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E10" t="s">
         <v>25</v>
       </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="F10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="D11" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E11" t="s">
         <v>37</v>
       </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="F11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="E8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="E9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="D13" s="3"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
@@ -4638,19 +4581,42 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>251</v>
+        <v>16</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
         <v>9</v>
       </c>
       <c r="G14" t="s">
-        <v>35</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
@@ -4658,13 +4624,13 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>251</v>
+        <v>27</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E16" t="s">
         <v>25</v>
@@ -4673,100 +4639,17 @@
         <v>9</v>
       </c>
       <c r="G16" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" t="s">
-        <v>273</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="E17" t="s">
-        <v>101</v>
-      </c>
-      <c r="F17" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" t="s">
-        <v>283</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" t="s">
-        <v>284</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="E18" t="s">
-        <v>59</v>
-      </c>
-      <c r="F18" t="s">
-        <v>9</v>
-      </c>
-      <c r="G18" t="s">
-        <v>285</v>
-      </c>
+      <c r="D18"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>9</v>
-      </c>
-      <c r="G19" t="s">
-        <v>65</v>
-      </c>
+      <c r="D19"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" t="s">
-        <v>66</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="E20" t="s">
-        <v>67</v>
-      </c>
-      <c r="F20" t="s">
-        <v>9</v>
-      </c>
-      <c r="G20" t="s">
-        <v>68</v>
-      </c>
+      <c r="D20"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
@@ -4776,42 +4659,19 @@
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E21" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="F21" t="s">
         <v>9</v>
       </c>
       <c r="G21" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" t="s">
-        <v>77</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="E22" t="s">
-        <v>78</v>
-      </c>
-      <c r="F22" t="s">
-        <v>9</v>
-      </c>
-      <c r="G22" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
@@ -4819,22 +4679,22 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E23" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="F23" t="s">
         <v>9</v>
       </c>
       <c r="G23" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
@@ -4842,22 +4702,22 @@
         <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>273</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E24" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="F24" t="s">
         <v>9</v>
       </c>
       <c r="G24" t="s">
-        <v>81</v>
+        <v>282</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
@@ -4868,7 +4728,7 @@
         <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>251</v>
@@ -4880,7 +4740,7 @@
         <v>9</v>
       </c>
       <c r="G25" t="s">
-        <v>83</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
@@ -4891,19 +4751,19 @@
         <v>6</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>251</v>
+        <v>64</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E26" t="s">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="F26" t="s">
         <v>9</v>
       </c>
       <c r="G26" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
@@ -4911,22 +4771,22 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E27" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F27" t="s">
         <v>9</v>
       </c>
       <c r="G27" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
@@ -4937,19 +4797,19 @@
         <v>6</v>
       </c>
       <c r="C28" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>254</v>
+        <v>69</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E28" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="F28" t="s">
         <v>9</v>
       </c>
       <c r="G28" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
@@ -4960,19 +4820,19 @@
         <v>6</v>
       </c>
       <c r="C29" t="s">
-        <v>255</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>254</v>
+        <v>77</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
+        <v>78</v>
       </c>
       <c r="F29" t="s">
         <v>9</v>
       </c>
       <c r="G29" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
@@ -4983,19 +4843,19 @@
         <v>6</v>
       </c>
       <c r="C30" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>254</v>
+        <v>75</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E30" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="F30" t="s">
         <v>9</v>
       </c>
       <c r="G30" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
@@ -5003,22 +4863,22 @@
         <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>254</v>
+        <v>80</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E31" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="F31" t="s">
         <v>9</v>
       </c>
       <c r="G31" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
@@ -5029,19 +4889,19 @@
         <v>6</v>
       </c>
       <c r="C32" t="s">
-        <v>274</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>254</v>
+        <v>82</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E32" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="F32" t="s">
         <v>9</v>
       </c>
       <c r="G32" t="s">
-        <v>286</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
@@ -5052,19 +4912,19 @@
         <v>6</v>
       </c>
       <c r="C33" t="s">
-        <v>275</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>254</v>
+        <v>84</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E33" t="s">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="F33" t="s">
         <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>276</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
@@ -5075,19 +4935,19 @@
         <v>6</v>
       </c>
       <c r="C34" t="s">
-        <v>277</v>
+        <v>71</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E34" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="F34" t="s">
         <v>9</v>
       </c>
       <c r="G34" t="s">
-        <v>278</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
@@ -5098,19 +4958,19 @@
         <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>279</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>251</v>
+        <v>7</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E35" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="F35" t="s">
         <v>9</v>
       </c>
       <c r="G35" t="s">
-        <v>280</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
@@ -5121,7 +4981,7 @@
         <v>6</v>
       </c>
       <c r="C36" t="s">
-        <v>52</v>
+        <v>255</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>254</v>
@@ -5133,7 +4993,7 @@
         <v>9</v>
       </c>
       <c r="G36" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
@@ -5141,22 +5001,22 @@
         <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C37" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>251</v>
+        <v>60</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E37" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="F37" t="s">
         <v>9</v>
       </c>
       <c r="G37" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
@@ -5167,19 +5027,19 @@
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>46</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>251</v>
+        <v>48</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E38" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="F38" t="s">
         <v>9</v>
       </c>
       <c r="G38" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
@@ -5190,19 +5050,19 @@
         <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>73</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>251</v>
+        <v>287</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E39" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="F39" t="s">
         <v>9</v>
       </c>
       <c r="G39" t="s">
-        <v>74</v>
+        <v>288</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
@@ -5210,22 +5070,22 @@
         <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C40" t="s">
-        <v>54</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>251</v>
+        <v>274</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E40" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="F40" t="s">
         <v>9</v>
       </c>
       <c r="G40" t="s">
-        <v>55</v>
+        <v>275</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
@@ -5236,19 +5096,19 @@
         <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>56</v>
+        <v>276</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E41" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="F41" t="s">
         <v>9</v>
       </c>
       <c r="G41" t="s">
-        <v>58</v>
+        <v>277</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
@@ -5259,19 +5119,19 @@
         <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>22</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>254</v>
+        <v>278</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E42" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F42" t="s">
         <v>9</v>
       </c>
       <c r="G42" t="s">
-        <v>23</v>
+        <v>279</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
@@ -5282,19 +5142,19 @@
         <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>95</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>251</v>
+        <v>52</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E43" t="s">
-        <v>96</v>
+        <v>8</v>
       </c>
       <c r="F43" t="s">
         <v>9</v>
       </c>
       <c r="G43" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
@@ -5302,22 +5162,22 @@
         <v>6</v>
       </c>
       <c r="B44" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C44" t="s">
-        <v>62</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>254</v>
+        <v>43</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E44" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="F44" t="s">
         <v>9</v>
       </c>
       <c r="G44" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
@@ -5328,19 +5188,19 @@
         <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>50</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>254</v>
+        <v>46</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E45" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F45" t="s">
         <v>9</v>
       </c>
       <c r="G45" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.45">
@@ -5351,19 +5211,19 @@
         <v>6</v>
       </c>
       <c r="C46" t="s">
-        <v>106</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>254</v>
+        <v>73</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E46" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="F46" t="s">
         <v>9</v>
       </c>
       <c r="G46" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.45">
@@ -5371,22 +5231,22 @@
         <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C47" t="s">
-        <v>92</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>254</v>
+        <v>54</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E47" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="F47" t="s">
         <v>9</v>
       </c>
       <c r="G47" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.45">
@@ -5397,19 +5257,19 @@
         <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>89</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>254</v>
+        <v>56</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E48" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="F48" t="s">
         <v>9</v>
       </c>
       <c r="G48" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.45">
@@ -5420,10 +5280,10 @@
         <v>6</v>
       </c>
       <c r="C49" t="s">
-        <v>281</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>251</v>
+        <v>22</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -5432,7 +5292,7 @@
         <v>9</v>
       </c>
       <c r="G49" t="s">
-        <v>282</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.45">
@@ -5443,19 +5303,19 @@
         <v>6</v>
       </c>
       <c r="C50" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E50" t="s">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="F50" t="s">
         <v>9</v>
       </c>
       <c r="G50" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.45">
@@ -5466,10 +5326,10 @@
         <v>6</v>
       </c>
       <c r="C51" t="s">
-        <v>104</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>251</v>
+        <v>62</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -5478,13 +5338,174 @@
         <v>9</v>
       </c>
       <c r="G51" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>6</v>
+      </c>
+      <c r="B52" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" t="s">
+        <v>50</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E52" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" t="s">
+        <v>9</v>
+      </c>
+      <c r="G52" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" t="s">
+        <v>106</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E53" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" t="s">
+        <v>9</v>
+      </c>
+      <c r="G53" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>6</v>
+      </c>
+      <c r="B54" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" t="s">
+        <v>92</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E54" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54" t="s">
+        <v>9</v>
+      </c>
+      <c r="G54" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" t="s">
+        <v>89</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E55" t="s">
+        <v>90</v>
+      </c>
+      <c r="F55" t="s">
+        <v>9</v>
+      </c>
+      <c r="G55" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>6</v>
+      </c>
+      <c r="B56" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" t="s">
+        <v>280</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E56" t="s">
+        <v>8</v>
+      </c>
+      <c r="F56" t="s">
+        <v>9</v>
+      </c>
+      <c r="G56" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>6</v>
+      </c>
+      <c r="B57" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" t="s">
+        <v>102</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E57" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" t="s">
+        <v>9</v>
+      </c>
+      <c r="G57" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>6</v>
+      </c>
+      <c r="B58" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" t="s">
+        <v>104</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E58" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" t="s">
+        <v>9</v>
+      </c>
+      <c r="G58" t="s">
         <v>105</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G51" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G51">
-      <sortCondition ref="C1:C51"/>
+  <autoFilter ref="A1:G58" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G58">
+      <sortCondition ref="C1:C58"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/DropDownAccessMethods.xlsx
+++ b/docs/DropDownAccessMethods.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robin\spCoin\SPCOIN-PROJECT-MODULES\spcoin-nextjs-front-end\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC273C88-5394-46A2-92E4-DAB9C600DA24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0902D76B-AB7B-4727-8809-41BB35210D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="10965" windowHeight="12863" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Methods" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2009" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2023" uniqueCount="308">
   <si>
     <t>Panel</t>
   </si>
@@ -858,9 +858,6 @@
     <t>getMasterAccountKeys</t>
   </si>
   <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getMasterAccountKeys.ts</t>
-  </si>
-  <si>
     <t>getRecipientRateAgentKeys</t>
   </si>
   <si>
@@ -898,6 +895,66 @@
   </si>
   <si>
     <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getMasterAccountElement.ts</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getRecipientRateList.ts</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getRecipientRateAgentList.ts</t>
+  </si>
+  <si>
+    <t>getRecipientKeys</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getRecipientList.ts</t>
+  </si>
+  <si>
+    <t>getRecipientKeyCount</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getRecipientListSize.ts</t>
+  </si>
+  <si>
+    <t>getAgentKeys</t>
+  </si>
+  <si>
+    <t>Recipient</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getAgentList.ts</t>
+  </si>
+  <si>
+    <t>getAgentKeyCount</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getAgentListSize.ts</t>
+  </si>
+  <si>
+    <t>getAccountRateRecordList</t>
+  </si>
+  <si>
+    <t>Rate Reward List</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getAccountRateRecordList.ts</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getMasterAccountListSize.ts</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getMasterAccountList.ts</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getAgentRateList.ts</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getInitialTotalSupply.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">getMasterAccountElement </t>
+  </si>
+  <si>
+    <t>getMasterAccountCount</t>
   </si>
 </sst>
 </file>
@@ -1421,7 +1478,7 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>251</v>
@@ -1433,7 +1490,7 @@
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
@@ -1674,7 +1731,7 @@
         <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>251</v>
@@ -1686,7 +1743,7 @@
         <v>9</v>
       </c>
       <c r="G16" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
@@ -1743,7 +1800,7 @@
         <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>251</v>
@@ -1755,7 +1812,7 @@
         <v>9</v>
       </c>
       <c r="G19" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
@@ -1881,7 +1938,7 @@
         <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>251</v>
@@ -1893,7 +1950,7 @@
         <v>9</v>
       </c>
       <c r="G25" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
@@ -2249,7 +2306,7 @@
         <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>251</v>
@@ -2261,7 +2318,7 @@
         <v>9</v>
       </c>
       <c r="G41" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
@@ -2330,7 +2387,7 @@
         <v>9</v>
       </c>
       <c r="G44" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
@@ -2341,7 +2398,7 @@
         <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>251</v>
@@ -2353,7 +2410,7 @@
         <v>9</v>
       </c>
       <c r="G45" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.45">
@@ -4448,7 +4505,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.1328125" customWidth="1"/>
@@ -4507,47 +4564,141 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="D3" s="3"/>
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E3" t="s">
+        <v>300</v>
+      </c>
+      <c r="F3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G3" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="D4" s="3"/>
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="D5" s="3"/>
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" t="s">
+        <v>126</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="D8" s="3"/>
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" t="s">
+        <v>126</v>
+      </c>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="D9" s="3"/>
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>306</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E9" t="s">
+        <v>94</v>
+      </c>
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>307</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>254</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>30</v>
+        <v>302</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
@@ -4558,19 +4709,42 @@
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>251</v>
+        <v>274</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>38</v>
+        <v>303</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>282</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
@@ -4581,7 +4755,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>254</v>
@@ -4593,7 +4767,7 @@
         <v>9</v>
       </c>
       <c r="G14" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
@@ -4601,22 +4775,22 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>254</v>
+        <v>66</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E15" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="F15" t="s">
         <v>9</v>
       </c>
       <c r="G15" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
@@ -4627,51 +4801,111 @@
         <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E16" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E17" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="E16" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" t="s">
-        <v>9</v>
-      </c>
-      <c r="G16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="D18"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="D19"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="D20"/>
+      <c r="E18" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" t="s">
+        <v>9</v>
+      </c>
+      <c r="G18" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E21" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F21" t="s">
         <v>9</v>
       </c>
       <c r="G21" t="s">
-        <v>35</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>297</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E22" t="s">
+        <v>295</v>
+      </c>
+      <c r="F22" t="s">
+        <v>9</v>
+      </c>
+      <c r="G22" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
@@ -4679,160 +4913,22 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C23" t="s">
-        <v>31</v>
+        <v>294</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E23" t="s">
-        <v>25</v>
+        <v>295</v>
       </c>
       <c r="F23" t="s">
         <v>9</v>
       </c>
       <c r="G23" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" t="s">
-        <v>273</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="E24" t="s">
-        <v>101</v>
-      </c>
-      <c r="F24" t="s">
-        <v>9</v>
-      </c>
-      <c r="G24" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>6</v>
-      </c>
-      <c r="B25" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" t="s">
-        <v>283</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="E25" t="s">
-        <v>59</v>
-      </c>
-      <c r="F25" t="s">
-        <v>9</v>
-      </c>
-      <c r="G25" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>6</v>
-      </c>
-      <c r="B26" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" t="s">
-        <v>64</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>9</v>
-      </c>
-      <c r="G26" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>6</v>
-      </c>
-      <c r="B27" t="s">
-        <v>18</v>
-      </c>
-      <c r="C27" t="s">
-        <v>66</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="E27" t="s">
-        <v>67</v>
-      </c>
-      <c r="F27" t="s">
-        <v>9</v>
-      </c>
-      <c r="G27" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" t="s">
-        <v>69</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="E28" t="s">
-        <v>59</v>
-      </c>
-      <c r="F28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G28" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" t="s">
-        <v>77</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="E29" t="s">
-        <v>78</v>
-      </c>
-      <c r="F29" t="s">
-        <v>9</v>
-      </c>
-      <c r="G29" t="s">
-        <v>79</v>
+        <v>296</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
@@ -4843,19 +4939,19 @@
         <v>6</v>
       </c>
       <c r="C30" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E30" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F30" t="s">
         <v>9</v>
       </c>
       <c r="G30" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
@@ -4863,22 +4959,22 @@
         <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C31" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E31" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="F31" t="s">
         <v>9</v>
       </c>
       <c r="G31" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
@@ -4889,7 +4985,7 @@
         <v>6</v>
       </c>
       <c r="C32" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>251</v>
@@ -4901,7 +4997,7 @@
         <v>9</v>
       </c>
       <c r="G32" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
@@ -4912,19 +5008,19 @@
         <v>6</v>
       </c>
       <c r="C33" t="s">
-        <v>84</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>251</v>
+        <v>7</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E33" t="s">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="F33" t="s">
         <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
@@ -4935,19 +5031,19 @@
         <v>6</v>
       </c>
       <c r="C34" t="s">
-        <v>71</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>251</v>
+        <v>255</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E34" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="F34" t="s">
         <v>9</v>
       </c>
       <c r="G34" t="s">
-        <v>72</v>
+        <v>305</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
@@ -4958,7 +5054,7 @@
         <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>254</v>
@@ -4970,7 +5066,7 @@
         <v>9</v>
       </c>
       <c r="G35" t="s">
-        <v>10</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
@@ -4981,7 +5077,7 @@
         <v>6</v>
       </c>
       <c r="C36" t="s">
-        <v>255</v>
+        <v>48</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>254</v>
@@ -4993,7 +5089,7 @@
         <v>9</v>
       </c>
       <c r="G36" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
@@ -5004,19 +5100,19 @@
         <v>6</v>
       </c>
       <c r="C37" t="s">
-        <v>60</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>254</v>
+        <v>39</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E37" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F37" t="s">
-        <v>9</v>
+        <v>126</v>
       </c>
       <c r="G37" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
@@ -5027,19 +5123,19 @@
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>48</v>
+        <v>292</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>254</v>
       </c>
       <c r="E38" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F38" t="s">
         <v>9</v>
       </c>
       <c r="G38" t="s">
-        <v>49</v>
+        <v>293</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
@@ -5050,19 +5146,19 @@
         <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>254</v>
       </c>
       <c r="E39" t="s">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c r="F39" t="s">
         <v>9</v>
       </c>
       <c r="G39" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
@@ -5073,19 +5169,19 @@
         <v>6</v>
       </c>
       <c r="C40" t="s">
-        <v>274</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>254</v>
+        <v>275</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E40" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="F40" t="s">
         <v>9</v>
       </c>
       <c r="G40" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
@@ -5096,19 +5192,19 @@
         <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E41" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F41" t="s">
         <v>9</v>
       </c>
       <c r="G41" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
@@ -5119,19 +5215,19 @@
         <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>278</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>251</v>
+        <v>52</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E42" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="F42" t="s">
         <v>9</v>
       </c>
       <c r="G42" t="s">
-        <v>279</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
@@ -5139,22 +5235,22 @@
         <v>6</v>
       </c>
       <c r="B43" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C43" t="s">
-        <v>52</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>254</v>
+        <v>43</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E43" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="F43" t="s">
         <v>9</v>
       </c>
       <c r="G43" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
@@ -5162,22 +5258,22 @@
         <v>6</v>
       </c>
       <c r="B44" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E44" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F44" t="s">
         <v>9</v>
       </c>
       <c r="G44" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
@@ -5188,19 +5284,19 @@
         <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E45" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F45" t="s">
         <v>9</v>
       </c>
       <c r="G45" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.45">
@@ -5208,22 +5304,22 @@
         <v>6</v>
       </c>
       <c r="B46" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C46" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E46" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F46" t="s">
         <v>9</v>
       </c>
       <c r="G46" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.45">
@@ -5231,22 +5327,22 @@
         <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C47" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E47" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="F47" t="s">
         <v>9</v>
       </c>
       <c r="G47" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.45">
@@ -5257,19 +5353,19 @@
         <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>56</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>251</v>
+        <v>22</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E48" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="F48" t="s">
         <v>9</v>
       </c>
       <c r="G48" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.45">
@@ -5280,19 +5376,19 @@
         <v>6</v>
       </c>
       <c r="C49" t="s">
-        <v>22</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>254</v>
+        <v>95</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E49" t="s">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="F49" t="s">
         <v>9</v>
       </c>
       <c r="G49" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.45">
@@ -5303,19 +5399,19 @@
         <v>6</v>
       </c>
       <c r="C50" t="s">
-        <v>95</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>251</v>
+        <v>62</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E50" t="s">
-        <v>96</v>
+        <v>8</v>
       </c>
       <c r="F50" t="s">
         <v>9</v>
       </c>
       <c r="G50" t="s">
-        <v>97</v>
+        <v>63</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.45">
@@ -5326,7 +5422,7 @@
         <v>6</v>
       </c>
       <c r="C51" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>254</v>
@@ -5338,7 +5434,7 @@
         <v>9</v>
       </c>
       <c r="G51" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.45">
@@ -5349,7 +5445,7 @@
         <v>6</v>
       </c>
       <c r="C52" t="s">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>254</v>
@@ -5361,7 +5457,7 @@
         <v>9</v>
       </c>
       <c r="G52" t="s">
-        <v>51</v>
+        <v>107</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.45">
@@ -5372,19 +5468,19 @@
         <v>6</v>
       </c>
       <c r="C53" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>254</v>
       </c>
       <c r="E53" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F53" t="s">
         <v>9</v>
       </c>
       <c r="G53" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.45">
@@ -5395,19 +5491,19 @@
         <v>6</v>
       </c>
       <c r="C54" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>254</v>
       </c>
       <c r="E54" t="s">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="F54" t="s">
         <v>9</v>
       </c>
       <c r="G54" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.45">
@@ -5418,19 +5514,19 @@
         <v>6</v>
       </c>
       <c r="C55" t="s">
-        <v>89</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>254</v>
+        <v>102</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E55" t="s">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="F55" t="s">
         <v>9</v>
       </c>
       <c r="G55" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.45">
@@ -5441,7 +5537,7 @@
         <v>6</v>
       </c>
       <c r="C56" t="s">
-        <v>280</v>
+        <v>104</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>251</v>
@@ -5453,7 +5549,7 @@
         <v>9</v>
       </c>
       <c r="G56" t="s">
-        <v>281</v>
+        <v>105</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.45">
@@ -5464,7 +5560,7 @@
         <v>6</v>
       </c>
       <c r="C57" t="s">
-        <v>102</v>
+        <v>279</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>251</v>
@@ -5476,36 +5572,13 @@
         <v>9</v>
       </c>
       <c r="G57" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A58" t="s">
-        <v>6</v>
-      </c>
-      <c r="B58" t="s">
-        <v>6</v>
-      </c>
-      <c r="C58" t="s">
-        <v>104</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="E58" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" t="s">
-        <v>9</v>
-      </c>
-      <c r="G58" t="s">
-        <v>105</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G58" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G58">
-      <sortCondition ref="C1:C58"/>
+  <autoFilter ref="A1:G57" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G57">
+      <sortCondition ref="C1:C57"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/DropDownAccessMethods.xlsx
+++ b/docs/DropDownAccessMethods.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robin\spCoin\SPCOIN-PROJECT-MODULES\spcoin-nextjs-front-end\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0902D76B-AB7B-4727-8809-41BB35210D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF02CBB7-76CB-4F02-8A30-D3E0C7EE4E2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2023" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2016" uniqueCount="309">
   <si>
     <t>Panel</t>
   </si>
@@ -955,6 +955,9 @@
   </si>
   <si>
     <t>getMasterAccountCount</t>
+  </si>
+  <si>
+    <t>getAgentRateTransaction</t>
   </si>
 </sst>
 </file>
@@ -4505,7 +4508,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.1328125" customWidth="1"/>
@@ -4655,27 +4658,73 @@
         <v>38</v>
       </c>
     </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>282</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s">
+        <v>65</v>
+      </c>
+    </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>254</v>
       </c>
       <c r="E9" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>287</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
@@ -4686,19 +4735,19 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>307</v>
+        <v>75</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>254</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>302</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
@@ -4706,68 +4755,22 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>274</v>
+        <v>80</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>254</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="F11" t="s">
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" t="s">
-        <v>282</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="E13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G13" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" t="s">
-        <v>64</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>9</v>
-      </c>
-      <c r="G14" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
@@ -4775,22 +4778,22 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>251</v>
+        <v>306</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E15" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="F15" t="s">
         <v>9</v>
       </c>
       <c r="G15" t="s">
-        <v>68</v>
+        <v>287</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
@@ -4801,19 +4804,19 @@
         <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>251</v>
+        <v>307</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E16" t="s">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
         <v>9</v>
       </c>
       <c r="G16" t="s">
-        <v>79</v>
+        <v>302</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
@@ -4824,42 +4827,65 @@
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>251</v>
+        <v>274</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E17" t="s">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
         <v>9</v>
       </c>
       <c r="G17" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" t="s">
         <v>18</v>
       </c>
-      <c r="C18" t="s">
-        <v>80</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="E18" t="s">
-        <v>67</v>
-      </c>
-      <c r="F18" t="s">
-        <v>9</v>
-      </c>
-      <c r="G18" t="s">
-        <v>81</v>
+      <c r="C19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s">
+        <v>297</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E20" t="s">
+        <v>295</v>
+      </c>
+      <c r="F20" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
@@ -4867,68 +4893,68 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>294</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E21" t="s">
-        <v>25</v>
+        <v>295</v>
       </c>
       <c r="F21" t="s">
         <v>9</v>
       </c>
       <c r="G21" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" t="s">
-        <v>297</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="E22" t="s">
-        <v>295</v>
-      </c>
-      <c r="F22" t="s">
-        <v>9</v>
-      </c>
-      <c r="G22" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" t="s">
-        <v>294</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="E23" t="s">
-        <v>295</v>
-      </c>
-      <c r="F23" t="s">
-        <v>9</v>
-      </c>
-      <c r="G23" t="s">
         <v>296</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E28" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" t="s">
+        <v>9</v>
+      </c>
+      <c r="G28" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E29" t="s">
+        <v>85</v>
+      </c>
+      <c r="F29" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
@@ -4939,7 +4965,7 @@
         <v>6</v>
       </c>
       <c r="C30" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>251</v>
@@ -4951,7 +4977,7 @@
         <v>9</v>
       </c>
       <c r="G30" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
@@ -4962,19 +4988,19 @@
         <v>6</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>251</v>
+        <v>7</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E31" t="s">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="F31" t="s">
         <v>9</v>
       </c>
       <c r="G31" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
@@ -4985,19 +5011,19 @@
         <v>6</v>
       </c>
       <c r="C32" t="s">
-        <v>71</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>251</v>
+        <v>255</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E32" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="F32" t="s">
         <v>9</v>
       </c>
       <c r="G32" t="s">
-        <v>72</v>
+        <v>305</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
@@ -5008,7 +5034,7 @@
         <v>6</v>
       </c>
       <c r="C33" t="s">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>254</v>
@@ -5020,7 +5046,7 @@
         <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>10</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
@@ -5031,7 +5057,7 @@
         <v>6</v>
       </c>
       <c r="C34" t="s">
-        <v>255</v>
+        <v>48</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>254</v>
@@ -5043,7 +5069,7 @@
         <v>9</v>
       </c>
       <c r="G34" t="s">
-        <v>305</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
@@ -5054,19 +5080,19 @@
         <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>60</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>254</v>
+        <v>39</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E35" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F35" t="s">
-        <v>9</v>
+        <v>126</v>
       </c>
       <c r="G35" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
@@ -5077,19 +5103,19 @@
         <v>6</v>
       </c>
       <c r="C36" t="s">
-        <v>48</v>
+        <v>292</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>254</v>
       </c>
       <c r="E36" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F36" t="s">
         <v>9</v>
       </c>
       <c r="G36" t="s">
-        <v>49</v>
+        <v>293</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
@@ -5100,19 +5126,19 @@
         <v>6</v>
       </c>
       <c r="C37" t="s">
-        <v>39</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>251</v>
+        <v>290</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E37" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F37" t="s">
-        <v>126</v>
+        <v>9</v>
       </c>
       <c r="G37" t="s">
-        <v>41</v>
+        <v>291</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
@@ -5123,19 +5149,19 @@
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>292</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>254</v>
+        <v>275</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E38" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F38" t="s">
         <v>9</v>
       </c>
       <c r="G38" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
@@ -5146,19 +5172,19 @@
         <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>290</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>254</v>
+        <v>277</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E39" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="F39" t="s">
         <v>9</v>
       </c>
       <c r="G39" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
@@ -5169,19 +5195,19 @@
         <v>6</v>
       </c>
       <c r="C40" t="s">
-        <v>275</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>251</v>
+        <v>52</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E40" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="F40" t="s">
         <v>9</v>
       </c>
       <c r="G40" t="s">
-        <v>289</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
@@ -5189,22 +5215,22 @@
         <v>6</v>
       </c>
       <c r="B41" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C41" t="s">
-        <v>277</v>
+        <v>43</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E41" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F41" t="s">
         <v>9</v>
       </c>
       <c r="G41" t="s">
-        <v>288</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
@@ -5215,19 +5241,19 @@
         <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>52</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>254</v>
+        <v>46</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E42" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F42" t="s">
         <v>9</v>
       </c>
       <c r="G42" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
@@ -5235,10 +5261,10 @@
         <v>6</v>
       </c>
       <c r="B43" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>251</v>
@@ -5250,7 +5276,7 @@
         <v>9</v>
       </c>
       <c r="G43" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
@@ -5258,10 +5284,10 @@
         <v>6</v>
       </c>
       <c r="B44" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C44" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>251</v>
@@ -5273,7 +5299,7 @@
         <v>9</v>
       </c>
       <c r="G44" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
@@ -5284,19 +5310,19 @@
         <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E45" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="F45" t="s">
         <v>9</v>
       </c>
       <c r="G45" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.45">
@@ -5304,22 +5330,22 @@
         <v>6</v>
       </c>
       <c r="B46" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C46" t="s">
-        <v>54</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>251</v>
+        <v>22</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E46" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="F46" t="s">
         <v>9</v>
       </c>
       <c r="G46" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.45">
@@ -5330,19 +5356,19 @@
         <v>6</v>
       </c>
       <c r="C47" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E47" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="F47" t="s">
         <v>9</v>
       </c>
       <c r="G47" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.45">
@@ -5353,7 +5379,7 @@
         <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>254</v>
@@ -5365,7 +5391,7 @@
         <v>9</v>
       </c>
       <c r="G48" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.45">
@@ -5376,19 +5402,19 @@
         <v>6</v>
       </c>
       <c r="C49" t="s">
-        <v>95</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>251</v>
+        <v>50</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E49" t="s">
-        <v>96</v>
+        <v>8</v>
       </c>
       <c r="F49" t="s">
         <v>9</v>
       </c>
       <c r="G49" t="s">
-        <v>97</v>
+        <v>51</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.45">
@@ -5399,7 +5425,7 @@
         <v>6</v>
       </c>
       <c r="C50" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>254</v>
@@ -5411,7 +5437,7 @@
         <v>9</v>
       </c>
       <c r="G50" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.45">
@@ -5422,19 +5448,19 @@
         <v>6</v>
       </c>
       <c r="C51" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>254</v>
       </c>
       <c r="E51" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F51" t="s">
         <v>9</v>
       </c>
       <c r="G51" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.45">
@@ -5445,19 +5471,19 @@
         <v>6</v>
       </c>
       <c r="C52" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>254</v>
       </c>
       <c r="E52" t="s">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="F52" t="s">
         <v>9</v>
       </c>
       <c r="G52" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.45">
@@ -5468,19 +5494,19 @@
         <v>6</v>
       </c>
       <c r="C53" t="s">
-        <v>92</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>254</v>
+        <v>102</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E53" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F53" t="s">
         <v>9</v>
       </c>
       <c r="G53" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.45">
@@ -5491,19 +5517,19 @@
         <v>6</v>
       </c>
       <c r="C54" t="s">
-        <v>89</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>254</v>
+        <v>104</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E54" t="s">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="F54" t="s">
         <v>9</v>
       </c>
       <c r="G54" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.45">
@@ -5514,7 +5540,7 @@
         <v>6</v>
       </c>
       <c r="C55" t="s">
-        <v>102</v>
+        <v>279</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>251</v>
@@ -5526,59 +5552,13 @@
         <v>9</v>
       </c>
       <c r="G55" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A56" t="s">
-        <v>6</v>
-      </c>
-      <c r="B56" t="s">
-        <v>6</v>
-      </c>
-      <c r="C56" t="s">
-        <v>104</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="E56" t="s">
-        <v>8</v>
-      </c>
-      <c r="F56" t="s">
-        <v>9</v>
-      </c>
-      <c r="G56" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A57" t="s">
-        <v>6</v>
-      </c>
-      <c r="B57" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57" t="s">
-        <v>279</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="E57" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" t="s">
-        <v>9</v>
-      </c>
-      <c r="G57" t="s">
         <v>280</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G57" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G57">
-      <sortCondition ref="C1:C57"/>
+  <autoFilter ref="A1:G55" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G55">
+      <sortCondition ref="C1:C55"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/DropDownAccessMethods.xlsx
+++ b/docs/DropDownAccessMethods.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robin\spCoin\SPCOIN-PROJECT-MODULES\spcoin-nextjs-front-end\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF02CBB7-76CB-4F02-8A30-D3E0C7EE4E2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACC85AC9-A35D-4379-B53B-0FFE1803CD40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2016" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2018" uniqueCount="311">
   <si>
     <t>Panel</t>
   </si>
@@ -958,6 +958,12 @@
   </si>
   <si>
     <t>getAgentRateTransaction</t>
+  </si>
+  <si>
+    <t>================================================================ TODO =========================================================================</t>
+  </si>
+  <si>
+    <t>================================================================ WIP =========================================================================</t>
   </si>
 </sst>
 </file>
@@ -1019,7 +1025,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1035,6 +1041,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4508,7 +4515,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.1328125" customWidth="1"/>
@@ -4773,6 +4780,52 @@
         <v>81</v>
       </c>
     </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>306</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E13" t="s">
+        <v>94</v>
+      </c>
+      <c r="F13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>307</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14" t="s">
+        <v>302</v>
+      </c>
+    </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>6</v>
@@ -4781,88 +4834,24 @@
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>306</v>
+        <v>274</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>254</v>
       </c>
       <c r="E15" t="s">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
         <v>9</v>
       </c>
       <c r="G15" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" t="s">
-        <v>307</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>9</v>
-      </c>
-      <c r="G16" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" t="s">
-        <v>274</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="E19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" t="s">
-        <v>9</v>
-      </c>
-      <c r="G19" t="s">
-        <v>32</v>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A18" s="7" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
@@ -4870,22 +4859,22 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>297</v>
+        <v>31</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E20" t="s">
-        <v>295</v>
+        <v>25</v>
       </c>
       <c r="F20" t="s">
         <v>9</v>
       </c>
       <c r="G20" t="s">
-        <v>298</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
@@ -4896,7 +4885,7 @@
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>251</v>
@@ -4908,30 +4897,35 @@
         <v>9</v>
       </c>
       <c r="G21" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>294</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E22" t="s">
+        <v>295</v>
+      </c>
+      <c r="F22" t="s">
+        <v>9</v>
+      </c>
+      <c r="G22" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" t="s">
-        <v>82</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="E28" t="s">
-        <v>59</v>
-      </c>
-      <c r="F28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G28" t="s">
-        <v>83</v>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A26" s="7" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
@@ -4942,19 +4936,19 @@
         <v>6</v>
       </c>
       <c r="C29" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E29" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="F29" t="s">
         <v>9</v>
       </c>
       <c r="G29" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
@@ -4965,19 +4959,19 @@
         <v>6</v>
       </c>
       <c r="C30" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E30" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="F30" t="s">
         <v>9</v>
       </c>
       <c r="G30" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
@@ -4988,19 +4982,19 @@
         <v>6</v>
       </c>
       <c r="C31" t="s">
-        <v>7</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>254</v>
+        <v>71</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E31" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="F31" t="s">
         <v>9</v>
       </c>
       <c r="G31" t="s">
-        <v>10</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
@@ -5011,7 +5005,7 @@
         <v>6</v>
       </c>
       <c r="C32" t="s">
-        <v>255</v>
+        <v>7</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>254</v>
@@ -5023,7 +5017,7 @@
         <v>9</v>
       </c>
       <c r="G32" t="s">
-        <v>305</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
@@ -5034,7 +5028,7 @@
         <v>6</v>
       </c>
       <c r="C33" t="s">
-        <v>60</v>
+        <v>255</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>254</v>
@@ -5046,7 +5040,7 @@
         <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>61</v>
+        <v>305</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
@@ -5057,7 +5051,7 @@
         <v>6</v>
       </c>
       <c r="C34" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>254</v>
@@ -5069,7 +5063,7 @@
         <v>9</v>
       </c>
       <c r="G34" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
@@ -5080,19 +5074,19 @@
         <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>39</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>251</v>
+        <v>48</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E35" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>126</v>
+        <v>9</v>
       </c>
       <c r="G35" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
@@ -5103,19 +5097,19 @@
         <v>6</v>
       </c>
       <c r="C36" t="s">
-        <v>292</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>254</v>
+        <v>39</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E36" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F36" t="s">
-        <v>9</v>
+        <v>126</v>
       </c>
       <c r="G36" t="s">
-        <v>293</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
@@ -5126,7 +5120,7 @@
         <v>6</v>
       </c>
       <c r="C37" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>254</v>
@@ -5138,7 +5132,7 @@
         <v>9</v>
       </c>
       <c r="G37" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
@@ -5149,19 +5143,19 @@
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>275</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>251</v>
+        <v>290</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E38" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="F38" t="s">
         <v>9</v>
       </c>
       <c r="G38" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
@@ -5172,19 +5166,19 @@
         <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E39" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F39" t="s">
         <v>9</v>
       </c>
       <c r="G39" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
@@ -5195,19 +5189,19 @@
         <v>6</v>
       </c>
       <c r="C40" t="s">
-        <v>52</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>254</v>
+        <v>277</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E40" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F40" t="s">
         <v>9</v>
       </c>
       <c r="G40" t="s">
-        <v>53</v>
+        <v>288</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
@@ -5215,22 +5209,22 @@
         <v>6</v>
       </c>
       <c r="B41" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>43</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>251</v>
+        <v>52</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E41" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="F41" t="s">
         <v>9</v>
       </c>
       <c r="G41" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
@@ -5238,22 +5232,22 @@
         <v>6</v>
       </c>
       <c r="B42" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C42" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E42" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F42" t="s">
         <v>9</v>
       </c>
       <c r="G42" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
@@ -5264,19 +5258,19 @@
         <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E43" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F43" t="s">
         <v>9</v>
       </c>
       <c r="G43" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
@@ -5284,22 +5278,22 @@
         <v>6</v>
       </c>
       <c r="B44" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E44" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F44" t="s">
         <v>9</v>
       </c>
       <c r="G44" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
@@ -5307,22 +5301,22 @@
         <v>6</v>
       </c>
       <c r="B45" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C45" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E45" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="F45" t="s">
         <v>9</v>
       </c>
       <c r="G45" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.45">
@@ -5333,19 +5327,19 @@
         <v>6</v>
       </c>
       <c r="C46" t="s">
-        <v>22</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>254</v>
+        <v>56</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E46" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="F46" t="s">
         <v>9</v>
       </c>
       <c r="G46" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.45">
@@ -5356,19 +5350,19 @@
         <v>6</v>
       </c>
       <c r="C47" t="s">
-        <v>95</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>251</v>
+        <v>22</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E47" t="s">
-        <v>96</v>
+        <v>8</v>
       </c>
       <c r="F47" t="s">
         <v>9</v>
       </c>
       <c r="G47" t="s">
-        <v>97</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.45">
@@ -5379,19 +5373,19 @@
         <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>62</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>254</v>
+        <v>95</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E48" t="s">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="F48" t="s">
         <v>9</v>
       </c>
       <c r="G48" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.45">
@@ -5402,7 +5396,7 @@
         <v>6</v>
       </c>
       <c r="C49" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>254</v>
@@ -5414,7 +5408,7 @@
         <v>9</v>
       </c>
       <c r="G49" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.45">
@@ -5425,7 +5419,7 @@
         <v>6</v>
       </c>
       <c r="C50" t="s">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>254</v>
@@ -5437,7 +5431,7 @@
         <v>9</v>
       </c>
       <c r="G50" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.45">
@@ -5448,19 +5442,19 @@
         <v>6</v>
       </c>
       <c r="C51" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>254</v>
       </c>
       <c r="E51" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F51" t="s">
         <v>9</v>
       </c>
       <c r="G51" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.45">
@@ -5471,19 +5465,19 @@
         <v>6</v>
       </c>
       <c r="C52" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>254</v>
       </c>
       <c r="E52" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="F52" t="s">
         <v>9</v>
       </c>
       <c r="G52" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.45">
@@ -5494,19 +5488,19 @@
         <v>6</v>
       </c>
       <c r="C53" t="s">
-        <v>102</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>251</v>
+        <v>89</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E53" t="s">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="F53" t="s">
         <v>9</v>
       </c>
       <c r="G53" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.45">
@@ -5517,7 +5511,7 @@
         <v>6</v>
       </c>
       <c r="C54" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>251</v>
@@ -5529,7 +5523,7 @@
         <v>9</v>
       </c>
       <c r="G54" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.45">
@@ -5540,7 +5534,7 @@
         <v>6</v>
       </c>
       <c r="C55" t="s">
-        <v>279</v>
+        <v>104</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>251</v>
@@ -5552,13 +5546,36 @@
         <v>9</v>
       </c>
       <c r="G55" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>6</v>
+      </c>
+      <c r="B56" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" t="s">
+        <v>279</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E56" t="s">
+        <v>8</v>
+      </c>
+      <c r="F56" t="s">
+        <v>9</v>
+      </c>
+      <c r="G56" t="s">
         <v>280</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G55" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G55">
-      <sortCondition ref="C1:C55"/>
+  <autoFilter ref="A1:G56" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G56">
+      <sortCondition ref="C1:C56"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/DropDownAccessMethods.xlsx
+++ b/docs/DropDownAccessMethods.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robin\spCoin\SPCOIN-PROJECT-MODULES\spcoin-nextjs-front-end\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{585A375C-497E-499F-8BD3-74F80F38AEB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91F8F44-F0F8-4015-BB1F-06B285C1DBDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="358">
   <si>
     <t>Panel</t>
   </si>
@@ -135,21 +135,9 @@
     <t>Sponsor Key, Recipient Key</t>
   </si>
   <si>
-    <t>getRecipientRateRecord</t>
-  </si>
-  <si>
     <t>Sponsor Key, Recipient Key, Recipient Rate Key</t>
   </si>
   <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getRecipientRateRecord.ts</t>
-  </si>
-  <si>
-    <t>getRecipientRateRecordList</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getRecipientRateRecordList.ts</t>
-  </si>
-  <si>
     <t>getLowerRecipientRate</t>
   </si>
   <si>
@@ -204,15 +192,9 @@
     <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getAgentRateRange.ts</t>
   </si>
   <si>
-    <t>getAgentRateRecord</t>
-  </si>
-  <si>
     <t>Sponsor Key, Recipient Key, Recipient Rate Key, Agent Key, Agent Rate Key</t>
   </si>
   <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getAgentRateRecord.ts</t>
-  </si>
-  <si>
     <t>getAgentTotalRecipient</t>
   </si>
   <si>
@@ -672,9 +654,6 @@
     <t>external_getSerializedRecipientRateList</t>
   </si>
   <si>
-    <t>external_serializeAgentRateRecordStr</t>
-  </si>
-  <si>
     <t>external_getSerializedRateTransactionList</t>
   </si>
   <si>
@@ -825,15 +804,9 @@
     <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getAgentListSize.ts</t>
   </si>
   <si>
-    <t>getAccountRateRecordList</t>
-  </si>
-  <si>
     <t>Rate Reward List</t>
   </si>
   <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getAccountRateRecordList.ts</t>
-  </si>
-  <si>
     <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getMasterAccountListSize.ts</t>
   </si>
   <si>
@@ -1005,9 +978,6 @@
     <t>getRecipientRateList(address,address)</t>
   </si>
   <si>
-    <t>getRecipientRateRecordCore(address,address,uint256)</t>
-  </si>
-  <si>
     <t>addRecipientAgent(address,address,uint256,address)</t>
   </si>
   <si>
@@ -1020,9 +990,6 @@
     <t>getAgentRateList(address,address,uint256,address)</t>
   </si>
   <si>
-    <t>getAgentRateRecordCore(address,address,uint256,address,uint256)</t>
-  </si>
-  <si>
     <t>Rewards / staking</t>
   </si>
   <si>
@@ -1044,9 +1011,6 @@
     <t>updateAgentAccountRewards(address)</t>
   </si>
   <si>
-    <t>updateRecipietAccountRewards(address)</t>
-  </si>
-  <si>
     <t>Transaction methods</t>
   </si>
   <si>
@@ -1104,7 +1068,43 @@
     <t>deleteAccountRecord(address)</t>
   </si>
   <si>
-    <t>On Chain Methodss</t>
+    <t>getRecipientRateTransactionCore(address,address,uint256)</t>
+  </si>
+  <si>
+    <t>getAgentRateTransactionCore(address,address,uint256,address,uint256)</t>
+  </si>
+  <si>
+    <t>updateRecipientAccountRewards(address)</t>
+  </si>
+  <si>
+    <t>getRecipientRateTransaction</t>
+  </si>
+  <si>
+    <t>getRecipientRateTransactionList</t>
+  </si>
+  <si>
+    <t>getAccountRateTransactionList</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> calculateStakingRewards(uint256,uint256,uint256,uint256)</t>
+  </si>
+  <si>
+    <t>On Chain Methods</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getAccountRateTransactionList.ts</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getAgentRateTransaction.ts</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getRecipientRateTransaction.ts</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getRecipientRateTransactionList.ts</t>
+  </si>
+  <si>
+    <t>external_serializeAgentRateTransactionStr</t>
   </si>
 </sst>
 </file>
@@ -1144,12 +1144,13 @@
       <family val="3"/>
     </font>
     <font>
+      <b/>
       <sz val="18"/>
-      <name val="Calibri"/>
+      <name val="Segoe UI"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1176,13 +1177,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1199,7 +1206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1216,21 +1223,20 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1567,619 +1573,433 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:E118"/>
+  <dimension ref="A1:A83"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="103.73046875" customWidth="1"/>
-    <col min="4" max="4" width="12" style="4" customWidth="1"/>
-    <col min="5" max="5" width="72" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="7" width="96" customWidth="1"/>
+    <col min="1" max="1" width="99.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="72" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="96" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:5" s="11" customFormat="1" ht="23.25" x14ac:dyDescent="0.7">
-      <c r="D1" s="12"/>
-      <c r="E1" s="13" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="2" spans="3:5" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="C2" s="8" t="s">
+    <row r="1" spans="1:1" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="A1" s="12" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
+      <c r="A2" s="13" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
+      <c r="A3" s="10" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A4" s="9" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A5" s="9" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A6" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A7" s="9" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A8" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A9" s="9" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A10" s="9" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A11" s="9" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="3" spans="3:5" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="C3" s="14" t="s">
+    <row r="12" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A12" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="D3" s="5"/>
-    </row>
-    <row r="4" spans="3:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C4" s="10" t="s">
+    </row>
+    <row r="13" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A13" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="D4" s="5"/>
-    </row>
-    <row r="5" spans="3:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C5" s="10" t="s">
+    </row>
+    <row r="14" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
+      <c r="A14" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="D5" s="5"/>
-    </row>
-    <row r="6" spans="3:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C6" s="10" t="s">
+    </row>
+    <row r="15" spans="1:1" ht="20.350000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="D6" s="5"/>
-    </row>
-    <row r="7" spans="3:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C7" s="10" t="s">
+    </row>
+    <row r="16" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A16" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="D7" s="5"/>
-    </row>
-    <row r="8" spans="3:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C8" s="10" t="s">
+    </row>
+    <row r="17" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A17" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="3:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C9" s="10" t="s">
+    </row>
+    <row r="18" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A18" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="D9" s="5"/>
-    </row>
-    <row r="10" spans="3:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C10" s="10" t="s">
+    </row>
+    <row r="19" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A19" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" spans="3:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C11" s="10" t="s">
+    </row>
+    <row r="20" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A20" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12" spans="3:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C12" s="10" t="s">
+    </row>
+    <row r="21" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
+      <c r="A21" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13" spans="3:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C13" s="10" t="s">
+    </row>
+    <row r="22" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
+      <c r="A22" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="D13" s="5"/>
-    </row>
-    <row r="14" spans="3:5" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="C14" s="8" t="s">
+    </row>
+    <row r="23" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A23" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="3:5" ht="20.350000000000001" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C15" s="14" t="s">
+    </row>
+    <row r="24" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A24" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="D15" s="5"/>
-    </row>
-    <row r="16" spans="3:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C16" s="10" t="s">
+    </row>
+    <row r="25" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A25" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C17" s="10" t="s">
+    </row>
+    <row r="26" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A26" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="D17" s="5"/>
-    </row>
-    <row r="18" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C18" s="10" t="s">
+    </row>
+    <row r="27" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A27" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="D18" s="5"/>
-    </row>
-    <row r="19" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C19" s="10" t="s">
+    </row>
+    <row r="28" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A28" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="D19" s="5"/>
-    </row>
-    <row r="20" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C20" s="10" t="s">
+    </row>
+    <row r="29" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A29" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="3:4" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="C21" s="8" t="s">
+    </row>
+    <row r="30" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A30" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="D21" s="5"/>
-    </row>
-    <row r="22" spans="3:4" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="C22" s="14" t="s">
+    </row>
+    <row r="31" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A31" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="D22" s="5"/>
-    </row>
-    <row r="23" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C23" s="10" t="s">
+    </row>
+    <row r="32" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A32" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="D23" s="5"/>
-    </row>
-    <row r="24" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C24" s="10" t="s">
+    </row>
+    <row r="33" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A33" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="D24" s="5"/>
-    </row>
-    <row r="25" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C25" s="10" t="s">
+    </row>
+    <row r="34" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A34" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="D25" s="5"/>
-    </row>
-    <row r="26" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C26" s="10" t="s">
+    </row>
+    <row r="35" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A35" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="D26" s="5"/>
-    </row>
-    <row r="27" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C27" s="10" t="s">
+    </row>
+    <row r="36" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
+      <c r="A36" s="13" t="s">
         <v>301</v>
       </c>
-      <c r="D27" s="5"/>
-    </row>
-    <row r="28" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C28" s="10" t="s">
+    </row>
+    <row r="37" spans="1:1" ht="37.5" x14ac:dyDescent="0.45">
+      <c r="A37" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="D28" s="5"/>
-    </row>
-    <row r="29" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C29" s="10" t="s">
+    </row>
+    <row r="38" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A38" s="9" t="s">
         <v>303</v>
       </c>
-      <c r="D29" s="5"/>
-    </row>
-    <row r="30" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C30" s="10" t="s">
+    </row>
+    <row r="39" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A39" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="D30" s="5"/>
-    </row>
-    <row r="31" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C31" s="10" t="s">
+    </row>
+    <row r="40" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A40" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="D31" s="5"/>
-    </row>
-    <row r="32" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C32" s="10" t="s">
+    </row>
+    <row r="41" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A41" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="D32" s="5"/>
-    </row>
-    <row r="33" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C33" s="10" t="s">
+    </row>
+    <row r="42" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A42" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="D33" s="5"/>
-    </row>
-    <row r="34" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C34" s="10" t="s">
+    </row>
+    <row r="43" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A43" s="9" t="s">
         <v>308</v>
       </c>
-      <c r="D34" s="5"/>
-    </row>
-    <row r="35" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C35" s="10" t="s">
+    </row>
+    <row r="44" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A44" s="9" t="s">
         <v>309</v>
       </c>
-      <c r="D35" s="5"/>
-    </row>
-    <row r="36" spans="3:4" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="C36" s="8" t="s">
+    </row>
+    <row r="45" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A45" s="9" t="s">
         <v>310</v>
       </c>
-      <c r="D36" s="5"/>
-    </row>
-    <row r="37" spans="3:4" ht="37.5" x14ac:dyDescent="0.45">
-      <c r="C37" s="14" t="s">
+    </row>
+    <row r="46" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A46" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="D37" s="5"/>
-    </row>
-    <row r="38" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C38" s="10" t="s">
+    </row>
+    <row r="47" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A47" s="9" t="s">
         <v>312</v>
       </c>
-      <c r="D38" s="5"/>
-    </row>
-    <row r="39" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C39" s="10" t="s">
+    </row>
+    <row r="48" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A48" s="9" t="s">
         <v>313</v>
       </c>
-      <c r="D39" s="5"/>
-    </row>
-    <row r="40" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C40" s="10" t="s">
+    </row>
+    <row r="49" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A49" s="9" t="s">
         <v>314</v>
       </c>
-      <c r="D40" s="5"/>
-    </row>
-    <row r="41" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C41" s="10" t="s">
+    </row>
+    <row r="50" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A50" s="9" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A51" s="9" t="s">
         <v>315</v>
       </c>
-      <c r="D41" s="5"/>
-    </row>
-    <row r="42" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C42" s="10" t="s">
+    </row>
+    <row r="52" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A52" s="9" t="s">
         <v>316</v>
       </c>
-      <c r="D42" s="5"/>
-    </row>
-    <row r="43" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C43" s="10" t="s">
+    </row>
+    <row r="53" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A53" s="9" t="s">
         <v>317</v>
       </c>
-      <c r="D43" s="5"/>
-    </row>
-    <row r="44" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C44" s="10" t="s">
+    </row>
+    <row r="54" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A54" s="9" t="s">
         <v>318</v>
       </c>
-      <c r="D44" s="5"/>
-    </row>
-    <row r="45" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C45" s="10" t="s">
+    </row>
+    <row r="55" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A55" s="9" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
+      <c r="A56" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="D45" s="5"/>
-    </row>
-    <row r="46" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C46" s="10" t="s">
+    </row>
+    <row r="57" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
+      <c r="A57" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="D46" s="5"/>
-    </row>
-    <row r="47" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C47" s="10" t="s">
+    </row>
+    <row r="58" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A58" s="11" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A59" s="9" t="s">
         <v>321</v>
       </c>
-      <c r="D47" s="5"/>
-    </row>
-    <row r="48" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C48" s="10" t="s">
+    </row>
+    <row r="60" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A60" s="9" t="s">
         <v>322</v>
       </c>
-      <c r="D48" s="5"/>
-    </row>
-    <row r="49" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C49" s="10" t="s">
+    </row>
+    <row r="61" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A61" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="D49" s="5"/>
-    </row>
-    <row r="50" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C50" s="10" t="s">
+    </row>
+    <row r="62" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A62" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="D50" s="5"/>
-    </row>
-    <row r="51" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C51" s="10" t="s">
+    </row>
+    <row r="63" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A63" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="D51" s="5"/>
-    </row>
-    <row r="52" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C52" s="10" t="s">
+    </row>
+    <row r="64" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A64" s="9" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
+      <c r="A65" s="13" t="s">
         <v>326</v>
       </c>
-      <c r="D52" s="5"/>
-    </row>
-    <row r="53" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C53" s="10" t="s">
+    </row>
+    <row r="66" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
+      <c r="A66" s="8" t="s">
         <v>327</v>
       </c>
-      <c r="D53" s="5"/>
-    </row>
-    <row r="54" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C54" s="10" t="s">
+    </row>
+    <row r="67" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A67" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="D54" s="5"/>
-    </row>
-    <row r="55" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C55" s="10" t="s">
+    </row>
+    <row r="68" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A68" s="9" t="s">
         <v>329</v>
       </c>
-      <c r="D55" s="5"/>
-    </row>
-    <row r="56" spans="3:4" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="C56" s="8" t="s">
+    </row>
+    <row r="69" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A69" s="9" t="s">
         <v>330</v>
       </c>
-      <c r="D56" s="5"/>
-    </row>
-    <row r="57" spans="3:4" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="C57" s="14" t="s">
+    </row>
+    <row r="70" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A70" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="D57" s="5"/>
-    </row>
-    <row r="58" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C58" s="10" t="s">
+    </row>
+    <row r="71" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A71" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="D58" s="5"/>
-    </row>
-    <row r="59" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C59" s="10" t="s">
+    </row>
+    <row r="72" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A72" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="D59" s="5"/>
-    </row>
-    <row r="60" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C60" s="10" t="s">
+    </row>
+    <row r="73" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A73" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="D60" s="5"/>
-    </row>
-    <row r="61" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C61" s="10" t="s">
+    </row>
+    <row r="74" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
+      <c r="A74" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="D61" s="5"/>
-    </row>
-    <row r="62" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C62" s="10" t="s">
+    </row>
+    <row r="75" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
+      <c r="A75" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="D62" s="5"/>
-    </row>
-    <row r="63" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C63" s="10" t="s">
+    </row>
+    <row r="76" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A76" s="9" t="s">
         <v>337</v>
       </c>
-      <c r="D63" s="5"/>
-    </row>
-    <row r="64" spans="3:4" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="C64" s="8" t="s">
+    </row>
+    <row r="77" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A77" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="D64" s="5"/>
-    </row>
-    <row r="65" spans="3:4" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="C65" s="9" t="s">
+    </row>
+    <row r="78" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A78" s="9" t="s">
         <v>339</v>
       </c>
-      <c r="D65" s="5"/>
-    </row>
-    <row r="66" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C66" s="10" t="s">
+    </row>
+    <row r="79" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A79" s="9" t="s">
         <v>340</v>
       </c>
-      <c r="D66" s="5"/>
-    </row>
-    <row r="67" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C67" s="10" t="s">
+    </row>
+    <row r="80" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A80" s="9" t="s">
         <v>341</v>
       </c>
-      <c r="D67" s="5"/>
-    </row>
-    <row r="68" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C68" s="10" t="s">
+    </row>
+    <row r="81" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A81" s="9" t="s">
         <v>342</v>
       </c>
-      <c r="D68" s="5"/>
-    </row>
-    <row r="69" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C69" s="10" t="s">
+    </row>
+    <row r="82" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A82" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="D69" s="5"/>
-    </row>
-    <row r="70" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C70" s="10" t="s">
+    </row>
+    <row r="83" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A83" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="D70" s="5"/>
-    </row>
-    <row r="71" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C71" s="10" t="s">
-        <v>345</v>
-      </c>
-      <c r="D71" s="5"/>
-    </row>
-    <row r="72" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C72" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="D72" s="5"/>
-    </row>
-    <row r="73" spans="3:4" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="C73" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="D73" s="5"/>
-    </row>
-    <row r="74" spans="3:4" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="C74" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="D74" s="5"/>
-    </row>
-    <row r="75" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C75" s="10" t="s">
-        <v>349</v>
-      </c>
-      <c r="D75" s="5"/>
-    </row>
-    <row r="76" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C76" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="D76" s="5"/>
-    </row>
-    <row r="77" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C77" s="10" t="s">
-        <v>351</v>
-      </c>
-      <c r="D77" s="5"/>
-    </row>
-    <row r="78" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C78" s="10" t="s">
-        <v>352</v>
-      </c>
-      <c r="D78" s="5"/>
-    </row>
-    <row r="79" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C79" s="10" t="s">
-        <v>353</v>
-      </c>
-      <c r="D79" s="5"/>
-    </row>
-    <row r="80" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C80" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="D80" s="5"/>
-    </row>
-    <row r="81" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C81" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="D81" s="5"/>
-    </row>
-    <row r="82" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C82" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="D82" s="5"/>
-    </row>
-    <row r="83" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D83" s="5"/>
-    </row>
-    <row r="84" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D84" s="5"/>
-    </row>
-    <row r="85" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D85" s="5"/>
-    </row>
-    <row r="86" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D86" s="5"/>
-    </row>
-    <row r="87" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D87" s="5"/>
-    </row>
-    <row r="88" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D88" s="5"/>
-    </row>
-    <row r="89" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D89" s="5"/>
-    </row>
-    <row r="90" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D90" s="5"/>
-    </row>
-    <row r="91" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D91" s="5"/>
-    </row>
-    <row r="92" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D92" s="5"/>
-    </row>
-    <row r="93" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D93" s="5"/>
-    </row>
-    <row r="94" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D94" s="5"/>
-    </row>
-    <row r="95" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D95" s="5"/>
-    </row>
-    <row r="96" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D96" s="5"/>
-    </row>
-    <row r="97" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D97" s="5"/>
-    </row>
-    <row r="98" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D98" s="5"/>
-    </row>
-    <row r="99" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D99" s="5"/>
-    </row>
-    <row r="100" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D100" s="5"/>
-    </row>
-    <row r="101" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D101" s="5"/>
-    </row>
-    <row r="102" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D102" s="5"/>
-    </row>
-    <row r="103" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D103" s="5"/>
-    </row>
-    <row r="104" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D104" s="5"/>
-    </row>
-    <row r="105" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D105" s="5"/>
-    </row>
-    <row r="106" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D106" s="5"/>
-    </row>
-    <row r="107" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D107" s="5"/>
-    </row>
-    <row r="108" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D108" s="5"/>
-    </row>
-    <row r="109" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D109" s="5"/>
-    </row>
-    <row r="110" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D110" s="5"/>
-    </row>
-    <row r="111" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D111" s="5"/>
-    </row>
-    <row r="112" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D112" s="5"/>
-    </row>
-    <row r="113" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D113" s="5"/>
-    </row>
-    <row r="114" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D114" s="5"/>
-    </row>
-    <row r="115" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D115" s="5"/>
-    </row>
-    <row r="116" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D116" s="5"/>
-    </row>
-    <row r="117" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D117" s="5"/>
-    </row>
-    <row r="118" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D118" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2208,7 +2028,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -2222,85 +2042,85 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" t="s">
         <v>88</v>
       </c>
-      <c r="B2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C2" t="s">
-        <v>94</v>
-      </c>
       <c r="D2" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="F2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E4" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E5" t="s">
         <v>33</v>
@@ -2309,76 +2129,76 @@
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" t="s">
         <v>106</v>
-      </c>
-      <c r="C7" t="s">
-        <v>111</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="E7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C8" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -2415,7 +2235,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -2426,71 +2246,71 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" t="s">
         <v>88</v>
       </c>
-      <c r="B2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C2" t="s">
-        <v>94</v>
-      </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F4" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G4" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2527,7 +2347,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -2538,71 +2358,71 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D2" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C4" t="s">
         <v>151</v>
       </c>
-      <c r="C4" t="s">
-        <v>157</v>
-      </c>
       <c r="D4" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -2636,7 +2456,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -2659,7 +2479,7 @@
         <v>11</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -2679,19 +2499,19 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>264</v>
+        <v>350</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E3" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="F3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G3" t="s">
-        <v>266</v>
+        <v>353</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
@@ -2705,7 +2525,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -2728,13 +2548,13 @@
         <v>24</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E5" t="s">
         <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G5" t="s">
         <v>26</v>
@@ -2751,13 +2571,13 @@
         <v>27</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
       </c>
       <c r="F6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G6" t="s">
         <v>29</v>
@@ -2771,19 +2591,19 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E7" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
@@ -2794,10 +2614,10 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -2806,7 +2626,7 @@
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
@@ -2817,19 +2637,19 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E9" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>59</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
@@ -2840,19 +2660,19 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E10" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
@@ -2863,19 +2683,19 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E11" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F11" t="s">
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
@@ -2886,19 +2706,19 @@
         <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E13" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F13" t="s">
         <v>9</v>
       </c>
       <c r="G13" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
@@ -2909,10 +2729,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -2921,7 +2741,7 @@
         <v>9</v>
       </c>
       <c r="G14" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
@@ -2932,10 +2752,10 @@
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -2944,12 +2764,12 @@
         <v>9</v>
       </c>
       <c r="G15" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="7" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
@@ -2963,7 +2783,7 @@
         <v>22</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
@@ -2983,19 +2803,19 @@
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E21" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="F21" t="s">
         <v>9</v>
       </c>
       <c r="G21" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
@@ -3006,24 +2826,24 @@
         <v>6</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E22" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="F22" t="s">
         <v>9</v>
       </c>
       <c r="G22" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="7" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
@@ -3034,19 +2854,19 @@
         <v>6</v>
       </c>
       <c r="C29" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E29" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F29" t="s">
         <v>9</v>
       </c>
       <c r="G29" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
@@ -3057,19 +2877,19 @@
         <v>6</v>
       </c>
       <c r="C30" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E30" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F30" t="s">
         <v>9</v>
       </c>
       <c r="G30" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
@@ -3080,19 +2900,19 @@
         <v>6</v>
       </c>
       <c r="C31" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E31" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F31" t="s">
         <v>9</v>
       </c>
       <c r="G31" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
@@ -3106,7 +2926,7 @@
         <v>7</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -3126,10 +2946,10 @@
         <v>6</v>
       </c>
       <c r="C33" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -3138,7 +2958,7 @@
         <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
@@ -3149,10 +2969,10 @@
         <v>6</v>
       </c>
       <c r="C34" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -3161,7 +2981,7 @@
         <v>9</v>
       </c>
       <c r="G34" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
@@ -3172,10 +2992,10 @@
         <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -3184,7 +3004,7 @@
         <v>9</v>
       </c>
       <c r="G35" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
@@ -3198,13 +3018,13 @@
         <v>30</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E36" t="s">
         <v>31</v>
       </c>
       <c r="F36" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G36" t="s">
         <v>32</v>
@@ -3218,10 +3038,10 @@
         <v>6</v>
       </c>
       <c r="C37" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E37" t="s">
         <v>19</v>
@@ -3230,7 +3050,7 @@
         <v>9</v>
       </c>
       <c r="G37" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
@@ -3241,10 +3061,10 @@
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E38" t="s">
         <v>19</v>
@@ -3253,7 +3073,7 @@
         <v>9</v>
       </c>
       <c r="G38" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
@@ -3264,19 +3084,19 @@
         <v>6</v>
       </c>
       <c r="C39" t="s">
+        <v>240</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E39" t="s">
+        <v>34</v>
+      </c>
+      <c r="F39" t="s">
+        <v>9</v>
+      </c>
+      <c r="G39" t="s">
         <v>247</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="E39" t="s">
-        <v>35</v>
-      </c>
-      <c r="F39" t="s">
-        <v>9</v>
-      </c>
-      <c r="G39" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
@@ -3287,10 +3107,10 @@
         <v>6</v>
       </c>
       <c r="C40" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E40" t="s">
         <v>33</v>
@@ -3299,7 +3119,7 @@
         <v>9</v>
       </c>
       <c r="G40" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
@@ -3310,10 +3130,10 @@
         <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -3322,7 +3142,7 @@
         <v>9</v>
       </c>
       <c r="G41" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
@@ -3333,19 +3153,19 @@
         <v>13</v>
       </c>
       <c r="C42" t="s">
+        <v>348</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E42" t="s">
         <v>34</v>
       </c>
-      <c r="D42" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="E42" t="s">
-        <v>35</v>
-      </c>
       <c r="F42" t="s">
         <v>9</v>
       </c>
       <c r="G42" t="s">
-        <v>36</v>
+        <v>355</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
@@ -3356,10 +3176,10 @@
         <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>37</v>
+        <v>349</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E43" t="s">
         <v>33</v>
@@ -3368,7 +3188,7 @@
         <v>9</v>
       </c>
       <c r="G43" t="s">
-        <v>38</v>
+        <v>356</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
@@ -3379,19 +3199,19 @@
         <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F44" t="s">
         <v>9</v>
       </c>
       <c r="G44" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
@@ -3402,10 +3222,10 @@
         <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E45" t="s">
         <v>33</v>
@@ -3414,7 +3234,7 @@
         <v>9</v>
       </c>
       <c r="G45" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.45">
@@ -3425,19 +3245,19 @@
         <v>6</v>
       </c>
       <c r="C46" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E46" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F46" t="s">
         <v>9</v>
       </c>
       <c r="G46" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.45">
@@ -3451,7 +3271,7 @@
         <v>17</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -3471,19 +3291,19 @@
         <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E48" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F48" t="s">
         <v>9</v>
       </c>
       <c r="G48" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.45">
@@ -3494,10 +3314,10 @@
         <v>6</v>
       </c>
       <c r="C49" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -3506,7 +3326,7 @@
         <v>9</v>
       </c>
       <c r="G49" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.45">
@@ -3517,10 +3337,10 @@
         <v>6</v>
       </c>
       <c r="C50" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -3529,7 +3349,7 @@
         <v>9</v>
       </c>
       <c r="G50" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.45">
@@ -3540,10 +3360,10 @@
         <v>6</v>
       </c>
       <c r="C51" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -3552,7 +3372,7 @@
         <v>9</v>
       </c>
       <c r="G51" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.45">
@@ -3563,10 +3383,10 @@
         <v>6</v>
       </c>
       <c r="C52" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E52" t="s">
         <v>19</v>
@@ -3575,7 +3395,7 @@
         <v>9</v>
       </c>
       <c r="G52" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.45">
@@ -3586,19 +3406,19 @@
         <v>6</v>
       </c>
       <c r="C53" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E53" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F53" t="s">
         <v>9</v>
       </c>
       <c r="G53" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.45">
@@ -3609,10 +3429,10 @@
         <v>6</v>
       </c>
       <c r="C54" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -3621,7 +3441,7 @@
         <v>9</v>
       </c>
       <c r="G54" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.45">
@@ -3632,10 +3452,10 @@
         <v>6</v>
       </c>
       <c r="C55" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -3644,7 +3464,7 @@
         <v>9</v>
       </c>
       <c r="G55" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.45">
@@ -3655,10 +3475,10 @@
         <v>6</v>
       </c>
       <c r="C56" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -3667,7 +3487,7 @@
         <v>9</v>
       </c>
       <c r="G56" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -3705,7 +3525,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -3719,177 +3539,177 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C2" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C4" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E4" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C5" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E5" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E6" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E7" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" t="s">
         <v>88</v>
       </c>
-      <c r="B8" t="s">
-        <v>93</v>
-      </c>
-      <c r="C8" t="s">
-        <v>94</v>
-      </c>
       <c r="D8" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E8" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="F8" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G8" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E9" t="s">
         <v>33</v>
@@ -3898,67 +3718,67 @@
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" t="s">
         <v>129</v>
       </c>
-      <c r="C10" t="s">
-        <v>135</v>
-      </c>
       <c r="D10" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C11" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E11" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F11" t="s">
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
@@ -3967,297 +3787,297 @@
         <v>9</v>
       </c>
       <c r="G12" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B13" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C13" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E13" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="F13" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G13" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E14" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F14" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G14" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B15" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C15" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F15" t="s">
         <v>9</v>
       </c>
       <c r="G15" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E16" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F16" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G16" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B17" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" t="s">
+        <v>225</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" t="s">
         <v>106</v>
-      </c>
-      <c r="C17" t="s">
-        <v>232</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="E17" t="s">
-        <v>50</v>
-      </c>
-      <c r="F17" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E18" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="F18" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G18" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B19" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C19" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F19" t="s">
         <v>9</v>
       </c>
       <c r="G19" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E20" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="F20" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G20" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E21" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="F21" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G21" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E22" t="s">
         <v>33</v>
       </c>
       <c r="F22" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G22" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F23" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G23" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E24" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="F24" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G24" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B25" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C25" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E25" t="s">
         <v>33</v>
@@ -4266,320 +4086,320 @@
         <v>9</v>
       </c>
       <c r="G25" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B26" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E26" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="F26" t="s">
         <v>9</v>
       </c>
       <c r="G26" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B27" t="s">
+        <v>145</v>
+      </c>
+      <c r="C27" t="s">
         <v>151</v>
       </c>
-      <c r="C27" t="s">
-        <v>157</v>
-      </c>
       <c r="D27" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E27" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F27" t="s">
         <v>9</v>
       </c>
       <c r="G27" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B28" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C28" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E28" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="F28" t="s">
         <v>9</v>
       </c>
       <c r="G28" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B29" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C29" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E29" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="F29" t="s">
         <v>9</v>
       </c>
       <c r="G29" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B30" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C30" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E30" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F30" t="s">
         <v>9</v>
       </c>
       <c r="G30" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B31" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C31" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E31" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F31" t="s">
         <v>9</v>
       </c>
       <c r="G31" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C32" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E32" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F32" t="s">
         <v>9</v>
       </c>
       <c r="G32" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B33" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C33" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E33" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="F33" t="s">
         <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B34" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C34" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E34" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="F34" t="s">
         <v>9</v>
       </c>
       <c r="G34" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B35" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C35" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E35" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="F35" t="s">
         <v>9</v>
       </c>
       <c r="G35" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B36" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C36" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E36" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="F36" t="s">
         <v>9</v>
       </c>
       <c r="G36" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B37" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C37" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E37" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F37" t="s">
         <v>9</v>
       </c>
       <c r="G37" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B38" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C38" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E38" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F38" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G38" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C39" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E39" t="s">
         <v>19</v>
@@ -4588,21 +4408,21 @@
         <v>9</v>
       </c>
       <c r="G39" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B40" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C40" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -4611,7 +4431,7 @@
         <v>9</v>
       </c>
       <c r="G40" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -4649,7 +4469,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -4663,16 +4483,16 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B2" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C2" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4681,21 +4501,21 @@
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C3" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4704,21 +4524,21 @@
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B4" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C4" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4727,21 +4547,21 @@
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B5" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C5" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4750,21 +4570,21 @@
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B6" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C6" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -4773,21 +4593,21 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B7" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C7" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -4796,7 +4616,7 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -4830,7 +4650,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -4844,16 +4664,16 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B2" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C2" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4862,21 +4682,21 @@
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4885,21 +4705,21 @@
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B4" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C4" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4908,7 +4728,7 @@
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -4942,7 +4762,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -4956,485 +4776,485 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B2" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C2" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G2" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B3" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C3" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G3" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C4" t="s">
         <v>204</v>
       </c>
-      <c r="B4" t="s">
-        <v>205</v>
-      </c>
-      <c r="C4" t="s">
-        <v>210</v>
-      </c>
       <c r="D4" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G4" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C5" t="s">
         <v>205</v>
       </c>
-      <c r="C5" t="s">
-        <v>211</v>
-      </c>
       <c r="D5" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E5" t="s">
         <v>33</v>
       </c>
       <c r="F5" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G5" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B6" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C6" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F6" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G6" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B7" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C7" t="s">
-        <v>213</v>
+        <v>357</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F7" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G7" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B8" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C8" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F8" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G8" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B9" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C9" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E9" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="F9" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G9" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B10" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C10" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G10" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B11" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C11" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G11" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B12" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C12" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G12" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B13" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C13" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E13" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F13" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G13" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B14" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C14" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G14" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B15" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E15" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="F15" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G15" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C16" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E16" t="s">
         <v>33</v>
       </c>
       <c r="F16" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G16" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C17" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F17" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G17" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C18" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E18" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F18" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G18" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C19" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E19" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F19" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G19" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B20" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E20" t="s">
         <v>33</v>
       </c>
       <c r="F20" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G20" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B21" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C21" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F21" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G21" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B22" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C22" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E22" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F22" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G22" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -5468,7 +5288,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -5482,108 +5302,108 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C2" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C3" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C4" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E4" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" t="s">
         <v>129</v>
       </c>
-      <c r="C5" t="s">
-        <v>135</v>
-      </c>
       <c r="D5" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E5" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C6" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -5592,421 +5412,421 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C7" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E7" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C8" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E8" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C9" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E9" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B10" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C10" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E10" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C11" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E11" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F11" t="s">
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C12" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E12" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="F12" t="s">
         <v>9</v>
       </c>
       <c r="G12" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B13" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C13" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E13" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F13" t="s">
         <v>9</v>
       </c>
       <c r="G13" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B14" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C14" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E14" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F14" t="s">
         <v>9</v>
       </c>
       <c r="G14" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B15" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C15" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E15" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F15" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G15" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C16" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G16" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E17" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="F17" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G17" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E18" t="s">
         <v>33</v>
       </c>
       <c r="F18" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G18" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C19" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F19" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G19" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B20" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E20" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F20" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G20" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B21" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C21" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E21" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F21" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G21" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B22" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E22" t="s">
         <v>33</v>
       </c>
       <c r="F22" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G22" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B23" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C23" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F23" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G23" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B24" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C24" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F24" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G24" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -6040,7 +5860,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -6054,94 +5874,94 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B2" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C2" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E2" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="F2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G2" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G3" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B4" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C4" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G4" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B5" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C5" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G5" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -6175,7 +5995,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -6198,7 +6018,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
@@ -6221,7 +6041,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
@@ -6244,7 +6064,7 @@
         <v>22</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -6264,19 +6084,19 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
+        <v>348</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E5" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="E5" t="s">
-        <v>35</v>
-      </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>355</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
@@ -6287,10 +6107,10 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E6" t="s">
         <v>33</v>
@@ -6299,7 +6119,7 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
@@ -6310,19 +6130,19 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>264</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>59</v>
+        <v>354</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
@@ -6333,19 +6153,19 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/docs/DropDownAccessMethods.xlsx
+++ b/docs/DropDownAccessMethods.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robin\spCoin\SPCOIN-PROJECT-MODULES\spcoin-nextjs-front-end\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{585A375C-497E-499F-8BD3-74F80F38AEB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F71465-E450-4FBE-B3A2-39F872C2135E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="4" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="On chain Methods" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="351">
   <si>
     <t>Panel</t>
   </si>
@@ -144,12 +144,6 @@
     <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getRecipientRateRecord.ts</t>
   </si>
   <si>
-    <t>getRecipientRateRecordList</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getRecipientRateRecordList.ts</t>
-  </si>
-  <si>
     <t>getLowerRecipientRate</t>
   </si>
   <si>
@@ -270,15 +264,9 @@
     <t>Index</t>
   </si>
   <si>
-    <t>getStakingRewards</t>
-  </si>
-  <si>
     <t>Last Update Time, Interest Rate, Quantity</t>
   </si>
   <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getStakingRewards.ts</t>
-  </si>
-  <si>
     <t>totalStakedSPCoins</t>
   </si>
   <si>
@@ -372,12 +360,6 @@
     <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteRecipientAgent.ts</t>
   </si>
   <si>
-    <t>deleteAgentRateBranch</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteAgentRateBranch.ts</t>
-  </si>
-  <si>
     <t>deleteRecipientSponsorships</t>
   </si>
   <si>
@@ -750,12 +732,6 @@
     <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteRecipientRate.ts</t>
   </si>
   <si>
-    <t>deleteRecipientRateBranch</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteRecipientRateBranch.ts</t>
-  </si>
-  <si>
     <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteRecipientTransaction.ts</t>
   </si>
   <si>
@@ -825,15 +801,9 @@
     <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getAgentListSize.ts</t>
   </si>
   <si>
-    <t>getAccountRateRecordList</t>
-  </si>
-  <si>
     <t>Rate Reward List</t>
   </si>
   <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getAccountRateRecordList.ts</t>
-  </si>
-  <si>
     <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getMasterAccountListSize.ts</t>
   </si>
   <si>
@@ -861,9 +831,6 @@
     <t>================================================================ WIP =========================================================================</t>
   </si>
   <si>
-    <t>Auto-generated public getters</t>
-  </si>
-  <si>
     <t>Source: SpCoinDataTypes.sol (line 16)</t>
   </si>
   <si>
@@ -924,194 +891,206 @@
     <t>Source: Security.sol (line 14)</t>
   </si>
   <si>
-    <t>owner()</t>
-  </si>
-  <si>
-    <t>isAccountInserted(address)</t>
-  </si>
-  <si>
-    <t>getInflationRate()</t>
-  </si>
-  <si>
-    <t>setInflationRate(uint256)</t>
-  </si>
-  <si>
-    <t>getLowerRecipientRate()</t>
-  </si>
-  <si>
-    <t>getUpperRecipientRate()</t>
-  </si>
-  <si>
-    <t>getRecipientRateRange()</t>
-  </si>
-  <si>
-    <t>setRecipientRateRange(uint256,uint256)</t>
-  </si>
-  <si>
-    <t>getLowerAgentRate()</t>
-  </si>
-  <si>
-    <t>getUpperAgentRate()</t>
-  </si>
-  <si>
-    <t>getAgentRateRange()</t>
-  </si>
-  <si>
-    <t>setAgentRateRange(uint256,uint256)</t>
-  </si>
-  <si>
-    <t>getInitialTotalSupply()</t>
-  </si>
-  <si>
     <t>Account / sponsor / recipient / agent reads</t>
   </si>
   <si>
     <t>Sources: Account.sol (line 66), Recipient.sol (line 13), RecipientRates.sol (line 54), Agent.sol (line 12), AgentRates.sol (line 37)</t>
   </si>
   <si>
-    <t>getMasterAccountKeys()</t>
-  </si>
-  <si>
-    <t>getMasterAccountKeyAt(uint256)</t>
-  </si>
-  <si>
-    <t>getAccountKeyCount()</t>
-  </si>
-  <si>
-    <t>getAccountCore(address)</t>
-  </si>
-  <si>
-    <t>getAccountLinks(address)</t>
-  </si>
-  <si>
-    <t>getRecipientKeys(address)</t>
-  </si>
-  <si>
-    <t>getAgentKeys(address)</t>
-  </si>
-  <si>
-    <t>getRecipientKeyCount(address)</t>
-  </si>
-  <si>
-    <t>getAgentKeyCount(address)</t>
-  </si>
-  <si>
-    <t>addSponsorRecipient(address,address)</t>
-  </si>
-  <si>
-    <t>getRecipientRecordCore(address,address)</t>
-  </si>
-  <si>
-    <t>getRecipientRateList(address,address)</t>
-  </si>
-  <si>
-    <t>getRecipientRateRecordCore(address,address,uint256)</t>
-  </si>
-  <si>
-    <t>addRecipientAgent(address,address,uint256,address)</t>
-  </si>
-  <si>
-    <t>getRecipientRateAgentList(address,address,uint256)</t>
-  </si>
-  <si>
-    <t>getAgentTotalRecipient(address,address,uint256,address)</t>
-  </si>
-  <si>
-    <t>getAgentRateList(address,address,uint256,address)</t>
-  </si>
-  <si>
-    <t>getAgentRateRecordCore(address,address,uint256,address,uint256)</t>
-  </si>
-  <si>
     <t>Rewards / staking</t>
   </si>
   <si>
     <t>Sources: StakingManager.sol (line 21), RewardsManager.sol (line 65)</t>
   </si>
   <si>
-    <t>depositStakingRewards(uint,address,address,uint,address,uint,uint)</t>
-  </si>
-  <si>
-    <t>getAccountRewardTotals(address)</t>
-  </si>
-  <si>
-    <t>updateAccountStakingRewards(address)</t>
-  </si>
-  <si>
-    <t>updateSponsorAccountRewards(address)</t>
-  </si>
-  <si>
-    <t>updateAgentAccountRewards(address)</t>
-  </si>
-  <si>
-    <t>updateRecipietAccountRewards(address)</t>
-  </si>
-  <si>
     <t>Transaction methods</t>
   </si>
   <si>
     <t>Source: Transactions.sol (line 9)</t>
   </si>
   <si>
-    <t>addSponsorship(address,uint,address,uint,string,string)</t>
-  </si>
-  <si>
-    <t>addRecipientRateTransaction(address,address,uint,string,string)</t>
-  </si>
-  <si>
-    <t>addAgentTransaction(address,address,uint,address,uint,string,string)</t>
-  </si>
-  <si>
-    <t>backDateTransactionDate(address,address,uint256,address,uint256,uint256,uint256)</t>
-  </si>
-  <si>
-    <t>getAgentRateTransactionCount(address,address,uint256,address,uint256)</t>
-  </si>
-  <si>
-    <t>getRecipientRateTransactionCount(address,address,uint256)</t>
-  </si>
-  <si>
-    <t>getAgentRateTransactionAt(address,address,uint256,address,uint256,uint256)</t>
-  </si>
-  <si>
     <t>Delete / unsubscribe</t>
   </si>
   <si>
     <t>Source: UnSubscribe.sol (line 26)</t>
   </si>
   <si>
-    <t>deleteSponsor(address)</t>
-  </si>
-  <si>
-    <t>deleteSponsorRecipient(address,address)</t>
-  </si>
-  <si>
-    <t>deleteRecipientRateBranch(address,address,uint256)</t>
-  </si>
-  <si>
-    <t>deleteRecipientAgent(address,address,uint256,address)</t>
-  </si>
-  <si>
-    <t>deleteAgentRateBranch(address,address,uint256,address,uint256)</t>
-  </si>
-  <si>
-    <t>unSponsorRecipient(address)</t>
-  </si>
-  <si>
-    <t>delRecipient(address,address)</t>
-  </si>
-  <si>
-    <t>deleteAccountRecord(address)</t>
-  </si>
-  <si>
     <t>On Chain Methodss</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> deleteRecipient(address,address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> deleteRecipientAgent(address,address,uint256,address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> deleteAccountRecord(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> addSponsorship(address,uint256,address,uint256,string,string)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> addRecipientRateTransaction(address,address,uint256,string,string)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> addAgentTransaction(address,address,uint256,address,uint256,string,string)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> backDateTransactionDate(address,address,uint256,address,uint256,uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAgentRateTransactionCount(address,address,uint256,address,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getRecipientRateTransactionCount(address,address,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  getAgentRateTransactionAt(address,address,uint256,address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> calculateStakingRewards(uint256,uint256,uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAccountRewardTotals(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> updateAccountStakingRewards(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> updateSponsorAccountRewards(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> updateAgentAccountRewards(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> updateRecipientAccountRewards(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getMasterAccountKeyAt(uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAccountKeyCount()</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAccountCore(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAccountLinks(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getRecipientKeys(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAgentKeys(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getRecipientKeyCount(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAgentKeyCount(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> addSponsorRecipient(address,address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getRecipientRecordCore(address,address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getRecipientRateList(address,address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getRecipientRateTransactionCore(address,address,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> addRecipientAgent(address,address,uint256,address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getRecipientRateAgentList(address,address,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAgentTotalRecipient(address,address,uint256,address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAgentRateList(address,address,uint256,address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAgentRateTransactionCore(address,address,uint256,address,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> owner()</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> isAccountInserted(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getInflationRate()</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> setInflationRate(uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getRecipientRateRange()</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> setRecipientRateRange(uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAgentRateRange()</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> setAgentRateRange(uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getInitialTotalSupply()</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getMasterAccountKeys()</t>
+  </si>
+  <si>
+    <t>getAccountRateTransactionList</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getAccountRateTransactionList.ts</t>
+  </si>
+  <si>
+    <t>getRecipientRateTransaction</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getRecipientRateTransaction.ts</t>
+  </si>
+  <si>
+    <t>getRecipientRateTransactionList</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getRecipientRateTransactionList.ts</t>
+  </si>
+  <si>
+    <t>calculateStakingRewards</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/calculateStakingRewards.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> deleteRecipientRate(address,address,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> deleteAgentRate(address,address,uint256,address,uint256)</t>
+  </si>
+  <si>
+    <t>deleteAgentRate</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/deleteAgentRate.ts</t>
+  </si>
+  <si>
+    <t>deleteRecipientRate</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1148,8 +1127,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1186,6 +1170,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1199,7 +1189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1216,21 +1206,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1567,616 +1553,393 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:E118"/>
+  <dimension ref="A1:A77"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="103.73046875" customWidth="1"/>
-    <col min="4" max="4" width="12" style="4" customWidth="1"/>
-    <col min="5" max="5" width="72" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="7" width="96" customWidth="1"/>
+    <col min="1" max="1" width="99.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="72" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="96" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:5" s="11" customFormat="1" ht="23.25" x14ac:dyDescent="0.7">
-      <c r="D1" s="12"/>
-      <c r="E1" s="13" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="2" spans="3:5" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="C2" s="8" t="s">
+    <row r="1" spans="1:1" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="A1" s="9" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
+      <c r="A2" s="10" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A3" s="8" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A5" s="8" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A6" s="8" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A7" s="8" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A8" s="8" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A9" s="8" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A10" s="8" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A11" s="8" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A12" s="8" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="3" spans="3:5" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="C3" s="14" t="s">
+    <row r="13" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
+      <c r="A13" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="D3" s="5"/>
-    </row>
-    <row r="4" spans="3:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C4" s="10" t="s">
+    </row>
+    <row r="14" spans="1:1" ht="20.350000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="D4" s="5"/>
-    </row>
-    <row r="5" spans="3:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C5" s="10" t="s">
+    </row>
+    <row r="15" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A15" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="D5" s="5"/>
-    </row>
-    <row r="6" spans="3:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C6" s="10" t="s">
+    </row>
+    <row r="16" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A16" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="D6" s="5"/>
-    </row>
-    <row r="7" spans="3:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C7" s="10" t="s">
+    </row>
+    <row r="17" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A17" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="D7" s="5"/>
-    </row>
-    <row r="8" spans="3:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C8" s="10" t="s">
+    </row>
+    <row r="18" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A18" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="3:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C9" s="10" t="s">
+    </row>
+    <row r="19" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A19" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="D9" s="5"/>
-    </row>
-    <row r="10" spans="3:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C10" s="10" t="s">
+    </row>
+    <row r="20" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
+      <c r="A20" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" spans="3:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C11" s="10" t="s">
+    </row>
+    <row r="21" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
+      <c r="A21" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12" spans="3:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C12" s="10" t="s">
+    </row>
+    <row r="22" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="11" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="11" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="11" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="11" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="11" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="11" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="11" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="11" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="11" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
+      <c r="A31" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13" spans="3:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C13" s="10" t="s">
+    </row>
+    <row r="32" spans="1:1" ht="37.5" x14ac:dyDescent="0.45">
+      <c r="A32" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="D13" s="5"/>
-    </row>
-    <row r="14" spans="3:5" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="C14" s="8" t="s">
+    </row>
+    <row r="33" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="11" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="11" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="11" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="11" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="11" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="11" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="11" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="11" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="11" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="11" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="11" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="11" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="11" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="11" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="11" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="11" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="11" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
+      <c r="A51" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="3:5" ht="20.350000000000001" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C15" s="14" t="s">
+    </row>
+    <row r="52" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
+      <c r="A52" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="D15" s="5"/>
-    </row>
-    <row r="16" spans="3:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C16" s="10" t="s">
+    </row>
+    <row r="53" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="11" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="11" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="11" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="11" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="11" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
+      <c r="A59" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C17" s="10" t="s">
+    </row>
+    <row r="60" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
+      <c r="A60" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="D17" s="5"/>
-    </row>
-    <row r="18" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C18" s="10" t="s">
+    </row>
+    <row r="61" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="11" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="11" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" s="11" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" s="11" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" s="11" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" s="11" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" s="11" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
+      <c r="A68" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="D18" s="5"/>
-    </row>
-    <row r="19" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C19" s="10" t="s">
+    </row>
+    <row r="69" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
+      <c r="A69" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="D19" s="5"/>
-    </row>
-    <row r="20" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C20" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="3:4" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="C21" s="8" t="s">
+    </row>
+    <row r="70" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="D21" s="5"/>
-    </row>
-    <row r="22" spans="3:4" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="C22" s="14" t="s">
+    </row>
+    <row r="71" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" s="11" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="D22" s="5"/>
-    </row>
-    <row r="23" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C23" s="10" t="s">
+    </row>
+    <row r="73" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" s="11" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="D23" s="5"/>
-    </row>
-    <row r="24" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C24" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="D24" s="5"/>
-    </row>
-    <row r="25" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C25" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="D25" s="5"/>
-    </row>
-    <row r="26" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C26" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="D26" s="5"/>
-    </row>
-    <row r="27" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C27" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="D27" s="5"/>
-    </row>
-    <row r="28" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C28" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="D28" s="5"/>
-    </row>
-    <row r="29" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C29" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="D29" s="5"/>
-    </row>
-    <row r="30" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C30" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="D30" s="5"/>
-    </row>
-    <row r="31" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C31" s="10" t="s">
-        <v>305</v>
-      </c>
-      <c r="D31" s="5"/>
-    </row>
-    <row r="32" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C32" s="10" t="s">
-        <v>306</v>
-      </c>
-      <c r="D32" s="5"/>
-    </row>
-    <row r="33" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C33" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="D33" s="5"/>
-    </row>
-    <row r="34" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C34" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="D34" s="5"/>
-    </row>
-    <row r="35" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C35" s="10" t="s">
-        <v>309</v>
-      </c>
-      <c r="D35" s="5"/>
-    </row>
-    <row r="36" spans="3:4" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="C36" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="D36" s="5"/>
-    </row>
-    <row r="37" spans="3:4" ht="37.5" x14ac:dyDescent="0.45">
-      <c r="C37" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="D37" s="5"/>
-    </row>
-    <row r="38" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C38" s="10" t="s">
-        <v>312</v>
-      </c>
-      <c r="D38" s="5"/>
-    </row>
-    <row r="39" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C39" s="10" t="s">
-        <v>313</v>
-      </c>
-      <c r="D39" s="5"/>
-    </row>
-    <row r="40" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C40" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="D40" s="5"/>
-    </row>
-    <row r="41" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C41" s="10" t="s">
-        <v>315</v>
-      </c>
-      <c r="D41" s="5"/>
-    </row>
-    <row r="42" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C42" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="D42" s="5"/>
-    </row>
-    <row r="43" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C43" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="D43" s="5"/>
-    </row>
-    <row r="44" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C44" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="D44" s="5"/>
-    </row>
-    <row r="45" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C45" s="10" t="s">
-        <v>319</v>
-      </c>
-      <c r="D45" s="5"/>
-    </row>
-    <row r="46" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C46" s="10" t="s">
-        <v>320</v>
-      </c>
-      <c r="D46" s="5"/>
-    </row>
-    <row r="47" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C47" s="10" t="s">
-        <v>321</v>
-      </c>
-      <c r="D47" s="5"/>
-    </row>
-    <row r="48" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C48" s="10" t="s">
-        <v>322</v>
-      </c>
-      <c r="D48" s="5"/>
-    </row>
-    <row r="49" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C49" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="D49" s="5"/>
-    </row>
-    <row r="50" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C50" s="10" t="s">
-        <v>324</v>
-      </c>
-      <c r="D50" s="5"/>
-    </row>
-    <row r="51" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C51" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="D51" s="5"/>
-    </row>
-    <row r="52" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C52" s="10" t="s">
-        <v>326</v>
-      </c>
-      <c r="D52" s="5"/>
-    </row>
-    <row r="53" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C53" s="10" t="s">
-        <v>327</v>
-      </c>
-      <c r="D53" s="5"/>
-    </row>
-    <row r="54" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C54" s="10" t="s">
-        <v>328</v>
-      </c>
-      <c r="D54" s="5"/>
-    </row>
-    <row r="55" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C55" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="D55" s="5"/>
-    </row>
-    <row r="56" spans="3:4" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="C56" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="D56" s="5"/>
-    </row>
-    <row r="57" spans="3:4" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="C57" s="14" t="s">
-        <v>331</v>
-      </c>
-      <c r="D57" s="5"/>
-    </row>
-    <row r="58" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C58" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="D58" s="5"/>
-    </row>
-    <row r="59" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C59" s="10" t="s">
-        <v>333</v>
-      </c>
-      <c r="D59" s="5"/>
-    </row>
-    <row r="60" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C60" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="D60" s="5"/>
-    </row>
-    <row r="61" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C61" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="D61" s="5"/>
-    </row>
-    <row r="62" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C62" s="10" t="s">
-        <v>336</v>
-      </c>
-      <c r="D62" s="5"/>
-    </row>
-    <row r="63" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C63" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="D63" s="5"/>
-    </row>
-    <row r="64" spans="3:4" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="C64" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="D64" s="5"/>
-    </row>
-    <row r="65" spans="3:4" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="C65" s="9" t="s">
-        <v>339</v>
-      </c>
-      <c r="D65" s="5"/>
-    </row>
-    <row r="66" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C66" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="D66" s="5"/>
-    </row>
-    <row r="67" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C67" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="D67" s="5"/>
-    </row>
-    <row r="68" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C68" s="10" t="s">
-        <v>342</v>
-      </c>
-      <c r="D68" s="5"/>
-    </row>
-    <row r="69" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C69" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="D69" s="5"/>
-    </row>
-    <row r="70" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C70" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="D70" s="5"/>
-    </row>
-    <row r="71" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C71" s="10" t="s">
-        <v>345</v>
-      </c>
-      <c r="D71" s="5"/>
-    </row>
-    <row r="72" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C72" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="D72" s="5"/>
-    </row>
-    <row r="73" spans="3:4" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="C73" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="D73" s="5"/>
-    </row>
-    <row r="74" spans="3:4" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="C74" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="D74" s="5"/>
-    </row>
-    <row r="75" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C75" s="10" t="s">
-        <v>349</v>
-      </c>
-      <c r="D75" s="5"/>
-    </row>
-    <row r="76" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C76" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="D76" s="5"/>
-    </row>
-    <row r="77" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C77" s="10" t="s">
-        <v>351</v>
-      </c>
-      <c r="D77" s="5"/>
-    </row>
-    <row r="78" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C78" s="10" t="s">
-        <v>352</v>
-      </c>
-      <c r="D78" s="5"/>
-    </row>
-    <row r="79" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C79" s="10" t="s">
-        <v>353</v>
-      </c>
-      <c r="D79" s="5"/>
-    </row>
-    <row r="80" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C80" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="D80" s="5"/>
-    </row>
-    <row r="81" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C81" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="D81" s="5"/>
-    </row>
-    <row r="82" spans="3:4" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="C82" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="D82" s="5"/>
-    </row>
-    <row r="83" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D83" s="5"/>
-    </row>
-    <row r="84" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D84" s="5"/>
-    </row>
-    <row r="85" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D85" s="5"/>
-    </row>
-    <row r="86" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D86" s="5"/>
-    </row>
-    <row r="87" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D87" s="5"/>
-    </row>
-    <row r="88" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D88" s="5"/>
-    </row>
-    <row r="89" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D89" s="5"/>
-    </row>
-    <row r="90" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D90" s="5"/>
-    </row>
-    <row r="91" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D91" s="5"/>
-    </row>
-    <row r="92" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D92" s="5"/>
-    </row>
-    <row r="93" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D93" s="5"/>
-    </row>
-    <row r="94" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D94" s="5"/>
-    </row>
-    <row r="95" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D95" s="5"/>
-    </row>
-    <row r="96" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D96" s="5"/>
-    </row>
-    <row r="97" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D97" s="5"/>
-    </row>
-    <row r="98" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D98" s="5"/>
-    </row>
-    <row r="99" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D99" s="5"/>
-    </row>
-    <row r="100" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D100" s="5"/>
-    </row>
-    <row r="101" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D101" s="5"/>
-    </row>
-    <row r="102" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D102" s="5"/>
-    </row>
-    <row r="103" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D103" s="5"/>
-    </row>
-    <row r="104" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D104" s="5"/>
-    </row>
-    <row r="105" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D105" s="5"/>
-    </row>
-    <row r="106" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D106" s="5"/>
-    </row>
-    <row r="107" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D107" s="5"/>
-    </row>
-    <row r="108" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D108" s="5"/>
-    </row>
-    <row r="109" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D109" s="5"/>
-    </row>
-    <row r="110" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D110" s="5"/>
-    </row>
-    <row r="111" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D111" s="5"/>
-    </row>
-    <row r="112" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D112" s="5"/>
-    </row>
-    <row r="113" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D113" s="5"/>
-    </row>
-    <row r="114" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D114" s="5"/>
-    </row>
-    <row r="115" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D115" s="5"/>
-    </row>
-    <row r="116" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D116" s="5"/>
-    </row>
-    <row r="117" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D117" s="5"/>
-    </row>
-    <row r="118" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D118" s="5"/>
+    </row>
+    <row r="75" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A75" s="8"/>
+    </row>
+    <row r="76" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A76" s="8"/>
+    </row>
+    <row r="77" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A77" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2208,7 +1971,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -2222,85 +1985,85 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="E2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G2" t="s">
         <v>93</v>
-      </c>
-      <c r="C2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="E2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E5" t="s">
         <v>33</v>
@@ -2309,21 +2072,21 @@
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E6" t="s">
         <v>35</v>
@@ -2332,53 +2095,53 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
-        <v>113</v>
+        <v>348</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>114</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -2415,7 +2178,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -2426,71 +2189,71 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="F2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G2" t="s">
         <v>93</v>
-      </c>
-      <c r="C2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="F2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="F3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B4" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="F4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G4" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2527,7 +2290,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -2538,71 +2301,71 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D2" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C4" t="s">
         <v>151</v>
       </c>
-      <c r="C4" t="s">
-        <v>157</v>
-      </c>
       <c r="D4" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -2636,7 +2399,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -2659,7 +2422,7 @@
         <v>11</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -2679,19 +2442,19 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>264</v>
+        <v>338</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E3" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="F3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G3" t="s">
-        <v>266</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
@@ -2705,7 +2468,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -2728,13 +2491,13 @@
         <v>24</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E5" t="s">
         <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G5" t="s">
         <v>26</v>
@@ -2751,13 +2514,13 @@
         <v>27</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
       </c>
       <c r="F6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G6" t="s">
         <v>29</v>
@@ -2771,19 +2534,19 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
@@ -2794,10 +2557,10 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -2806,7 +2569,7 @@
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
@@ -2817,19 +2580,19 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
@@ -2840,19 +2603,19 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
@@ -2863,19 +2626,19 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E11" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F11" t="s">
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
@@ -2886,19 +2649,19 @@
         <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F13" t="s">
         <v>9</v>
       </c>
       <c r="G13" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
@@ -2909,10 +2672,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -2921,7 +2684,7 @@
         <v>9</v>
       </c>
       <c r="G14" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
@@ -2932,10 +2695,10 @@
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -2944,12 +2707,12 @@
         <v>9</v>
       </c>
       <c r="G15" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="7" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
@@ -2963,7 +2726,7 @@
         <v>22</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
@@ -2983,19 +2746,19 @@
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E21" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="F21" t="s">
         <v>9</v>
       </c>
       <c r="G21" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
@@ -3006,24 +2769,24 @@
         <v>6</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E22" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="F22" t="s">
         <v>9</v>
       </c>
       <c r="G22" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="7" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
@@ -3034,19 +2797,19 @@
         <v>6</v>
       </c>
       <c r="C29" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E29" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F29" t="s">
         <v>9</v>
       </c>
       <c r="G29" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
@@ -3057,19 +2820,19 @@
         <v>6</v>
       </c>
       <c r="C30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="E30" t="s">
+        <v>69</v>
+      </c>
+      <c r="F30" t="s">
+        <v>9</v>
+      </c>
+      <c r="G30" t="s">
         <v>70</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="E30" t="s">
-        <v>71</v>
-      </c>
-      <c r="F30" t="s">
-        <v>9</v>
-      </c>
-      <c r="G30" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
@@ -3080,19 +2843,19 @@
         <v>6</v>
       </c>
       <c r="C31" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E31" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F31" t="s">
         <v>9</v>
       </c>
       <c r="G31" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
@@ -3106,7 +2869,7 @@
         <v>7</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -3126,10 +2889,10 @@
         <v>6</v>
       </c>
       <c r="C33" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -3138,7 +2901,7 @@
         <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
@@ -3149,10 +2912,10 @@
         <v>6</v>
       </c>
       <c r="C34" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -3161,7 +2924,7 @@
         <v>9</v>
       </c>
       <c r="G34" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
@@ -3172,10 +2935,10 @@
         <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -3184,7 +2947,7 @@
         <v>9</v>
       </c>
       <c r="G35" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
@@ -3198,13 +2961,13 @@
         <v>30</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E36" t="s">
         <v>31</v>
       </c>
       <c r="F36" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G36" t="s">
         <v>32</v>
@@ -3218,10 +2981,10 @@
         <v>6</v>
       </c>
       <c r="C37" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E37" t="s">
         <v>19</v>
@@ -3230,7 +2993,7 @@
         <v>9</v>
       </c>
       <c r="G37" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
@@ -3241,10 +3004,10 @@
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E38" t="s">
         <v>19</v>
@@ -3253,7 +3016,7 @@
         <v>9</v>
       </c>
       <c r="G38" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
@@ -3264,10 +3027,10 @@
         <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E39" t="s">
         <v>35</v>
@@ -3276,7 +3039,7 @@
         <v>9</v>
       </c>
       <c r="G39" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
@@ -3287,10 +3050,10 @@
         <v>6</v>
       </c>
       <c r="C40" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E40" t="s">
         <v>33</v>
@@ -3299,7 +3062,7 @@
         <v>9</v>
       </c>
       <c r="G40" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
@@ -3310,10 +3073,10 @@
         <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -3322,7 +3085,7 @@
         <v>9</v>
       </c>
       <c r="G41" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
@@ -3333,10 +3096,10 @@
         <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>34</v>
+        <v>340</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E42" t="s">
         <v>35</v>
@@ -3345,7 +3108,7 @@
         <v>9</v>
       </c>
       <c r="G42" t="s">
-        <v>36</v>
+        <v>341</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
@@ -3356,10 +3119,10 @@
         <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>37</v>
+        <v>342</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E43" t="s">
         <v>33</v>
@@ -3368,7 +3131,7 @@
         <v>9</v>
       </c>
       <c r="G43" t="s">
-        <v>38</v>
+        <v>343</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
@@ -3379,10 +3142,10 @@
         <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E44" t="s">
         <v>35</v>
@@ -3391,7 +3154,7 @@
         <v>9</v>
       </c>
       <c r="G44" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
@@ -3402,10 +3165,10 @@
         <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E45" t="s">
         <v>33</v>
@@ -3414,7 +3177,7 @@
         <v>9</v>
       </c>
       <c r="G45" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.45">
@@ -3425,19 +3188,19 @@
         <v>6</v>
       </c>
       <c r="C46" t="s">
+        <v>45</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="E46" t="s">
+        <v>46</v>
+      </c>
+      <c r="F46" t="s">
+        <v>9</v>
+      </c>
+      <c r="G46" t="s">
         <v>47</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="E46" t="s">
-        <v>48</v>
-      </c>
-      <c r="F46" t="s">
-        <v>9</v>
-      </c>
-      <c r="G46" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.45">
@@ -3451,7 +3214,7 @@
         <v>17</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -3471,19 +3234,19 @@
         <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>79</v>
+        <v>344</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E48" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F48" t="s">
         <v>9</v>
       </c>
       <c r="G48" t="s">
-        <v>81</v>
+        <v>345</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.45">
@@ -3494,10 +3257,10 @@
         <v>6</v>
       </c>
       <c r="C49" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -3506,7 +3269,7 @@
         <v>9</v>
       </c>
       <c r="G49" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.45">
@@ -3517,10 +3280,10 @@
         <v>6</v>
       </c>
       <c r="C50" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -3529,7 +3292,7 @@
         <v>9</v>
       </c>
       <c r="G50" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.45">
@@ -3540,10 +3303,10 @@
         <v>6</v>
       </c>
       <c r="C51" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -3552,7 +3315,7 @@
         <v>9</v>
       </c>
       <c r="G51" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.45">
@@ -3563,10 +3326,10 @@
         <v>6</v>
       </c>
       <c r="C52" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E52" t="s">
         <v>19</v>
@@ -3575,7 +3338,7 @@
         <v>9</v>
       </c>
       <c r="G52" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.45">
@@ -3586,19 +3349,19 @@
         <v>6</v>
       </c>
       <c r="C53" t="s">
+        <v>71</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E53" t="s">
+        <v>72</v>
+      </c>
+      <c r="F53" t="s">
+        <v>9</v>
+      </c>
+      <c r="G53" t="s">
         <v>73</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="E53" t="s">
-        <v>74</v>
-      </c>
-      <c r="F53" t="s">
-        <v>9</v>
-      </c>
-      <c r="G53" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.45">
@@ -3609,10 +3372,10 @@
         <v>6</v>
       </c>
       <c r="C54" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -3621,7 +3384,7 @@
         <v>9</v>
       </c>
       <c r="G54" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.45">
@@ -3632,10 +3395,10 @@
         <v>6</v>
       </c>
       <c r="C55" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -3644,7 +3407,7 @@
         <v>9</v>
       </c>
       <c r="G55" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.45">
@@ -3655,10 +3418,10 @@
         <v>6</v>
       </c>
       <c r="C56" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -3667,7 +3430,7 @@
         <v>9</v>
       </c>
       <c r="G56" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -3705,7 +3468,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -3719,177 +3482,177 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B4" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C4" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E4" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C5" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E5" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="E7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" t="s">
         <v>88</v>
-      </c>
-      <c r="B7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="E7" t="s">
-        <v>91</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="E8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F8" t="s">
+        <v>92</v>
+      </c>
+      <c r="G8" t="s">
         <v>93</v>
-      </c>
-      <c r="C8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="E8" t="s">
-        <v>95</v>
-      </c>
-      <c r="F8" t="s">
-        <v>96</v>
-      </c>
-      <c r="G8" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E9" t="s">
         <v>33</v>
@@ -3898,67 +3661,67 @@
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" t="s">
         <v>129</v>
       </c>
-      <c r="C10" t="s">
-        <v>135</v>
-      </c>
       <c r="D10" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C11" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E11" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F11" t="s">
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
@@ -3967,159 +3730,159 @@
         <v>9</v>
       </c>
       <c r="G12" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C13" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E13" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="F13" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G13" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E14" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F14" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G14" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B15" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C15" t="s">
-        <v>113</v>
+        <v>348</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F15" t="s">
         <v>9</v>
       </c>
       <c r="G15" t="s">
-        <v>114</v>
+        <v>349</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F16" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G16" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C17" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F17" t="s">
         <v>9</v>
       </c>
       <c r="G17" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E18" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="F18" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G18" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B19" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C19" t="s">
-        <v>239</v>
+        <v>350</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E19" t="s">
         <v>35</v>
@@ -4128,136 +3891,136 @@
         <v>9</v>
       </c>
       <c r="G19" t="s">
-        <v>240</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
+        <v>227</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="E20" t="s">
+        <v>115</v>
+      </c>
+      <c r="F20" t="s">
+        <v>100</v>
+      </c>
+      <c r="G20" t="s">
         <v>233</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="E20" t="s">
-        <v>121</v>
-      </c>
-      <c r="F20" t="s">
-        <v>104</v>
-      </c>
-      <c r="G20" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E21" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="F21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G21" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E22" t="s">
         <v>33</v>
       </c>
       <c r="F22" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G22" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E23" t="s">
         <v>35</v>
       </c>
       <c r="F23" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G23" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E24" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F24" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G24" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B25" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C25" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E25" t="s">
         <v>33</v>
@@ -4266,320 +4029,320 @@
         <v>9</v>
       </c>
       <c r="G25" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B26" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E26" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F26" t="s">
         <v>9</v>
       </c>
       <c r="G26" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B27" t="s">
+        <v>145</v>
+      </c>
+      <c r="C27" t="s">
         <v>151</v>
       </c>
-      <c r="C27" t="s">
-        <v>157</v>
-      </c>
       <c r="D27" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E27" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F27" t="s">
         <v>9</v>
       </c>
       <c r="G27" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B28" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C28" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E28" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="F28" t="s">
         <v>9</v>
       </c>
       <c r="G28" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B29" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C29" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E29" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="F29" t="s">
         <v>9</v>
       </c>
       <c r="G29" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B30" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C30" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E30" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F30" t="s">
         <v>9</v>
       </c>
       <c r="G30" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B31" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C31" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E31" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F31" t="s">
         <v>9</v>
       </c>
       <c r="G31" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C32" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E32" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F32" t="s">
         <v>9</v>
       </c>
       <c r="G32" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B33" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C33" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E33" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="F33" t="s">
         <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B34" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C34" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E34" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="F34" t="s">
         <v>9</v>
       </c>
       <c r="G34" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B35" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C35" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E35" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="F35" t="s">
         <v>9</v>
       </c>
       <c r="G35" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B36" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C36" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E36" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="F36" t="s">
         <v>9</v>
       </c>
       <c r="G36" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B37" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C37" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E37" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F37" t="s">
         <v>9</v>
       </c>
       <c r="G37" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B38" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C38" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E38" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F38" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G38" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C39" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E39" t="s">
         <v>19</v>
@@ -4588,21 +4351,21 @@
         <v>9</v>
       </c>
       <c r="G39" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B40" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C40" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -4611,7 +4374,7 @@
         <v>9</v>
       </c>
       <c r="G40" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -4649,7 +4412,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -4663,16 +4426,16 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B2" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C2" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4681,21 +4444,21 @@
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C3" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4704,21 +4467,21 @@
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B4" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C4" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4727,21 +4490,21 @@
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B5" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C5" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4750,21 +4513,21 @@
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B6" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C6" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -4773,21 +4536,21 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B7" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C7" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -4796,7 +4559,7 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -4830,7 +4593,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -4844,16 +4607,16 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B2" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C2" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4862,21 +4625,21 @@
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4885,21 +4648,21 @@
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B4" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C4" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4908,7 +4671,7 @@
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -4942,7 +4705,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -4956,485 +4719,485 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B2" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C2" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G2" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B3" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C3" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G3" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C4" t="s">
         <v>204</v>
       </c>
-      <c r="B4" t="s">
-        <v>205</v>
-      </c>
-      <c r="C4" t="s">
-        <v>210</v>
-      </c>
       <c r="D4" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G4" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C5" t="s">
         <v>205</v>
       </c>
-      <c r="C5" t="s">
-        <v>211</v>
-      </c>
       <c r="D5" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E5" t="s">
         <v>33</v>
       </c>
       <c r="F5" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G5" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B6" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C6" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E6" t="s">
         <v>35</v>
       </c>
       <c r="F6" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G6" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B7" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C7" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F7" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G7" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B8" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C8" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F8" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G8" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B9" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C9" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E9" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="F9" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G9" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B10" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C10" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G10" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B11" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C11" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G11" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B12" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C12" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G12" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B13" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C13" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E13" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="F13" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G13" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B14" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C14" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G14" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B15" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E15" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F15" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G15" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C16" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E16" t="s">
         <v>33</v>
       </c>
       <c r="F16" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G16" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C17" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E17" t="s">
         <v>35</v>
       </c>
       <c r="F17" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G17" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C18" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F18" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G18" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C19" t="s">
-        <v>113</v>
+        <v>348</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E19" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F19" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G19" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B20" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E20" t="s">
         <v>33</v>
       </c>
       <c r="F20" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G20" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B21" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C21" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E21" t="s">
         <v>35</v>
       </c>
       <c r="F21" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G21" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B22" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C22" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E22" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F22" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G22" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -5468,7 +5231,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -5482,108 +5245,108 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C2" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C3" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B4" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C4" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E4" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" t="s">
         <v>129</v>
       </c>
-      <c r="C5" t="s">
-        <v>135</v>
-      </c>
       <c r="D5" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E5" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C6" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -5592,421 +5355,421 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C7" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E7" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C8" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E8" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C9" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E9" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C10" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E10" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C11" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E11" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F11" t="s">
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C12" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E12" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="F12" t="s">
         <v>9</v>
       </c>
       <c r="G12" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C13" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E13" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F13" t="s">
         <v>9</v>
       </c>
       <c r="G13" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C14" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E14" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F14" t="s">
         <v>9</v>
       </c>
       <c r="G14" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B15" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C15" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E15" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="F15" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G15" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C16" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G16" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E17" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F17" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G17" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E18" t="s">
         <v>33</v>
       </c>
       <c r="F18" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G18" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C19" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E19" t="s">
         <v>35</v>
       </c>
       <c r="F19" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G19" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B20" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F20" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G20" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B21" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C21" t="s">
-        <v>113</v>
+        <v>348</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E21" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F21" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G21" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B22" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E22" t="s">
         <v>33</v>
       </c>
       <c r="F22" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G22" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B23" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C23" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E23" t="s">
         <v>35</v>
       </c>
       <c r="F23" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G23" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B24" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C24" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F24" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G24" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -6040,7 +5803,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -6054,94 +5817,94 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B2" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C2" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E2" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="F2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G2" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B3" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C3" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G3" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B4" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C4" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G4" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B5" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C5" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G5" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -6175,7 +5938,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -6198,7 +5961,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
@@ -6221,7 +5984,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
@@ -6244,7 +6007,7 @@
         <v>22</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -6267,7 +6030,7 @@
         <v>34</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E5" t="s">
         <v>35</v>
@@ -6287,10 +6050,10 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E6" t="s">
         <v>33</v>
@@ -6299,7 +6062,7 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
@@ -6310,19 +6073,19 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="E7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" t="s">
         <v>57</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="E7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
@@ -6333,19 +6096,19 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/docs/DropDownAccessMethods.xlsx
+++ b/docs/DropDownAccessMethods.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robin\spCoin\SPCOIN-PROJECT-MODULES\spcoin-nextjs-front-end\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F71465-E450-4FBE-B3A2-39F872C2135E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A2732F-00FB-45AA-8846-993DB284AC81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="4" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="13403" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="On chain Methods" sheetId="1" r:id="rId1"/>
@@ -123,15 +123,9 @@
     <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getAccountRewardTransactionRecord.ts</t>
   </si>
   <si>
-    <t>getRateTransactionList</t>
-  </si>
-  <si>
     <t>Reward Rate Row List</t>
   </si>
   <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getRateTransactionList.ts</t>
-  </si>
-  <si>
     <t>Sponsor Key, Recipient Key</t>
   </si>
   <si>
@@ -213,24 +207,6 @@
     <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getAgentTotalRecipient.ts</t>
   </si>
   <si>
-    <t>getRecipientRateTransactionCount</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getRecipientRateTransactionCount.ts</t>
-  </si>
-  <si>
-    <t>getAgentRateTransactionCount</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getAgentRateTransactionCount.ts</t>
-  </si>
-  <si>
-    <t>getAgentRateTransactionList</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getAgentRateTransactionList.ts</t>
-  </si>
-  <si>
     <t>getAgentRecord</t>
   </si>
   <si>
@@ -291,15 +267,9 @@
     <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/addRecipient.ts</t>
   </si>
   <si>
-    <t>addRecipientRateTransaction</t>
-  </si>
-  <si>
     <t>Sponsor Key, Recipient Key, Recipient Rate Key, Transaction Quantity</t>
   </si>
   <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/addRecipientRateTransaction.ts</t>
-  </si>
-  <si>
     <t>Todo / Offchain Utility</t>
   </si>
   <si>
@@ -657,9 +627,6 @@
     <t>external_serializeAgentRateRecordStr</t>
   </si>
   <si>
-    <t>external_getSerializedRateTransactionList</t>
-  </si>
-  <si>
     <t>Read Admin</t>
   </si>
   <si>
@@ -822,9 +789,6 @@
     <t>getMasterAccountCount</t>
   </si>
   <si>
-    <t>getAgentRateTransaction</t>
-  </si>
-  <si>
     <t>================================================================ TODO =========================================================================</t>
   </si>
   <si>
@@ -930,24 +894,12 @@
     <t xml:space="preserve"> addSponsorship(address,uint256,address,uint256,string,string)</t>
   </si>
   <si>
-    <t xml:space="preserve"> addRecipientRateTransaction(address,address,uint256,string,string)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> addAgentTransaction(address,address,uint256,address,uint256,string,string)</t>
   </si>
   <si>
     <t xml:space="preserve"> backDateTransactionDate(address,address,uint256,address,uint256,uint256,uint256)</t>
   </si>
   <si>
-    <t xml:space="preserve"> getAgentRateTransactionCount(address,address,uint256,address,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getRecipientRateTransactionCount(address,address,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  getAgentRateTransactionAt(address,address,uint256,address,uint256,uint256)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> calculateStakingRewards(uint256,uint256,uint256,uint256)</t>
   </si>
   <si>
@@ -999,9 +951,6 @@
     <t xml:space="preserve"> getRecipientRateList(address,address)</t>
   </si>
   <si>
-    <t xml:space="preserve"> getRecipientRateTransactionCore(address,address,uint256)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> addRecipientAgent(address,address,uint256,address)</t>
   </si>
   <si>
@@ -1014,9 +963,6 @@
     <t xml:space="preserve"> getAgentRateList(address,address,uint256,address)</t>
   </si>
   <si>
-    <t xml:space="preserve"> getAgentRateTransactionCore(address,address,uint256,address,uint256)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> owner()</t>
   </si>
   <si>
@@ -1047,24 +993,6 @@
     <t xml:space="preserve"> getMasterAccountKeys()</t>
   </si>
   <si>
-    <t>getAccountRateTransactionList</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getAccountRateTransactionList.ts</t>
-  </si>
-  <si>
-    <t>getRecipientRateTransaction</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getRecipientRateTransaction.ts</t>
-  </si>
-  <si>
-    <t>getRecipientRateTransactionList</t>
-  </si>
-  <si>
-    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getRecipientRateTransactionList.ts</t>
-  </si>
-  <si>
     <t>calculateStakingRewards</t>
   </si>
   <si>
@@ -1084,6 +1012,78 @@
   </si>
   <si>
     <t>deleteRecipientRate</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getRecipientTransactionCore(address,address,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAgentTransactionCore(address,address,uint256,address,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> addRecipientTransaction(address,address,uint256,string,string)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAgentTransactionCount(address,address,uint256,address,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getRecipientTransactionCount(address,address,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  getAgentTransactionAt(address,address,uint256,address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t>getAccountTransactionList</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getAccountTransactionList.ts</t>
+  </si>
+  <si>
+    <t>getAgentTransaction</t>
+  </si>
+  <si>
+    <t>getAgentTransactionCount</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getAgentTransactionCount.ts</t>
+  </si>
+  <si>
+    <t>getAgentTransactionList</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getAgentTransactionList.ts</t>
+  </si>
+  <si>
+    <t>getTransactionList</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getTransactionList.ts</t>
+  </si>
+  <si>
+    <t>getRecipientTransaction</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getRecipientTransaction.ts</t>
+  </si>
+  <si>
+    <t>getRecipientTransactionList</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getRecipientTransactionList.ts</t>
+  </si>
+  <si>
+    <t>getRecipientTransactionCount</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/getRecipientTransactionCount.ts</t>
+  </si>
+  <si>
+    <t>addRecipientTransaction</t>
+  </si>
+  <si>
+    <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/write/defs/addRecipientTransaction.ts</t>
+  </si>
+  <si>
+    <t>external_getSerializedTransactionList</t>
   </si>
 </sst>
 </file>
@@ -1564,372 +1564,372 @@
   <sheetData>
     <row r="1" spans="1:1" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A1" s="9" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A2" s="10" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A3" s="8" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A4" s="8" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A5" s="8" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A6" s="8" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A7" s="8" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A8" s="8" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A9" s="8" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A10" s="8" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A11" s="8" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A12" s="8" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A13" s="12" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="20.350000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="10" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A15" s="8" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A16" s="8" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A17" s="8" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A18" s="8" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A19" s="8" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A20" s="12" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A21" s="10" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="11" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="11" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="11" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="11" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="11" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="11" t="s">
-        <v>333</v>
+        <v>315</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="11" t="s">
-        <v>334</v>
+        <v>316</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="11" t="s">
-        <v>335</v>
+        <v>317</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="11" t="s">
-        <v>336</v>
+        <v>318</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A31" s="12" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="37.5" x14ac:dyDescent="0.45">
       <c r="A32" s="10" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="11" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="11" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="11" t="s">
-        <v>312</v>
+        <v>296</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="11" t="s">
-        <v>313</v>
+        <v>297</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="11" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="11" t="s">
-        <v>315</v>
+        <v>299</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="11" t="s">
-        <v>316</v>
+        <v>300</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="11" t="s">
-        <v>317</v>
+        <v>301</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="11" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="11" t="s">
-        <v>319</v>
+        <v>303</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="11" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="11" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="11" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="11" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="11" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="11" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
     </row>
     <row r="49" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="11" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
     </row>
     <row r="50" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="51" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A51" s="12" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="52" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A52" s="10" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="53" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="11" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
     </row>
     <row r="54" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="11" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
     </row>
     <row r="55" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="11" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
     </row>
     <row r="56" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="11" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
     </row>
     <row r="57" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="11" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
     </row>
     <row r="58" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="11" t="s">
-        <v>310</v>
+        <v>294</v>
       </c>
     </row>
     <row r="59" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A59" s="12" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
     </row>
     <row r="60" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A60" s="10" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
     </row>
     <row r="61" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="11" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
     </row>
     <row r="62" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="11" t="s">
-        <v>299</v>
+        <v>329</v>
       </c>
     </row>
     <row r="63" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="11" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
     </row>
     <row r="64" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="11" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
     </row>
     <row r="65" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="11" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="11" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="11" t="s">
-        <v>304</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A68" s="12" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
     </row>
     <row r="69" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A69" s="10" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
     </row>
     <row r="70" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="11" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
     </row>
     <row r="71" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="11" t="s">
-        <v>346</v>
+        <v>322</v>
       </c>
     </row>
     <row r="72" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="11" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="73" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="11" t="s">
-        <v>347</v>
+        <v>323</v>
       </c>
     </row>
     <row r="74" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="11" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="75" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
@@ -1971,7 +1971,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -1985,163 +1985,163 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E2" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="F2" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G2" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E3" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G3" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B4" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E4" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>348</v>
+        <v>324</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>349</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -2178,7 +2178,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -2189,71 +2189,71 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="F2" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G2" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="F3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G3" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B4" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="C4" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="D4" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="F4" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G4" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2290,7 +2290,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -2301,71 +2301,71 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C2" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D2" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B3" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C3" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D3" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B4" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C4" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="D4" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -2399,7 +2399,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -2422,7 +2422,7 @@
         <v>11</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -2442,19 +2442,19 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E3" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="F3" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G3" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
@@ -2468,7 +2468,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -2491,13 +2491,13 @@
         <v>24</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E5" t="s">
         <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G5" t="s">
         <v>26</v>
@@ -2514,13 +2514,13 @@
         <v>27</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
       </c>
       <c r="F6" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G6" t="s">
         <v>29</v>
@@ -2534,19 +2534,19 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
@@ -2557,10 +2557,10 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -2569,7 +2569,7 @@
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
@@ -2580,19 +2580,19 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>263</v>
+        <v>335</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
@@ -2603,19 +2603,19 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>336</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>63</v>
+        <v>337</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
@@ -2626,19 +2626,19 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>338</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F11" t="s">
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>65</v>
+        <v>339</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
@@ -2649,19 +2649,19 @@
         <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E13" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="F13" t="s">
         <v>9</v>
       </c>
       <c r="G13" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
@@ -2672,10 +2672,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -2684,7 +2684,7 @@
         <v>9</v>
       </c>
       <c r="G14" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
@@ -2695,10 +2695,10 @@
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -2707,12 +2707,12 @@
         <v>9</v>
       </c>
       <c r="G15" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="7" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
@@ -2726,7 +2726,7 @@
         <v>22</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
@@ -2746,19 +2746,19 @@
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E21" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F21" t="s">
         <v>9</v>
       </c>
       <c r="G21" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
@@ -2769,24 +2769,24 @@
         <v>6</v>
       </c>
       <c r="C22" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E22" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F22" t="s">
         <v>9</v>
       </c>
       <c r="G22" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="7" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
@@ -2797,19 +2797,19 @@
         <v>6</v>
       </c>
       <c r="C29" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F29" t="s">
         <v>9</v>
       </c>
       <c r="G29" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
@@ -2820,19 +2820,19 @@
         <v>6</v>
       </c>
       <c r="C30" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E30" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F30" t="s">
         <v>9</v>
       </c>
       <c r="G30" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
@@ -2843,19 +2843,19 @@
         <v>6</v>
       </c>
       <c r="C31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F31" t="s">
         <v>9</v>
       </c>
       <c r="G31" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
@@ -2869,7 +2869,7 @@
         <v>7</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -2889,10 +2889,10 @@
         <v>6</v>
       </c>
       <c r="C33" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -2901,7 +2901,7 @@
         <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
@@ -2912,10 +2912,10 @@
         <v>6</v>
       </c>
       <c r="C34" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2924,7 +2924,7 @@
         <v>9</v>
       </c>
       <c r="G34" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
@@ -2935,10 +2935,10 @@
         <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2947,7 +2947,7 @@
         <v>9</v>
       </c>
       <c r="G35" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
@@ -2958,19 +2958,19 @@
         <v>6</v>
       </c>
       <c r="C36" t="s">
+        <v>340</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="E36" t="s">
         <v>30</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="E36" t="s">
-        <v>31</v>
-      </c>
       <c r="F36" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G36" t="s">
-        <v>32</v>
+        <v>341</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
@@ -2981,10 +2981,10 @@
         <v>6</v>
       </c>
       <c r="C37" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E37" t="s">
         <v>19</v>
@@ -2993,7 +2993,7 @@
         <v>9</v>
       </c>
       <c r="G37" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
@@ -3004,10 +3004,10 @@
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E38" t="s">
         <v>19</v>
@@ -3016,7 +3016,7 @@
         <v>9</v>
       </c>
       <c r="G38" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
@@ -3027,19 +3027,19 @@
         <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E39" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F39" t="s">
         <v>9</v>
       </c>
       <c r="G39" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
@@ -3050,19 +3050,19 @@
         <v>6</v>
       </c>
       <c r="C40" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E40" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F40" t="s">
         <v>9</v>
       </c>
       <c r="G40" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
@@ -3073,10 +3073,10 @@
         <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -3085,7 +3085,7 @@
         <v>9</v>
       </c>
       <c r="G41" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
@@ -3096,19 +3096,19 @@
         <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E42" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F42" t="s">
         <v>9</v>
       </c>
       <c r="G42" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
@@ -3119,19 +3119,19 @@
         <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E43" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F43" t="s">
         <v>9</v>
       </c>
       <c r="G43" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
@@ -3142,19 +3142,19 @@
         <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>60</v>
+        <v>346</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E44" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F44" t="s">
         <v>9</v>
       </c>
       <c r="G44" t="s">
-        <v>61</v>
+        <v>347</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
@@ -3165,19 +3165,19 @@
         <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E45" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F45" t="s">
         <v>9</v>
       </c>
       <c r="G45" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.45">
@@ -3188,19 +3188,19 @@
         <v>6</v>
       </c>
       <c r="C46" t="s">
+        <v>43</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="E46" t="s">
+        <v>44</v>
+      </c>
+      <c r="F46" t="s">
+        <v>9</v>
+      </c>
+      <c r="G46" t="s">
         <v>45</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="E46" t="s">
-        <v>46</v>
-      </c>
-      <c r="F46" t="s">
-        <v>9</v>
-      </c>
-      <c r="G46" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.45">
@@ -3214,7 +3214,7 @@
         <v>17</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -3234,19 +3234,19 @@
         <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>344</v>
+        <v>320</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E48" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F48" t="s">
         <v>9</v>
       </c>
       <c r="G48" t="s">
-        <v>345</v>
+        <v>321</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.45">
@@ -3257,10 +3257,10 @@
         <v>6</v>
       </c>
       <c r="C49" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -3269,7 +3269,7 @@
         <v>9</v>
       </c>
       <c r="G49" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.45">
@@ -3280,10 +3280,10 @@
         <v>6</v>
       </c>
       <c r="C50" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -3292,7 +3292,7 @@
         <v>9</v>
       </c>
       <c r="G50" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.45">
@@ -3303,10 +3303,10 @@
         <v>6</v>
       </c>
       <c r="C51" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -3315,7 +3315,7 @@
         <v>9</v>
       </c>
       <c r="G51" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.45">
@@ -3326,10 +3326,10 @@
         <v>6</v>
       </c>
       <c r="C52" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E52" t="s">
         <v>19</v>
@@ -3338,7 +3338,7 @@
         <v>9</v>
       </c>
       <c r="G52" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.45">
@@ -3349,19 +3349,19 @@
         <v>6</v>
       </c>
       <c r="C53" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E53" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F53" t="s">
         <v>9</v>
       </c>
       <c r="G53" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.45">
@@ -3372,10 +3372,10 @@
         <v>6</v>
       </c>
       <c r="C54" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -3384,7 +3384,7 @@
         <v>9</v>
       </c>
       <c r="G54" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.45">
@@ -3395,10 +3395,10 @@
         <v>6</v>
       </c>
       <c r="C55" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -3407,7 +3407,7 @@
         <v>9</v>
       </c>
       <c r="G55" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.45">
@@ -3418,10 +3418,10 @@
         <v>6</v>
       </c>
       <c r="C56" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -3430,7 +3430,7 @@
         <v>9</v>
       </c>
       <c r="G56" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -3468,7 +3468,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -3482,246 +3482,246 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="E2" t="s">
         <v>84</v>
       </c>
-      <c r="B2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="E2" t="s">
-        <v>94</v>
-      </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E3" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G3" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B4" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C4" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E4" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C5" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E5" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="E6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" t="s">
         <v>218</v>
-      </c>
-      <c r="E6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>348</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E7" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>88</v>
+        <v>349</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E8" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="F8" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G8" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B10" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C10" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E10" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B11" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C11" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E11" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F11" t="s">
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
@@ -3730,619 +3730,619 @@
         <v>9</v>
       </c>
       <c r="G12" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B13" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="C13" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E13" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="F13" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G13" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E14" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="F14" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G14" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B15" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>348</v>
+        <v>324</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F15" t="s">
         <v>9</v>
       </c>
       <c r="G15" t="s">
-        <v>349</v>
+        <v>325</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F16" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G16" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B17" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F17" t="s">
         <v>9</v>
       </c>
       <c r="G17" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E18" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="F18" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G18" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B19" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>350</v>
+        <v>326</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F19" t="s">
         <v>9</v>
       </c>
       <c r="G19" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E20" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="F20" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G20" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E21" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="F21" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G21" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E22" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G22" t="s">
         <v>100</v>
-      </c>
-      <c r="G22" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F23" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G23" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E24" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="F24" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G24" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E25" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F25" t="s">
         <v>9</v>
       </c>
       <c r="G25" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B26" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E26" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="F26" t="s">
         <v>9</v>
       </c>
       <c r="G26" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B27" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C27" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E27" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="F27" t="s">
         <v>9</v>
       </c>
       <c r="G27" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B28" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C28" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E28" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="F28" t="s">
         <v>9</v>
       </c>
       <c r="G28" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B29" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C29" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E29" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="F29" t="s">
         <v>9</v>
       </c>
       <c r="G29" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B30" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C30" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E30" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F30" t="s">
         <v>9</v>
       </c>
       <c r="G30" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B31" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C31" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E31" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="F31" t="s">
         <v>9</v>
       </c>
       <c r="G31" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B32" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C32" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E32" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="F32" t="s">
         <v>9</v>
       </c>
       <c r="G32" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B33" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C33" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E33" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="F33" t="s">
         <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B34" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C34" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E34" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="F34" t="s">
         <v>9</v>
       </c>
       <c r="G34" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B35" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C35" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E35" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="F35" t="s">
         <v>9</v>
       </c>
       <c r="G35" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B36" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C36" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E36" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="F36" t="s">
         <v>9</v>
       </c>
       <c r="G36" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C37" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E37" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="F37" t="s">
         <v>9</v>
       </c>
       <c r="G37" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B38" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C38" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E38" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="F38" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G38" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B39" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C39" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E39" t="s">
         <v>19</v>
@@ -4351,21 +4351,21 @@
         <v>9</v>
       </c>
       <c r="G39" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B40" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C40" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -4374,7 +4374,7 @@
         <v>9</v>
       </c>
       <c r="G40" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -4412,7 +4412,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -4426,16 +4426,16 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="B2" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="C2" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4444,21 +4444,21 @@
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="C3" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4467,21 +4467,21 @@
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="B4" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="C4" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4490,21 +4490,21 @@
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="B5" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="C5" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4513,21 +4513,21 @@
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="B6" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="C6" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -4536,21 +4536,21 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="B7" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="C7" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -4559,7 +4559,7 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -4593,7 +4593,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -4607,16 +4607,16 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="B2" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="C2" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4625,21 +4625,21 @@
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="B3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="C3" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4648,21 +4648,21 @@
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="B4" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="C4" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4671,7 +4671,7 @@
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -4705,7 +4705,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -4719,485 +4719,485 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B2" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C2" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G2" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B3" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C3" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G3" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B4" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C4" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G4" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B5" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C5" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G5" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B6" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C6" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G6" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B7" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C7" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F7" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G7" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B8" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C8" t="s">
-        <v>208</v>
+        <v>350</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F8" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G8" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
+        <v>188</v>
+      </c>
+      <c r="B9" t="s">
         <v>198</v>
       </c>
-      <c r="B9" t="s">
-        <v>209</v>
-      </c>
       <c r="C9" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E9" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="F9" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G9" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
+        <v>188</v>
+      </c>
+      <c r="B10" t="s">
         <v>198</v>
       </c>
-      <c r="B10" t="s">
-        <v>209</v>
-      </c>
       <c r="C10" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G10" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
+        <v>188</v>
+      </c>
+      <c r="B11" t="s">
         <v>198</v>
       </c>
-      <c r="B11" t="s">
-        <v>209</v>
-      </c>
       <c r="C11" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G11" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
+        <v>188</v>
+      </c>
+      <c r="B12" t="s">
         <v>198</v>
       </c>
-      <c r="B12" t="s">
-        <v>209</v>
-      </c>
       <c r="C12" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G12" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B13" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C13" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E13" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="F13" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G13" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B14" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C14" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G14" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B15" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E15" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="F15" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G15" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B16" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F16" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G16" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B17" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C17" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E17" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F17" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G17" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F18" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G18" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B19" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C19" t="s">
-        <v>348</v>
+        <v>324</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F19" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G19" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B20" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E20" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F20" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G20" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B21" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C21" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E21" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F21" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G21" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B22" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C22" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F22" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G22" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -5231,7 +5231,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -5245,108 +5245,108 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B2" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C2" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B3" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C3" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E3" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B4" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C4" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E4" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E5" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C6" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -5355,421 +5355,421 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C7" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E7" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B8" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C8" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E8" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C9" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E9" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B10" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C10" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E10" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B11" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C11" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E11" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="F11" t="s">
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B12" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C12" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E12" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="F12" t="s">
         <v>9</v>
       </c>
       <c r="G12" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B13" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C13" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E13" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F13" t="s">
         <v>9</v>
       </c>
       <c r="G13" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B14" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C14" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E14" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="F14" t="s">
         <v>9</v>
       </c>
       <c r="G14" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B15" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C15" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E15" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="F15" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G15" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B16" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C16" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G16" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B17" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E17" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="F17" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G17" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E18" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F18" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G18" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B19" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C19" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F19" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G19" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B20" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E20" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F20" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G20" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B21" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C21" t="s">
-        <v>348</v>
+        <v>324</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F21" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G21" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B22" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E22" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F22" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G22" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B23" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C23" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F23" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G23" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B24" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C24" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E24" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F24" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G24" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -5803,7 +5803,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -5817,94 +5817,94 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B2" t="s">
         <v>198</v>
       </c>
-      <c r="B2" t="s">
-        <v>209</v>
-      </c>
       <c r="C2" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E2" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="F2" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G2" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B3" t="s">
         <v>198</v>
       </c>
-      <c r="B3" t="s">
-        <v>209</v>
-      </c>
       <c r="C3" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G3" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B4" t="s">
         <v>198</v>
       </c>
-      <c r="B4" t="s">
-        <v>209</v>
-      </c>
       <c r="C4" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G4" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B5" t="s">
         <v>198</v>
       </c>
-      <c r="B5" t="s">
-        <v>209</v>
-      </c>
       <c r="C5" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G5" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -5938,7 +5938,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -5961,7 +5961,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
@@ -5984,7 +5984,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
@@ -6007,7 +6007,7 @@
         <v>22</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -6027,19 +6027,19 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" t="s">
         <v>34</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="E5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
@@ -6050,19 +6050,19 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
@@ -6073,19 +6073,19 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="E7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" t="s">
         <v>55</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="E7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
@@ -6096,19 +6096,19 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>338</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>65</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>

--- a/docs/DropDownAccessMethods.xlsx
+++ b/docs/DropDownAccessMethods.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robin\spCoin\SPCOIN-PROJECT-MODULES\spcoin-nextjs-front-end\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A2732F-00FB-45AA-8846-993DB284AC81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88C93E37-575E-4122-9F8B-1032C0CC1260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="13403" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="351">
   <si>
     <t>Panel</t>
   </si>
@@ -897,9 +897,6 @@
     <t xml:space="preserve"> addAgentTransaction(address,address,uint256,address,uint256,string,string)</t>
   </si>
   <si>
-    <t xml:space="preserve"> backDateTransactionDate(address,address,uint256,address,uint256,uint256,uint256)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> calculateStakingRewards(uint256,uint256,uint256,uint256)</t>
   </si>
   <si>
@@ -1084,6 +1081,9 @@
   </si>
   <si>
     <t>external_getSerializedTransactionList</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> backDateTransaction(address,address,uint256,address,uint256,uint256,uint256)</t>
   </si>
 </sst>
 </file>
@@ -1213,7 +1213,7 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1669,47 +1669,47 @@
     </row>
     <row r="22" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="11" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="11" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="11" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="11" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="11" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="11" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="11" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="11" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
@@ -1724,92 +1724,92 @@
     </row>
     <row r="33" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="11" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="11" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="11" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="11" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="11" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="11" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="11" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="11" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="11" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="49" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="11" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="50" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="11" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="51" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
@@ -1824,32 +1824,32 @@
     </row>
     <row r="53" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="54" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="55" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="56" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="11" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="57" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="11" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="58" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="59" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
@@ -1869,7 +1869,7 @@
     </row>
     <row r="62" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="11" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
@@ -1879,22 +1879,22 @@
     </row>
     <row r="64" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="11" t="s">
-        <v>288</v>
+        <v>350</v>
       </c>
     </row>
     <row r="65" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="11" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="11" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
@@ -1914,7 +1914,7 @@
     </row>
     <row r="71" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="11" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="72" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
@@ -1924,7 +1924,7 @@
     </row>
     <row r="73" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="11" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="74" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
@@ -2129,7 +2129,7 @@
         <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>207</v>
@@ -2141,7 +2141,7 @@
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -2442,7 +2442,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>207</v>
@@ -2454,7 +2454,7 @@
         <v>90</v>
       </c>
       <c r="G3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
@@ -2580,7 +2580,7 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>210</v>
@@ -2603,7 +2603,7 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>210</v>
@@ -2615,7 +2615,7 @@
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
@@ -2626,7 +2626,7 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>210</v>
@@ -2638,7 +2638,7 @@
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
@@ -2958,7 +2958,7 @@
         <v>6</v>
       </c>
       <c r="C36" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>207</v>
@@ -2970,7 +2970,7 @@
         <v>90</v>
       </c>
       <c r="G36" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
@@ -3096,7 +3096,7 @@
         <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>207</v>
@@ -3108,7 +3108,7 @@
         <v>9</v>
       </c>
       <c r="G42" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
@@ -3119,7 +3119,7 @@
         <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>207</v>
@@ -3131,7 +3131,7 @@
         <v>9</v>
       </c>
       <c r="G43" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
@@ -3142,7 +3142,7 @@
         <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>207</v>
@@ -3154,7 +3154,7 @@
         <v>9</v>
       </c>
       <c r="G44" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
@@ -3234,7 +3234,7 @@
         <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>207</v>
@@ -3246,7 +3246,7 @@
         <v>9</v>
       </c>
       <c r="G48" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.45">
@@ -3603,7 +3603,7 @@
         <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>207</v>
@@ -3615,7 +3615,7 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
@@ -3787,7 +3787,7 @@
         <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>207</v>
@@ -3799,7 +3799,7 @@
         <v>9</v>
       </c>
       <c r="G15" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
@@ -3879,7 +3879,7 @@
         <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>207</v>
@@ -4863,7 +4863,7 @@
         <v>189</v>
       </c>
       <c r="C8" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>207</v>
@@ -5116,7 +5116,7 @@
         <v>113</v>
       </c>
       <c r="C19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>207</v>
@@ -5688,7 +5688,7 @@
         <v>113</v>
       </c>
       <c r="C21" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>207</v>
@@ -6096,7 +6096,7 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>207</v>
@@ -6108,7 +6108,7 @@
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>

--- a/docs/DropDownAccessMethods.xlsx
+++ b/docs/DropDownAccessMethods.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robin\spCoin\SPCOIN-PROJECT-MODULES\spcoin-nextjs-front-end\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88C93E37-575E-4122-9F8B-1032C0CC1260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED6D5D90-A913-4C92-B6CE-AABABAD6957E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="13403" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="On chain Methods" sheetId="1" r:id="rId1"/>
@@ -885,9 +885,6 @@
     <t xml:space="preserve"> deleteRecipient(address,address)</t>
   </si>
   <si>
-    <t xml:space="preserve"> deleteRecipientAgent(address,address,uint256,address)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> deleteAccountRecord(address)</t>
   </si>
   <si>
@@ -939,18 +936,12 @@
     <t xml:space="preserve"> getAgentKeyCount(address)</t>
   </si>
   <si>
-    <t xml:space="preserve"> addSponsorRecipient(address,address)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> getRecipientRecordCore(address,address)</t>
   </si>
   <si>
     <t xml:space="preserve"> getRecipientRateList(address,address)</t>
   </si>
   <si>
-    <t xml:space="preserve"> addRecipientAgent(address,address,uint256,address)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> getRecipientRateAgentList(address,address,uint256)</t>
   </si>
   <si>
@@ -1026,9 +1017,6 @@
     <t xml:space="preserve"> getRecipientTransactionCount(address,address,uint256)</t>
   </si>
   <si>
-    <t xml:space="preserve">  getAgentTransactionAt(address,address,uint256,address,uint256,uint256)</t>
-  </si>
-  <si>
     <t>getAccountTransactionList</t>
   </si>
   <si>
@@ -1084,6 +1072,18 @@
   </si>
   <si>
     <t xml:space="preserve"> backDateTransaction(address,address,uint256,address,uint256,uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> addAgent(address,address,uint256,address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> deleteAgent(address,address,uint256,address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAgentTransactionAt(address,address,uint256,address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> addSponsor(address,address)</t>
   </si>
 </sst>
 </file>
@@ -1669,47 +1669,47 @@
     </row>
     <row r="22" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="11" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="11" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="11" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="11" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="11" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="11" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="11" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="11" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="11" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
@@ -1724,92 +1724,92 @@
     </row>
     <row r="33" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="11" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="11" t="s">
-        <v>299</v>
+        <v>347</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="11" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="11" t="s">
-        <v>303</v>
+        <v>350</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="11" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="11" t="s">
-        <v>326</v>
+        <v>302</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="11" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="11" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="11" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="49" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="11" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="50" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="11" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="51" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
@@ -1824,32 +1824,32 @@
     </row>
     <row r="53" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="54" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="55" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="56" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="57" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="11" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="58" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="11" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="59" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
@@ -1864,37 +1864,37 @@
     </row>
     <row r="61" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="11" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="62" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="11" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="11" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="64" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="11" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="65" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="11" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="11" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="11" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
     </row>
     <row r="68" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
@@ -1909,27 +1909,27 @@
     </row>
     <row r="70" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="11" t="s">
-        <v>283</v>
+        <v>348</v>
       </c>
     </row>
     <row r="71" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="11" t="s">
-        <v>321</v>
+        <v>283</v>
       </c>
     </row>
     <row r="72" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="11" t="s">
-        <v>284</v>
+        <v>318</v>
       </c>
     </row>
     <row r="73" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="11" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="74" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="75" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
@@ -2129,7 +2129,7 @@
         <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>207</v>
@@ -2141,7 +2141,7 @@
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -2442,7 +2442,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>207</v>
@@ -2454,7 +2454,7 @@
         <v>90</v>
       </c>
       <c r="G3" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
@@ -2580,7 +2580,7 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>210</v>
@@ -2603,7 +2603,7 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>210</v>
@@ -2615,7 +2615,7 @@
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
@@ -2626,7 +2626,7 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>210</v>
@@ -2638,7 +2638,7 @@
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
@@ -2958,7 +2958,7 @@
         <v>6</v>
       </c>
       <c r="C36" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>207</v>
@@ -2970,7 +2970,7 @@
         <v>90</v>
       </c>
       <c r="G36" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
@@ -3096,7 +3096,7 @@
         <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>207</v>
@@ -3108,7 +3108,7 @@
         <v>9</v>
       </c>
       <c r="G42" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
@@ -3119,7 +3119,7 @@
         <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>207</v>
@@ -3131,7 +3131,7 @@
         <v>9</v>
       </c>
       <c r="G43" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
@@ -3142,7 +3142,7 @@
         <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>207</v>
@@ -3154,7 +3154,7 @@
         <v>9</v>
       </c>
       <c r="G44" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
@@ -3234,7 +3234,7 @@
         <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>207</v>
@@ -3246,7 +3246,7 @@
         <v>9</v>
       </c>
       <c r="G48" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.45">
@@ -3603,7 +3603,7 @@
         <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>207</v>
@@ -3615,7 +3615,7 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
@@ -3787,7 +3787,7 @@
         <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>207</v>
@@ -3799,7 +3799,7 @@
         <v>9</v>
       </c>
       <c r="G15" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
@@ -3879,7 +3879,7 @@
         <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>207</v>
@@ -4863,7 +4863,7 @@
         <v>189</v>
       </c>
       <c r="C8" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>207</v>
@@ -5116,7 +5116,7 @@
         <v>113</v>
       </c>
       <c r="C19" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>207</v>
@@ -5688,7 +5688,7 @@
         <v>113</v>
       </c>
       <c r="C21" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>207</v>
@@ -6096,7 +6096,7 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>207</v>
@@ -6108,7 +6108,7 @@
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>

--- a/docs/DropDownAccessMethods.xlsx
+++ b/docs/DropDownAccessMethods.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robin\spCoin\SPCOIN-PROJECT-MODULES\spcoin-nextjs-front-end\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED6D5D90-A913-4C92-B6CE-AABABAD6957E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1507572C-F03B-4357-8A9E-39D5E2ABC4C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="On chain Methods" sheetId="1" r:id="rId1"/>
@@ -3605,8 +3605,8 @@
       <c r="C7" t="s">
         <v>343</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>207</v>
+      <c r="D7" s="3" t="s">
+        <v>210</v>
       </c>
       <c r="E7" t="s">
         <v>78</v>

--- a/docs/DropDownAccessMethods.xlsx
+++ b/docs/DropDownAccessMethods.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robin\spCoin\SPCOIN-PROJECT-MODULES\spcoin-nextjs-front-end\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88C93E37-575E-4122-9F8B-1032C0CC1260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1507572C-F03B-4357-8A9E-39D5E2ABC4C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="13403" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="On chain Methods" sheetId="1" r:id="rId1"/>
@@ -885,9 +885,6 @@
     <t xml:space="preserve"> deleteRecipient(address,address)</t>
   </si>
   <si>
-    <t xml:space="preserve"> deleteRecipientAgent(address,address,uint256,address)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> deleteAccountRecord(address)</t>
   </si>
   <si>
@@ -939,18 +936,12 @@
     <t xml:space="preserve"> getAgentKeyCount(address)</t>
   </si>
   <si>
-    <t xml:space="preserve"> addSponsorRecipient(address,address)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> getRecipientRecordCore(address,address)</t>
   </si>
   <si>
     <t xml:space="preserve"> getRecipientRateList(address,address)</t>
   </si>
   <si>
-    <t xml:space="preserve"> addRecipientAgent(address,address,uint256,address)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> getRecipientRateAgentList(address,address,uint256)</t>
   </si>
   <si>
@@ -1026,9 +1017,6 @@
     <t xml:space="preserve"> getRecipientTransactionCount(address,address,uint256)</t>
   </si>
   <si>
-    <t xml:space="preserve">  getAgentTransactionAt(address,address,uint256,address,uint256,uint256)</t>
-  </si>
-  <si>
     <t>getAccountTransactionList</t>
   </si>
   <si>
@@ -1084,6 +1072,18 @@
   </si>
   <si>
     <t xml:space="preserve"> backDateTransaction(address,address,uint256,address,uint256,uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> addAgent(address,address,uint256,address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> deleteAgent(address,address,uint256,address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAgentTransactionAt(address,address,uint256,address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> addSponsor(address,address)</t>
   </si>
 </sst>
 </file>
@@ -1669,47 +1669,47 @@
     </row>
     <row r="22" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="11" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="11" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="11" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="11" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="11" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="11" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="11" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="11" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="11" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
@@ -1724,92 +1724,92 @@
     </row>
     <row r="33" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="11" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="11" t="s">
-        <v>299</v>
+        <v>347</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="11" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="11" t="s">
-        <v>303</v>
+        <v>350</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="11" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="11" t="s">
-        <v>326</v>
+        <v>302</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="11" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="11" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="11" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="49" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="11" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="50" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="11" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="51" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
@@ -1824,32 +1824,32 @@
     </row>
     <row r="53" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="54" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="55" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="56" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="57" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="11" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="58" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="11" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="59" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
@@ -1864,37 +1864,37 @@
     </row>
     <row r="61" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="11" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="62" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="11" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="11" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="64" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="11" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="65" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="11" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="11" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="11" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
     </row>
     <row r="68" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
@@ -1909,27 +1909,27 @@
     </row>
     <row r="70" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="11" t="s">
-        <v>283</v>
+        <v>348</v>
       </c>
     </row>
     <row r="71" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="11" t="s">
-        <v>321</v>
+        <v>283</v>
       </c>
     </row>
     <row r="72" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="11" t="s">
-        <v>284</v>
+        <v>318</v>
       </c>
     </row>
     <row r="73" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="11" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="74" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="75" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
@@ -2129,7 +2129,7 @@
         <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>207</v>
@@ -2141,7 +2141,7 @@
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -2442,7 +2442,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>207</v>
@@ -2454,7 +2454,7 @@
         <v>90</v>
       </c>
       <c r="G3" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
@@ -2580,7 +2580,7 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>210</v>
@@ -2603,7 +2603,7 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>210</v>
@@ -2615,7 +2615,7 @@
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
@@ -2626,7 +2626,7 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>210</v>
@@ -2638,7 +2638,7 @@
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
@@ -2958,7 +2958,7 @@
         <v>6</v>
       </c>
       <c r="C36" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>207</v>
@@ -2970,7 +2970,7 @@
         <v>90</v>
       </c>
       <c r="G36" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
@@ -3096,7 +3096,7 @@
         <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>207</v>
@@ -3108,7 +3108,7 @@
         <v>9</v>
       </c>
       <c r="G42" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
@@ -3119,7 +3119,7 @@
         <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>207</v>
@@ -3131,7 +3131,7 @@
         <v>9</v>
       </c>
       <c r="G43" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
@@ -3142,7 +3142,7 @@
         <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>207</v>
@@ -3154,7 +3154,7 @@
         <v>9</v>
       </c>
       <c r="G44" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
@@ -3234,7 +3234,7 @@
         <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>207</v>
@@ -3246,7 +3246,7 @@
         <v>9</v>
       </c>
       <c r="G48" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.45">
@@ -3603,10 +3603,10 @@
         <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>347</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>207</v>
+        <v>343</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>210</v>
       </c>
       <c r="E7" t="s">
         <v>78</v>
@@ -3615,7 +3615,7 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
@@ -3787,7 +3787,7 @@
         <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>207</v>
@@ -3799,7 +3799,7 @@
         <v>9</v>
       </c>
       <c r="G15" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
@@ -3879,7 +3879,7 @@
         <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>207</v>
@@ -4863,7 +4863,7 @@
         <v>189</v>
       </c>
       <c r="C8" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>207</v>
@@ -5116,7 +5116,7 @@
         <v>113</v>
       </c>
       <c r="C19" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>207</v>
@@ -5688,7 +5688,7 @@
         <v>113</v>
       </c>
       <c r="C21" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>207</v>
@@ -6096,7 +6096,7 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>207</v>
@@ -6108,7 +6108,7 @@
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>

--- a/docs/DropDownAccessMethods.xlsx
+++ b/docs/DropDownAccessMethods.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robin\spCoin\SPCOIN-PROJECT-MODULES\spcoin-nextjs-front-end\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1507572C-F03B-4357-8A9E-39D5E2ABC4C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C562D596-13D5-4128-98D3-F8FADE60127B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="On chain Methods" sheetId="1" r:id="rId1"/>
+    <sheet name="OnChainMethods" sheetId="13" r:id="rId1"/>
     <sheet name="SpCoin Read" sheetId="2" r:id="rId2"/>
     <sheet name="SpCoin Write" sheetId="3" r:id="rId3"/>
     <sheet name="ERC20 Read" sheetId="4" r:id="rId4"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="357">
   <si>
     <t>Panel</t>
   </si>
@@ -795,9 +795,6 @@
     <t>================================================================ WIP =========================================================================</t>
   </si>
   <si>
-    <t>Source: SpCoinDataTypes.sol (line 16)</t>
-  </si>
-  <si>
     <t>balanceOf(address)</t>
   </si>
   <si>
@@ -828,18 +825,6 @@
     <t>totalUnstakedSpCoins()</t>
   </si>
   <si>
-    <t>SPCoin / ERC20</t>
-  </si>
-  <si>
-    <t>Sources: SPCoin.sol (line 24), Token.sol (line 23)</t>
-  </si>
-  <si>
-    <t>getVersion()</t>
-  </si>
-  <si>
-    <t>setVersion(string)</t>
-  </si>
-  <si>
     <t>transfer(address,uint256)</t>
   </si>
   <si>
@@ -849,150 +834,12 @@
     <t>transferFrom(address,address,uint256)</t>
   </si>
   <si>
-    <t>Security / config</t>
-  </si>
-  <si>
-    <t>Source: Security.sol (line 14)</t>
-  </si>
-  <si>
-    <t>Account / sponsor / recipient / agent reads</t>
-  </si>
-  <si>
-    <t>Sources: Account.sol (line 66), Recipient.sol (line 13), RecipientRates.sol (line 54), Agent.sol (line 12), AgentRates.sol (line 37)</t>
-  </si>
-  <si>
-    <t>Rewards / staking</t>
-  </si>
-  <si>
-    <t>Sources: StakingManager.sol (line 21), RewardsManager.sol (line 65)</t>
-  </si>
-  <si>
-    <t>Transaction methods</t>
-  </si>
-  <si>
-    <t>Source: Transactions.sol (line 9)</t>
-  </si>
-  <si>
-    <t>Delete / unsubscribe</t>
-  </si>
-  <si>
-    <t>Source: UnSubscribe.sol (line 26)</t>
-  </si>
-  <si>
-    <t>On Chain Methodss</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> deleteRecipient(address,address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> deleteAccountRecord(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> addSponsorship(address,uint256,address,uint256,string,string)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> addAgentTransaction(address,address,uint256,address,uint256,string,string)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> calculateStakingRewards(uint256,uint256,uint256,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getAccountRewardTotals(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> updateAccountStakingRewards(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> updateSponsorAccountRewards(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> updateAgentAccountRewards(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> updateRecipientAccountRewards(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getMasterAccountKeyAt(uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getAccountKeyCount()</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getAccountCore(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getAccountLinks(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getRecipientKeys(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getAgentKeys(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getRecipientKeyCount(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getAgentKeyCount(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getRecipientRecordCore(address,address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getRecipientRateList(address,address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getRecipientRateAgentList(address,address,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getAgentTotalRecipient(address,address,uint256,address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getAgentRateList(address,address,uint256,address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> owner()</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> isAccountInserted(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getInflationRate()</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> setInflationRate(uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getRecipientRateRange()</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> setRecipientRateRange(uint256,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getAgentRateRange()</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> setAgentRateRange(uint256,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getInitialTotalSupply()</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getMasterAccountKeys()</t>
-  </si>
-  <si>
     <t>calculateStakingRewards</t>
   </si>
   <si>
     <t>app/(menu)/(dynamic)/SponsorCoinLab/jsonMethods/spCoin/read/defs/calculateStakingRewards.ts</t>
   </si>
   <si>
-    <t xml:space="preserve"> deleteRecipientRate(address,address,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> deleteAgentRate(address,address,uint256,address,uint256)</t>
-  </si>
-  <si>
     <t>deleteAgentRate</t>
   </si>
   <si>
@@ -1002,21 +849,6 @@
     <t>deleteRecipientRate</t>
   </si>
   <si>
-    <t xml:space="preserve"> getRecipientTransactionCore(address,address,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getAgentTransactionCore(address,address,uint256,address,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> addRecipientTransaction(address,address,uint256,string,string)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getAgentTransactionCount(address,address,uint256,address,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getRecipientTransactionCount(address,address,uint256)</t>
-  </si>
-  <si>
     <t>getAccountTransactionList</t>
   </si>
   <si>
@@ -1071,19 +903,205 @@
     <t>external_getSerializedTransactionList</t>
   </si>
   <si>
-    <t xml:space="preserve"> backDateTransaction(address,address,uint256,address,uint256,uint256,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> addAgent(address,address,uint256,address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> deleteAgent(address,address,uint256,address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getAgentTransactionAt(address,address,uint256,address,uint256,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> addSponsor(address,address)</t>
+    <t>version()</t>
+  </si>
+  <si>
+    <t>init()</t>
+  </si>
+  <si>
+    <t>initToken(string,string,uint,uint)</t>
+  </si>
+  <si>
+    <t>owner()</t>
+  </si>
+  <si>
+    <t>isAccountInserted(address)</t>
+  </si>
+  <si>
+    <t>getInflationRate()</t>
+  </si>
+  <si>
+    <t>setInflationRate(uint256)</t>
+  </si>
+  <si>
+    <t>getRecipientRateRange()</t>
+  </si>
+  <si>
+    <t>setRecipientRateRange(uint256,uint256)</t>
+  </si>
+  <si>
+    <t>getAgentRateRange()</t>
+  </si>
+  <si>
+    <t>setAgentRateRange(uint256,uint256)</t>
+  </si>
+  <si>
+    <t>getMasterAccountKeys()</t>
+  </si>
+  <si>
+    <t>getMasterAccountKeyAt(uint256)</t>
+  </si>
+  <si>
+    <t>getAccountKeyCount()</t>
+  </si>
+  <si>
+    <t>getAccountCore(address)</t>
+  </si>
+  <si>
+    <t>getAccountLinks(address)</t>
+  </si>
+  <si>
+    <t>getRecipientKeys(address)</t>
+  </si>
+  <si>
+    <t>getAgentKeys(address)</t>
+  </si>
+  <si>
+    <t>getRecipientKeyCount(address)</t>
+  </si>
+  <si>
+    <t>getAgentKeyCount(address)</t>
+  </si>
+  <si>
+    <t>getRecipientRecordCore(address,address)</t>
+  </si>
+  <si>
+    <t>getRecipientRateList(address,address)</t>
+  </si>
+  <si>
+    <t>getRecipientTransactionCore(address,address,uint256)</t>
+  </si>
+  <si>
+    <t>getRecipientRateAgentList(address,address,uint256)</t>
+  </si>
+  <si>
+    <t>getAgentTotalRecipient(address,address,uint256,address)</t>
+  </si>
+  <si>
+    <t>getAgentRateList(address,address,uint256,address)</t>
+  </si>
+  <si>
+    <t>getAgentTransactionCore(address,address,uint256,address,uint256)</t>
+  </si>
+  <si>
+    <t>addRecipient(address,address)</t>
+  </si>
+  <si>
+    <t>addAgent(address,address,uint256,address)</t>
+  </si>
+  <si>
+    <t>calculateStakingRewards(uint256,uint256,uint256,uint256)</t>
+  </si>
+  <si>
+    <t>getAccountRewardTotals(address)</t>
+  </si>
+  <si>
+    <t>updateAccountStakingRewards(address)</t>
+  </si>
+  <si>
+    <t>updateSponsorAccountRewards(address)</t>
+  </si>
+  <si>
+    <t>updateAgentAccountRewards(address)</t>
+  </si>
+  <si>
+    <t>updateRecipientAccountRewards(address)</t>
+  </si>
+  <si>
+    <t>addSponsorship(address,uint,address,uint,string,string)</t>
+  </si>
+  <si>
+    <t>addRecipientTransaction(address,address,uint,string,string)</t>
+  </si>
+  <si>
+    <t>addAgentTransaction(address,address,uint,address,uint,string,string)</t>
+  </si>
+  <si>
+    <t>backDateTransaction(address,address,uint256,address,uint256,uint256,uint256)</t>
+  </si>
+  <si>
+    <t>getAgentTransactionCount(address,address,uint256,address,uint256)</t>
+  </si>
+  <si>
+    <t>getRecipientTransactionCount(address,address,uint256)</t>
+  </si>
+  <si>
+    <t>getAgentTransactionAt(address,address,uint256,address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t>getRecipientTransactionAt(address,address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t>deleteSponsor(address)</t>
+  </si>
+  <si>
+    <t>deleteRecipient(address,address)</t>
+  </si>
+  <si>
+    <t>deleteRecipientRate(address,address,uint256)</t>
+  </si>
+  <si>
+    <t>deleteAgent(address,address,uint256,address)</t>
+  </si>
+  <si>
+    <t>deleteAgentRate(address,address,uint256,address,uint256)</t>
+  </si>
+  <si>
+    <t>deleteAccountRecord(address)</t>
+  </si>
+  <si>
+    <t>SpCoinDataTypes.sol</t>
+  </si>
+  <si>
+    <t>Security.sol</t>
+  </si>
+  <si>
+    <t>Account.sol</t>
+  </si>
+  <si>
+    <t>Recipient.sol</t>
+  </si>
+  <si>
+    <t>RecipientRates.sol</t>
+  </si>
+  <si>
+    <t>Agent.sol</t>
+  </si>
+  <si>
+    <t>AgentRates.sol</t>
+  </si>
+  <si>
+    <t>Transactions.sol</t>
+  </si>
+  <si>
+    <t>UnSubscribe.sol</t>
+  </si>
+  <si>
+    <t>Read</t>
+  </si>
+  <si>
+    <t>Write</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>SPCoin.sol</t>
+  </si>
+  <si>
+    <t>Token.sol</t>
+  </si>
+  <si>
+    <t>StakingManager.sol</t>
+  </si>
+  <si>
+    <t>RewardsManager.sol</t>
+  </si>
+  <si>
+    <t>Exported On Chain Methods</t>
+  </si>
+  <si>
+    <t>totalInitialSupply()</t>
   </si>
 </sst>
 </file>
@@ -1107,33 +1125,33 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
       <sz val="18"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="12"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1176,6 +1194,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1189,7 +1213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1206,17 +1230,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1552,394 +1583,570 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A77"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD098BC8-8253-4308-BB80-99C559D5DD3D}">
+  <dimension ref="A1:A111"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="99.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="72" customWidth="1"/>
+    <col min="2" max="2" width="82.1328125" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="96" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="23.25" x14ac:dyDescent="0.7">
-      <c r="A1" s="9" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A2" s="10" t="s">
+      <c r="A1" s="8" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A2" s="13" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A3" s="14" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A4" s="11" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A3" s="8" t="s">
+    <row r="5" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A5" s="11" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A4" s="8" t="s">
+    <row r="6" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A6" s="11" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A5" s="8" t="s">
+    <row r="7" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A7" s="11" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A6" s="8" t="s">
+    <row r="8" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A8" s="11" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A9" s="11" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A7" s="8" t="s">
+    <row r="10" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A10" s="11" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A8" s="8" t="s">
+    <row r="11" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A11" s="11" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A9" s="8" t="s">
+    <row r="12" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A12" s="11" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A13" s="11" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A10" s="8" t="s">
+    <row r="14" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A14" s="11" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A11" s="8" t="s">
+    <row r="15" spans="1:1" s="9" customFormat="1" ht="20.65" x14ac:dyDescent="0.5">
+      <c r="A15" s="11" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A12" s="8" t="s">
+    <row r="16" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A16" s="15" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A17" s="12" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A18" s="13" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A19" s="14" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A20" s="12" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A21" s="15" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A22" s="11" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A23" s="11" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A24" s="13" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A25" s="14" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A26" s="12" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A27" s="15" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A28" s="11" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A13" s="12" t="s">
+    <row r="29" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A29" s="11" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="20.350000000000001" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="10" t="s">
+    <row r="30" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A30" s="11" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A15" s="8" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A16" s="8" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A17" s="8" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A18" s="8" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A19" s="8" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A20" s="12" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A21" s="10" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="11" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="11" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="11" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="11" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="11" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="11" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="11" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="11" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="11" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A31" s="12" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" ht="37.5" x14ac:dyDescent="0.45">
-      <c r="A32" s="10" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A31" s="13" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A32" s="14" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A33" s="11" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A34" s="11" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A35" s="11" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A36" s="11" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A37" s="11" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A38" s="15" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A39" s="11" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="38" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="11" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="11" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A40" s="11" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="41" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A41" s="11" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="11" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="43" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="11" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A42" s="13" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A43" s="14" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A44" s="11" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="45" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A45" s="11" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="46" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A46" s="11" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A47" s="11" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A48" s="11" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A49" s="11" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A50" s="11" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A51" s="12" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A52" s="10" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="11" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="11" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="11" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="11" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A51" s="11" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A52" s="11" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A53" s="15" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A54" s="12" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A55" s="13" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A56" s="14" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A57" s="11" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A58" s="11" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A59" s="12" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A60" s="10" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="11" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="11" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A59" s="15" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A60" s="11" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A61" s="13" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A62" s="14" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A63" s="11" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="11" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" s="11" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" s="11" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" s="11" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A64" s="15" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="68" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A68" s="12" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A69" s="10" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A65" s="12" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A66" s="13" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A67" s="14" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A68" s="11" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A69" s="11" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A70" s="11" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" s="11" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A71" s="15" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A72" s="11" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="73" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" s="11" t="s">
+    <row r="73" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A73" s="13" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A74" s="14" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" ht="41.25" x14ac:dyDescent="0.45">
+      <c r="A75" s="11" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A76" s="10" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A77" s="12" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A78" s="13" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A79" s="14" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A80" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A81" s="15" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A82" s="12" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A83" s="13" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A84" s="14" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A85" s="11" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="74" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A74" s="11" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A75" s="8"/>
-    </row>
-    <row r="76" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A76" s="8"/>
-    </row>
-    <row r="77" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A77" s="8"/>
+    <row r="86" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A86" s="15" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A87" s="11" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A88" s="11" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A89" s="11" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A90" s="11" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A91" s="13" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A92" s="14" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" ht="41.25" x14ac:dyDescent="0.45">
+      <c r="A93" s="11" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A94" s="11" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" ht="41.25" x14ac:dyDescent="0.45">
+      <c r="A95" s="11" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A96" s="11" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A97" s="15" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A98" s="11" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A99" s="11" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" ht="41.25" x14ac:dyDescent="0.45">
+      <c r="A100" s="11" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" ht="41.25" x14ac:dyDescent="0.45">
+      <c r="A101" s="11" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A102" s="13" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A103" s="14" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A104" s="12" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A105" s="15" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A106" s="11" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A107" s="11" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A108" s="11" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A109" s="11" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A110" s="11" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A111" s="11" t="s">
+        <v>338</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2129,7 +2336,7 @@
         <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>320</v>
+        <v>269</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>207</v>
@@ -2141,7 +2348,7 @@
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>321</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -2442,7 +2649,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>328</v>
+        <v>272</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>207</v>
@@ -2454,7 +2661,7 @@
         <v>90</v>
       </c>
       <c r="G3" t="s">
-        <v>329</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
@@ -2580,7 +2787,7 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>330</v>
+        <v>274</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>210</v>
@@ -2603,7 +2810,7 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>331</v>
+        <v>275</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>210</v>
@@ -2615,7 +2822,7 @@
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>332</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
@@ -2626,7 +2833,7 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>333</v>
+        <v>277</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>210</v>
@@ -2638,7 +2845,7 @@
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>334</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
@@ -2958,7 +3165,7 @@
         <v>6</v>
       </c>
       <c r="C36" t="s">
-        <v>335</v>
+        <v>279</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>207</v>
@@ -2970,7 +3177,7 @@
         <v>90</v>
       </c>
       <c r="G36" t="s">
-        <v>336</v>
+        <v>280</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
@@ -3096,7 +3303,7 @@
         <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>337</v>
+        <v>281</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>207</v>
@@ -3108,7 +3315,7 @@
         <v>9</v>
       </c>
       <c r="G42" t="s">
-        <v>338</v>
+        <v>282</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
@@ -3119,7 +3326,7 @@
         <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>339</v>
+        <v>283</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>207</v>
@@ -3131,7 +3338,7 @@
         <v>9</v>
       </c>
       <c r="G43" t="s">
-        <v>340</v>
+        <v>284</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
@@ -3142,7 +3349,7 @@
         <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>341</v>
+        <v>285</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>207</v>
@@ -3154,7 +3361,7 @@
         <v>9</v>
       </c>
       <c r="G44" t="s">
-        <v>342</v>
+        <v>286</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
@@ -3234,7 +3441,7 @@
         <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>207</v>
@@ -3246,7 +3453,7 @@
         <v>9</v>
       </c>
       <c r="G48" t="s">
-        <v>317</v>
+        <v>268</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.45">
@@ -3603,7 +3810,7 @@
         <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>343</v>
+        <v>287</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>210</v>
@@ -3615,7 +3822,7 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>344</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
@@ -3787,7 +3994,7 @@
         <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>320</v>
+        <v>269</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>207</v>
@@ -3799,7 +4006,7 @@
         <v>9</v>
       </c>
       <c r="G15" t="s">
-        <v>321</v>
+        <v>270</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
@@ -3879,7 +4086,7 @@
         <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>322</v>
+        <v>271</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>207</v>
@@ -4863,7 +5070,7 @@
         <v>189</v>
       </c>
       <c r="C8" t="s">
-        <v>345</v>
+        <v>289</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>207</v>
@@ -5116,7 +5323,7 @@
         <v>113</v>
       </c>
       <c r="C19" t="s">
-        <v>320</v>
+        <v>269</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>207</v>
@@ -5688,7 +5895,7 @@
         <v>113</v>
       </c>
       <c r="C21" t="s">
-        <v>320</v>
+        <v>269</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>207</v>
@@ -6096,7 +6303,7 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>333</v>
+        <v>277</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>207</v>
@@ -6108,7 +6315,7 @@
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>334</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>

--- a/docs/DropDownAccessMethods.xlsx
+++ b/docs/DropDownAccessMethods.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robin\spCoin\SPCOIN-PROJECT-MODULES\spcoin-nextjs-front-end\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C562D596-13D5-4128-98D3-F8FADE60127B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5232384-434D-46ED-8655-13939F939AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OnChainMethods" sheetId="13" r:id="rId1"/>
@@ -1151,7 +1151,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1200,6 +1200,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1213,7 +1219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1249,6 +1255,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1604,7 +1616,7 @@
       </c>
     </row>
     <row r="3" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="16" t="s">
         <v>348</v>
       </c>
     </row>
@@ -1619,32 +1631,32 @@
       </c>
     </row>
     <row r="6" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="17" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="17" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="17" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="17" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="17" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="17" t="s">
         <v>260</v>
       </c>
     </row>
@@ -1684,7 +1696,7 @@
       </c>
     </row>
     <row r="19" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="16" t="s">
         <v>348</v>
       </c>
     </row>
@@ -1714,7 +1726,7 @@
       </c>
     </row>
     <row r="25" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="16" t="s">
         <v>348</v>
       </c>
     </row>
@@ -1749,32 +1761,32 @@
       </c>
     </row>
     <row r="32" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="16" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="17" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="17" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A35" s="11" t="s">
+      <c r="A35" s="17" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A36" s="11" t="s">
+      <c r="A36" s="17" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="17" t="s">
         <v>299</v>
       </c>
     </row>
@@ -1784,17 +1796,17 @@
       </c>
     </row>
     <row r="39" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A39" s="11" t="s">
+      <c r="A39" s="17" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A40" s="11" t="s">
+      <c r="A40" s="17" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A41" s="11" t="s">
+      <c r="A41" s="17" t="s">
         <v>300</v>
       </c>
     </row>
@@ -1804,32 +1816,32 @@
       </c>
     </row>
     <row r="43" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A43" s="14" t="s">
+      <c r="A43" s="16" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A44" s="11" t="s">
+      <c r="A44" s="17" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A45" s="11" t="s">
+      <c r="A45" s="17" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A46" s="11" t="s">
+      <c r="A46" s="17" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A47" s="11" t="s">
+      <c r="A47" s="17" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A48" s="11" t="s">
+      <c r="A48" s="17" t="s">
         <v>305</v>
       </c>
     </row>
@@ -1899,7 +1911,7 @@
       </c>
     </row>
     <row r="62" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A62" s="14" t="s">
+      <c r="A62" s="16" t="s">
         <v>348</v>
       </c>
     </row>
@@ -1924,7 +1936,7 @@
       </c>
     </row>
     <row r="67" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A67" s="14" t="s">
+      <c r="A67" s="16" t="s">
         <v>348</v>
       </c>
     </row>
@@ -1959,7 +1971,7 @@
       </c>
     </row>
     <row r="74" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A74" s="14" t="s">
+      <c r="A74" s="16" t="s">
         <v>348</v>
       </c>
     </row>
@@ -1984,7 +1996,7 @@
       </c>
     </row>
     <row r="79" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A79" s="14" t="s">
+      <c r="A79" s="16" t="s">
         <v>348</v>
       </c>
     </row>
@@ -2009,7 +2021,7 @@
       </c>
     </row>
     <row r="84" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A84" s="14" t="s">
+      <c r="A84" s="16" t="s">
         <v>348</v>
       </c>
     </row>
@@ -2049,7 +2061,7 @@
       </c>
     </row>
     <row r="92" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A92" s="14" t="s">
+      <c r="A92" s="16" t="s">
         <v>348</v>
       </c>
     </row>
@@ -2104,7 +2116,7 @@
       </c>
     </row>
     <row r="103" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A103" s="14" t="s">
+      <c r="A103" s="16" t="s">
         <v>348</v>
       </c>
     </row>

--- a/docs/DropDownAccessMethods.xlsx
+++ b/docs/DropDownAccessMethods.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robin\spCoin\SPCOIN-PROJECT-MODULES\spcoin-nextjs-front-end\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5232384-434D-46ED-8655-13939F939AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC0699DA-BC4D-4C97-A503-D0E7E0CB3564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="378">
   <si>
     <t>Panel</t>
   </si>
@@ -1020,18 +1020,6 @@
     <t>backDateTransaction(address,address,uint256,address,uint256,uint256,uint256)</t>
   </si>
   <si>
-    <t>getAgentTransactionCount(address,address,uint256,address,uint256)</t>
-  </si>
-  <si>
-    <t>getRecipientTransactionCount(address,address,uint256)</t>
-  </si>
-  <si>
-    <t>getAgentTransactionAt(address,address,uint256,address,uint256,uint256)</t>
-  </si>
-  <si>
-    <t>getRecipientTransactionAt(address,address,uint256,uint256)</t>
-  </si>
-  <si>
     <t>deleteSponsor(address)</t>
   </si>
   <si>
@@ -1102,13 +1090,88 @@
   </si>
   <si>
     <t>totalInitialSupply()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  getMasterAccountKeys()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  getMasterAccountKeyAt(uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  getAccountKeyCount()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  isAccountActive(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  accountHasActiveLinks(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  getAccountCore(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  getAccountRecord(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  getAccountLinks(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  getRecipientKeys(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  getAgentKeys(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  getRecipientKeyCount(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  getAgentKeyCount(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  getRecipientRateTransactionSetKey(address,address,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  getAgentRateTransactionSetKey(address,address,uint256,address,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  getAgentTransactionCount(address,address,uint256,address,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  getRecipientTransactionCount(address,address,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  getAgentTransactionAt(address,address,uint256,address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  getRecipientTransactionAt(address,address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  getTransactionRecord(uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  getRecipientTransactionIdKeys(address,address,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  getAgentTransactionIdKeys(address,address,uint256,address,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  getRecipientRateTransactionSetKeys(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  getAgentRateTransactionSetKeys(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  getRateTransactionSet(bytes32)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  getRateTransactionSetTransactionIds(bytes32)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1149,6 +1212,11 @@
       <sz val="16"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1219,7 +1287,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1262,6 +1330,7 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1596,571 +1665,763 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD098BC8-8253-4308-BB80-99C559D5DD3D}">
-  <dimension ref="A1:A111"/>
+  <dimension ref="A1:B123"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="99.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="125.53125" customWidth="1"/>
     <col min="2" max="2" width="82.1328125" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="96" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:2" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A1" s="8" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+        <v>351</v>
+      </c>
+      <c r="B1" s="18"/>
+    </row>
+    <row r="2" spans="1:2" ht="24" x14ac:dyDescent="0.65">
       <c r="A2" s="13" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+        <v>335</v>
+      </c>
+      <c r="B2" s="18"/>
+    </row>
+    <row r="3" spans="1:2" ht="24" x14ac:dyDescent="0.65">
       <c r="A3" s="16" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+        <v>344</v>
+      </c>
+      <c r="B3" s="18"/>
+    </row>
+    <row r="4" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A4" s="11" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="B4" s="18"/>
+    </row>
+    <row r="5" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A5" s="11" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="B5" s="18"/>
+    </row>
+    <row r="6" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A6" s="17" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="B6" s="18"/>
+    </row>
+    <row r="7" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A7" s="17" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="B7" s="18"/>
+    </row>
+    <row r="8" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A8" s="17" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="B8" s="18"/>
+    </row>
+    <row r="9" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A9" s="17" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="B9" s="18"/>
+    </row>
+    <row r="10" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A10" s="17" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="B10" s="18"/>
+    </row>
+    <row r="11" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A11" s="17" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="B11" s="18"/>
+    </row>
+    <row r="12" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A12" s="11" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+        <v>352</v>
+      </c>
+      <c r="B12" s="18"/>
+    </row>
+    <row r="13" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A13" s="11" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="B13" s="18"/>
+    </row>
+    <row r="14" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A14" s="11" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" s="9" customFormat="1" ht="20.65" x14ac:dyDescent="0.5">
+      <c r="B14" s="18"/>
+    </row>
+    <row r="15" spans="1:2" s="9" customFormat="1" ht="21" x14ac:dyDescent="0.65">
       <c r="A15" s="11" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="B15" s="18"/>
+    </row>
+    <row r="16" spans="1:2" ht="24" x14ac:dyDescent="0.65">
       <c r="A16" s="15" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+        <v>345</v>
+      </c>
+      <c r="B16" s="18"/>
+    </row>
+    <row r="17" spans="1:2" ht="24" x14ac:dyDescent="0.65">
       <c r="A17" s="12" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+        <v>346</v>
+      </c>
+      <c r="B17" s="18"/>
+    </row>
+    <row r="18" spans="1:2" ht="24" x14ac:dyDescent="0.65">
       <c r="A18" s="13" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+        <v>347</v>
+      </c>
+      <c r="B18" s="18"/>
+    </row>
+    <row r="19" spans="1:2" ht="24" x14ac:dyDescent="0.65">
       <c r="A19" s="16" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+        <v>344</v>
+      </c>
+      <c r="B19" s="18"/>
+    </row>
+    <row r="20" spans="1:2" ht="24" x14ac:dyDescent="0.65">
       <c r="A20" s="12" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+        <v>346</v>
+      </c>
+      <c r="B20" s="18"/>
+    </row>
+    <row r="21" spans="1:2" ht="24" x14ac:dyDescent="0.65">
       <c r="A21" s="15" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+        <v>345</v>
+      </c>
+      <c r="B21" s="18"/>
+    </row>
+    <row r="22" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A22" s="11" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="B22" s="18"/>
+    </row>
+    <row r="23" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A23" s="11" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="B23" s="18"/>
+    </row>
+    <row r="24" spans="1:2" ht="24" x14ac:dyDescent="0.65">
       <c r="A24" s="13" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+        <v>348</v>
+      </c>
+      <c r="B24" s="18"/>
+    </row>
+    <row r="25" spans="1:2" ht="24" x14ac:dyDescent="0.65">
       <c r="A25" s="16" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+        <v>344</v>
+      </c>
+      <c r="B25" s="18"/>
+    </row>
+    <row r="26" spans="1:2" ht="24" x14ac:dyDescent="0.65">
       <c r="A26" s="12" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+        <v>346</v>
+      </c>
+      <c r="B26" s="18"/>
+    </row>
+    <row r="27" spans="1:2" ht="24" x14ac:dyDescent="0.65">
       <c r="A27" s="15" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+        <v>345</v>
+      </c>
+      <c r="B27" s="18"/>
+    </row>
+    <row r="28" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A28" s="11" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="B28" s="18"/>
+    </row>
+    <row r="29" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A29" s="11" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="B29" s="18"/>
+    </row>
+    <row r="30" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A30" s="11" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="B30" s="18"/>
+    </row>
+    <row r="31" spans="1:2" ht="24" x14ac:dyDescent="0.65">
       <c r="A31" s="13" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+        <v>336</v>
+      </c>
+      <c r="B31" s="18"/>
+    </row>
+    <row r="32" spans="1:2" ht="24" x14ac:dyDescent="0.65">
       <c r="A32" s="16" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+        <v>344</v>
+      </c>
+      <c r="B32" s="18"/>
+    </row>
+    <row r="33" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A33" s="17" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="B33" s="18"/>
+    </row>
+    <row r="34" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A34" s="17" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="B34" s="18"/>
+    </row>
+    <row r="35" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A35" s="17" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="B35" s="18"/>
+    </row>
+    <row r="36" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A36" s="17" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="B36" s="18"/>
+    </row>
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A37" s="17" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="B37" s="18"/>
+    </row>
+    <row r="38" spans="1:2" ht="24" x14ac:dyDescent="0.65">
       <c r="A38" s="15" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+        <v>345</v>
+      </c>
+      <c r="B38" s="18"/>
+    </row>
+    <row r="39" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A39" s="17" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="B39" s="18"/>
+    </row>
+    <row r="40" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A40" s="17" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="B40" s="18"/>
+    </row>
+    <row r="41" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A41" s="17" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="B41" s="18"/>
+    </row>
+    <row r="42" spans="1:2" ht="24" x14ac:dyDescent="0.65">
       <c r="A42" s="13" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+        <v>337</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="24" x14ac:dyDescent="0.65">
       <c r="A43" s="16" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+        <v>344</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A44" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A45" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="B45" s="18" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A46" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="B46" s="18" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A47" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A48" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="B48" s="18" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A49" s="17" t="s">
+        <v>302</v>
+      </c>
+      <c r="B49" s="18" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A50" s="17" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A45" s="17" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A46" s="17" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A47" s="17" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A48" s="17" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A49" s="11" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A50" s="11" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="B50" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A51" s="11" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="52" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="B51" s="18" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A52" s="11" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A53" s="15" t="s">
+        <v>306</v>
+      </c>
+      <c r="B52" s="18" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="B53" s="18" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="B54" s="18" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="B55" s="18" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A56" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="B56" s="18"/>
+    </row>
+    <row r="57" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A57" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="B57" s="18"/>
+    </row>
+    <row r="58" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A58" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="B58" s="18"/>
+    </row>
+    <row r="59" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A59" s="14" t="s">
+        <v>344</v>
+      </c>
+      <c r="B59" s="18"/>
+    </row>
+    <row r="60" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A60" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="B60" s="18"/>
+    </row>
+    <row r="61" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A61" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="B61" s="18"/>
+    </row>
+    <row r="62" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A62" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="B62" s="18"/>
+    </row>
+    <row r="63" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A63" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="B63" s="18"/>
+    </row>
+    <row r="64" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A64" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="B64" s="18"/>
+    </row>
+    <row r="65" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A65" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="B65" s="18"/>
+    </row>
+    <row r="66" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A66" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="B66" s="18"/>
+    </row>
+    <row r="67" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A67" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="B67" s="18"/>
+    </row>
+    <row r="68" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A68" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="B68" s="18"/>
+    </row>
+    <row r="69" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A69" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="B69" s="18"/>
+    </row>
+    <row r="70" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A70" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="B70" s="18"/>
+    </row>
+    <row r="71" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A71" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="B71" s="18"/>
+    </row>
+    <row r="72" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A72" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="B72" s="18"/>
+    </row>
+    <row r="73" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A73" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="B73" s="18"/>
+    </row>
+    <row r="74" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A74" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="B74" s="18"/>
+    </row>
+    <row r="75" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A75" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="B75" s="18"/>
+    </row>
+    <row r="76" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A76" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="B76" s="18"/>
+    </row>
+    <row r="77" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A77" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="B77" s="18"/>
+    </row>
+    <row r="78" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A78" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="B78" s="18"/>
+    </row>
+    <row r="79" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A79" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="B79" s="18"/>
+    </row>
+    <row r="80" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A80" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="B80" s="18"/>
+    </row>
+    <row r="81" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A81" s="13" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="54" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A54" s="12" t="s">
+      <c r="B81" s="18"/>
+    </row>
+    <row r="82" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A82" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="B82" s="18"/>
+    </row>
+    <row r="83" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A83" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="B83" s="18"/>
+    </row>
+    <row r="84" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A84" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="B84" s="18"/>
+    </row>
+    <row r="85" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A85" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="B85" s="18"/>
+    </row>
+    <row r="86" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A86" s="13" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="55" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A55" s="13" t="s">
+      <c r="B86" s="18"/>
+    </row>
+    <row r="87" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A87" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="B87" s="18"/>
+    </row>
+    <row r="88" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A88" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="B88" s="18"/>
+    </row>
+    <row r="89" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A89" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="B89" s="18"/>
+    </row>
+    <row r="90" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A90" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="B90" s="18"/>
+    </row>
+    <row r="91" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A91" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="B91" s="18"/>
+    </row>
+    <row r="92" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A92" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="B92" s="18"/>
+    </row>
+    <row r="93" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A93" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="B93" s="18"/>
+    </row>
+    <row r="94" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A94" s="13" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="56" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A56" s="14" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A57" s="11" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A58" s="11" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A59" s="15" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A60" s="11" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A61" s="13" t="s">
+      <c r="B94" s="18"/>
+    </row>
+    <row r="95" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A95" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="B95" s="18"/>
+    </row>
+    <row r="96" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A96" s="18" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A97" s="18" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A98" s="18" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A99" s="18" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A100" s="18" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A101" s="18" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A102" s="18" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A103" s="18" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A104" s="18" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A105" s="18" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A106" s="18" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A107" s="18" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A108" s="18" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A109" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="B109" s="18"/>
+    </row>
+    <row r="110" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A110" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="B110" s="18"/>
+    </row>
+    <row r="111" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A111" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="B111" s="18"/>
+    </row>
+    <row r="112" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A112" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="B112" s="18"/>
+    </row>
+    <row r="113" spans="1:2" ht="41.25" x14ac:dyDescent="0.65">
+      <c r="A113" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="B113" s="18"/>
+    </row>
+    <row r="114" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A114" s="13" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="62" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A62" s="16" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A63" s="11" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A64" s="15" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A65" s="12" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A66" s="13" t="s">
+      <c r="B114" s="18"/>
+    </row>
+    <row r="115" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A115" s="16" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="67" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A67" s="16" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A68" s="11" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A69" s="11" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A70" s="11" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A71" s="15" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A72" s="11" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A73" s="13" t="s">
+      <c r="B115" s="18"/>
+    </row>
+    <row r="116" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A116" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="B116" s="18"/>
+    </row>
+    <row r="117" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A117" s="15" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="74" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A74" s="16" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" ht="41.25" x14ac:dyDescent="0.45">
-      <c r="A75" s="11" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A76" s="10" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A77" s="12" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A78" s="13" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A79" s="16" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A80" s="11" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A81" s="15" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A82" s="12" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A83" s="13" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A84" s="16" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A85" s="11" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A86" s="15" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A87" s="11" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A88" s="11" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A89" s="11" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A90" s="11" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A91" s="13" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A92" s="16" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" ht="41.25" x14ac:dyDescent="0.45">
-      <c r="A93" s="11" t="s">
+      <c r="B117" s="18"/>
+    </row>
+    <row r="118" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A118" s="11" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="94" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A94" s="11" t="s">
+      <c r="B118" s="18"/>
+    </row>
+    <row r="119" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A119" s="11" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="95" spans="1:1" ht="41.25" x14ac:dyDescent="0.45">
-      <c r="A95" s="11" t="s">
+      <c r="B119" s="18"/>
+    </row>
+    <row r="120" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A120" s="11" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="96" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A96" s="11" t="s">
+      <c r="B120" s="18"/>
+    </row>
+    <row r="121" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A121" s="11" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="97" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A97" s="15" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A98" s="11" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A99" s="11" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" ht="41.25" x14ac:dyDescent="0.45">
-      <c r="A100" s="11" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" ht="41.25" x14ac:dyDescent="0.45">
-      <c r="A101" s="11" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A102" s="13" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A103" s="16" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A104" s="12" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" ht="24" x14ac:dyDescent="0.45">
-      <c r="A105" s="15" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A106" s="11" t="s">
+      <c r="B121" s="18"/>
+    </row>
+    <row r="122" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A122" s="11" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="107" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A107" s="11" t="s">
+      <c r="B122" s="18"/>
+    </row>
+    <row r="123" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A123" s="11" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="108" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A108" s="11" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A109" s="11" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A110" s="11" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
-      <c r="A111" s="11" t="s">
-        <v>338</v>
-      </c>
+      <c r="B123" s="18"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B44:B55">
+    <sortCondition ref="B44:B55"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/docs/DropDownAccessMethods.xlsx
+++ b/docs/DropDownAccessMethods.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robin\spCoin\SPCOIN-PROJECT-MODULES\spcoin-nextjs-front-end\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC0699DA-BC4D-4C97-A503-D0E7E0CB3564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14EFC976-5E0E-46C1-96A3-A332C961AC48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1309" uniqueCount="364">
   <si>
     <t>Panel</t>
   </si>
@@ -906,12 +906,6 @@
     <t>version()</t>
   </si>
   <si>
-    <t>init()</t>
-  </si>
-  <si>
-    <t>initToken(string,string,uint,uint)</t>
-  </si>
-  <si>
     <t>owner()</t>
   </si>
   <si>
@@ -936,42 +930,9 @@
     <t>setAgentRateRange(uint256,uint256)</t>
   </si>
   <si>
-    <t>getMasterAccountKeys()</t>
-  </si>
-  <si>
-    <t>getMasterAccountKeyAt(uint256)</t>
-  </si>
-  <si>
-    <t>getAccountKeyCount()</t>
-  </si>
-  <si>
-    <t>getAccountCore(address)</t>
-  </si>
-  <si>
-    <t>getAccountLinks(address)</t>
-  </si>
-  <si>
-    <t>getRecipientKeys(address)</t>
-  </si>
-  <si>
-    <t>getAgentKeys(address)</t>
-  </si>
-  <si>
-    <t>getRecipientKeyCount(address)</t>
-  </si>
-  <si>
-    <t>getAgentKeyCount(address)</t>
-  </si>
-  <si>
-    <t>getRecipientRecordCore(address,address)</t>
-  </si>
-  <si>
     <t>getRecipientRateList(address,address)</t>
   </si>
   <si>
-    <t>getRecipientTransactionCore(address,address,uint256)</t>
-  </si>
-  <si>
     <t>getRecipientRateAgentList(address,address,uint256)</t>
   </si>
   <si>
@@ -981,15 +942,9 @@
     <t>getAgentRateList(address,address,uint256,address)</t>
   </si>
   <si>
-    <t>getAgentTransactionCore(address,address,uint256,address,uint256)</t>
-  </si>
-  <si>
     <t>addRecipient(address,address)</t>
   </si>
   <si>
-    <t>addAgent(address,address,uint256,address)</t>
-  </si>
-  <si>
     <t>calculateStakingRewards(uint256,uint256,uint256,uint256)</t>
   </si>
   <si>
@@ -1104,12 +1059,6 @@
     <t xml:space="preserve">  isAccountActive(address)</t>
   </si>
   <si>
-    <t xml:space="preserve">  accountHasActiveLinks(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  getAccountCore(address)</t>
-  </si>
-  <si>
     <t xml:space="preserve">  getAccountRecord(address)</t>
   </si>
   <si>
@@ -1165,13 +1114,22 @@
   </si>
   <si>
     <t xml:space="preserve">  getRateTransactionSetTransactionIds(bytes32)</t>
+  </si>
+  <si>
+    <t>getRecipientRecord(address,address)</t>
+  </si>
+  <si>
+    <t>getRecipientTransaction(address,address,uint256)</t>
+  </si>
+  <si>
+    <t>getAgentTransaction(address,address,uint256,address,uint256)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1217,6 +1175,17 @@
       <sz val="16"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="Cascadia Mono SemiLight"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Cascadia Mono SemiLight"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1287,7 +1256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1306,9 +1275,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1331,6 +1297,21 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1665,10 +1646,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD098BC8-8253-4308-BB80-99C559D5DD3D}">
-  <dimension ref="A1:B123"/>
+  <dimension ref="A1:B110"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="125.53125" customWidth="1"/>
+    <col min="1" max="1" width="131.19921875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="82.1328125" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="96" customWidth="1"/>
@@ -1676,752 +1657,639 @@
   <sheetData>
     <row r="1" spans="1:2" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A1" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="B1" s="18"/>
+        <v>336</v>
+      </c>
+      <c r="B1" s="17"/>
     </row>
     <row r="2" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A2" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="B2" s="18"/>
+      <c r="A2" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="B2" s="17"/>
     </row>
     <row r="3" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A3" s="16" t="s">
-        <v>344</v>
-      </c>
-      <c r="B3" s="18"/>
+      <c r="A3" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="B3" s="17"/>
     </row>
     <row r="4" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="16" t="s">
         <v>254</v>
       </c>
-      <c r="B4" s="18"/>
+      <c r="B4" s="17"/>
     </row>
     <row r="5" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="16" t="s">
         <v>255</v>
       </c>
-      <c r="B5" s="18"/>
+      <c r="B5" s="17"/>
     </row>
     <row r="6" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="16" t="s">
         <v>256</v>
       </c>
-      <c r="B6" s="18"/>
+      <c r="B6" s="17"/>
     </row>
     <row r="7" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="16" t="s">
         <v>257</v>
       </c>
-      <c r="B7" s="18"/>
+      <c r="B7" s="17"/>
     </row>
     <row r="8" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="16" t="s">
         <v>290</v>
       </c>
-      <c r="B8" s="18"/>
+      <c r="B8" s="17"/>
     </row>
     <row r="9" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="B9" s="18"/>
+      <c r="B9" s="17"/>
     </row>
     <row r="10" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="16" t="s">
         <v>259</v>
       </c>
-      <c r="B10" s="18"/>
+      <c r="B10" s="17"/>
     </row>
     <row r="11" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="16" t="s">
         <v>260</v>
       </c>
-      <c r="B11" s="18"/>
+      <c r="B11" s="17"/>
     </row>
     <row r="12" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A12" s="11" t="s">
-        <v>352</v>
-      </c>
-      <c r="B12" s="18"/>
+      <c r="A12" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="B12" s="17"/>
     </row>
     <row r="13" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="16" t="s">
         <v>261</v>
       </c>
-      <c r="B13" s="18"/>
+      <c r="B13" s="17"/>
     </row>
     <row r="14" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="B14" s="18"/>
+      <c r="B14" s="17"/>
     </row>
     <row r="15" spans="1:2" s="9" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="B15" s="18"/>
+      <c r="B15" s="17"/>
     </row>
     <row r="16" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A16" s="15" t="s">
-        <v>345</v>
-      </c>
-      <c r="B16" s="18"/>
+      <c r="A16" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="B16" s="17"/>
     </row>
     <row r="17" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A17" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="B17" s="18"/>
+      <c r="A17" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="B17" s="17"/>
     </row>
     <row r="18" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A18" s="13" t="s">
-        <v>347</v>
-      </c>
-      <c r="B18" s="18"/>
+      <c r="A18" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="B18" s="17"/>
     </row>
     <row r="19" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A19" s="16" t="s">
-        <v>344</v>
-      </c>
-      <c r="B19" s="18"/>
+      <c r="A19" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="B19" s="17"/>
     </row>
     <row r="20" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A20" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="B20" s="18"/>
-    </row>
-    <row r="21" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A21" s="15" t="s">
-        <v>345</v>
+      <c r="A20" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="B20" s="17"/>
+    </row>
+    <row r="21" spans="1:2" s="19" customFormat="1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A21" s="16" t="s">
+        <v>264</v>
       </c>
       <c r="B21" s="18"/>
     </row>
-    <row r="22" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A22" s="11" t="s">
+    <row r="22" spans="1:2" s="19" customFormat="1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A22" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="B22" s="18"/>
+    </row>
+    <row r="23" spans="1:2" s="19" customFormat="1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A23" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="B23" s="18"/>
+    </row>
+    <row r="24" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A24" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="B24" s="17"/>
+    </row>
+    <row r="25" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A25" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="B25" s="17"/>
+    </row>
+    <row r="26" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A26" s="16" t="s">
         <v>291</v>
       </c>
-      <c r="B22" s="18"/>
-    </row>
-    <row r="23" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A23" s="11" t="s">
+      <c r="B26" s="17"/>
+    </row>
+    <row r="27" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A27" s="16" t="s">
         <v>292</v>
       </c>
-      <c r="B23" s="18"/>
-    </row>
-    <row r="24" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A24" s="13" t="s">
-        <v>348</v>
-      </c>
-      <c r="B24" s="18"/>
-    </row>
-    <row r="25" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A25" s="16" t="s">
-        <v>344</v>
-      </c>
-      <c r="B25" s="18"/>
-    </row>
-    <row r="26" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A26" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="B26" s="18"/>
-    </row>
-    <row r="27" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A27" s="15" t="s">
-        <v>345</v>
-      </c>
-      <c r="B27" s="18"/>
+      <c r="B27" s="17"/>
     </row>
     <row r="28" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A28" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="B28" s="18"/>
+      <c r="A28" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="B28" s="17"/>
     </row>
     <row r="29" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A29" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="B29" s="18"/>
+      <c r="A29" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="B29" s="17"/>
     </row>
     <row r="30" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A30" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="B30" s="18"/>
+      <c r="A30" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="B30" s="17"/>
     </row>
     <row r="31" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A31" s="13" t="s">
-        <v>336</v>
-      </c>
-      <c r="B31" s="18"/>
-    </row>
-    <row r="32" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A31" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="B31" s="17"/>
+    </row>
+    <row r="32" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A32" s="16" t="s">
-        <v>344</v>
-      </c>
-      <c r="B32" s="18"/>
+        <v>294</v>
+      </c>
+      <c r="B32" s="17"/>
     </row>
     <row r="33" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A33" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="B33" s="18"/>
+      <c r="A33" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="B33" s="17"/>
     </row>
     <row r="34" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A34" s="17" t="s">
-        <v>294</v>
-      </c>
-      <c r="B34" s="18"/>
-    </row>
-    <row r="35" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A35" s="17" t="s">
-        <v>295</v>
-      </c>
-      <c r="B35" s="18"/>
-    </row>
-    <row r="36" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A36" s="17" t="s">
-        <v>297</v>
-      </c>
-      <c r="B36" s="18"/>
+      <c r="A34" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="B34" s="17"/>
+    </row>
+    <row r="35" spans="1:2" ht="24" x14ac:dyDescent="0.45">
+      <c r="A35" s="12" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="24" x14ac:dyDescent="0.45">
+      <c r="A36" s="15" t="s">
+        <v>329</v>
+      </c>
     </row>
     <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A37" s="17" t="s">
-        <v>299</v>
-      </c>
-      <c r="B37" s="18"/>
-    </row>
-    <row r="38" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A38" s="15" t="s">
-        <v>345</v>
-      </c>
-      <c r="B38" s="18"/>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A38" s="17" t="s">
+        <v>343</v>
+      </c>
     </row>
     <row r="39" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A39" s="17" t="s">
-        <v>296</v>
-      </c>
-      <c r="B39" s="18"/>
+        <v>342</v>
+      </c>
     </row>
     <row r="40" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A40" s="17" t="s">
-        <v>298</v>
-      </c>
-      <c r="B40" s="18"/>
+        <v>347</v>
+      </c>
     </row>
     <row r="41" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A41" s="17" t="s">
-        <v>300</v>
-      </c>
-      <c r="B41" s="18"/>
-    </row>
-    <row r="42" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A42" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="B42" s="18" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A43" s="16" t="s">
-        <v>344</v>
-      </c>
-      <c r="B43" s="18" t="s">
-        <v>344</v>
+        <v>345</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A42" s="17" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A43" s="17" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A44" s="17" t="s">
-        <v>304</v>
-      </c>
-      <c r="B44" s="18" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A45" s="17" t="s">
-        <v>303</v>
-      </c>
-      <c r="B45" s="18" t="s">
-        <v>358</v>
+        <v>344</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A46" s="17" t="s">
-        <v>305</v>
-      </c>
-      <c r="B46" s="18" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A47" s="11" t="s">
-        <v>309</v>
-      </c>
-      <c r="B47" s="18" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="24" x14ac:dyDescent="0.45">
+      <c r="A47" s="14" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="24" x14ac:dyDescent="0.65">
       <c r="A48" s="11" t="s">
-        <v>307</v>
-      </c>
-      <c r="B48" s="18" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A49" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="B48" s="17"/>
+    </row>
+    <row r="49" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A49" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="B49" s="17"/>
+    </row>
+    <row r="50" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A50" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="B50" s="17"/>
+    </row>
+    <row r="51" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A51" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="B51" s="17"/>
+    </row>
+    <row r="52" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A52" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="B52" s="17"/>
+    </row>
+    <row r="53" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A53" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="B53" s="17"/>
+    </row>
+    <row r="54" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A54" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="B54" s="17"/>
+    </row>
+    <row r="55" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A55" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="B55" s="17"/>
+    </row>
+    <row r="56" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A56" s="17" t="s">
+        <v>361</v>
+      </c>
+      <c r="B56" s="17"/>
+    </row>
+    <row r="57" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A57" s="17" t="s">
+        <v>362</v>
+      </c>
+      <c r="B57" s="17"/>
+    </row>
+    <row r="58" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A58" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="B58" s="17"/>
+    </row>
+    <row r="59" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A59" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="B59" s="17"/>
+    </row>
+    <row r="60" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A60" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="B60" s="17"/>
+    </row>
+    <row r="61" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A61" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="B61" s="17"/>
+    </row>
+    <row r="62" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A62" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="B62" s="17"/>
+    </row>
+    <row r="63" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A63" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="B63" s="17"/>
+    </row>
+    <row r="64" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A64" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="B49" s="18" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A50" s="17" t="s">
-        <v>301</v>
-      </c>
-      <c r="B50" s="18" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A51" s="11" t="s">
-        <v>308</v>
-      </c>
-      <c r="B51" s="18" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A52" s="11" t="s">
-        <v>306</v>
-      </c>
-      <c r="B52" s="18" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="B53" s="18" t="s">
+      <c r="B64" s="17"/>
+    </row>
+    <row r="65" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A65" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="B65" s="17"/>
+    </row>
+    <row r="66" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A66" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="B66" s="17"/>
+    </row>
+    <row r="67" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A67" s="10" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="B54" s="18" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="B55" s="18" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A56" s="15" t="s">
-        <v>345</v>
-      </c>
-      <c r="B56" s="18"/>
-    </row>
-    <row r="57" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A57" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="B57" s="18"/>
-    </row>
-    <row r="58" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A58" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="B58" s="18"/>
-    </row>
-    <row r="59" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A59" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="B59" s="18"/>
-    </row>
-    <row r="60" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A60" s="11" t="s">
-        <v>310</v>
-      </c>
-      <c r="B60" s="18"/>
-    </row>
-    <row r="61" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A61" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="B61" s="18"/>
-    </row>
-    <row r="62" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A62" s="15" t="s">
-        <v>345</v>
-      </c>
-      <c r="B62" s="18"/>
-    </row>
-    <row r="63" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A63" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="B63" s="18"/>
-    </row>
-    <row r="64" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A64" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="B64" s="18"/>
-    </row>
-    <row r="65" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A65" s="16" t="s">
-        <v>344</v>
-      </c>
-      <c r="B65" s="18"/>
-    </row>
-    <row r="66" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A66" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="B66" s="18"/>
-    </row>
-    <row r="67" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A67" s="15" t="s">
-        <v>345</v>
-      </c>
-      <c r="B67" s="18"/>
+      <c r="B67" s="17"/>
     </row>
     <row r="68" spans="1:2" ht="24" x14ac:dyDescent="0.65">
       <c r="A68" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="B68" s="18"/>
+        <v>334</v>
+      </c>
+      <c r="B68" s="17"/>
     </row>
     <row r="69" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A69" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="B69" s="18"/>
-    </row>
-    <row r="70" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A70" s="16" t="s">
-        <v>344</v>
-      </c>
-      <c r="B70" s="18"/>
-    </row>
-    <row r="71" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A71" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="B71" s="18"/>
-    </row>
-    <row r="72" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A69" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="B69" s="17"/>
+    </row>
+    <row r="70" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A70" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="B70" s="17"/>
+    </row>
+    <row r="71" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A71" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="B71" s="17"/>
+    </row>
+    <row r="72" spans="1:2" ht="24" x14ac:dyDescent="0.65">
       <c r="A72" s="11" t="s">
-        <v>314</v>
-      </c>
-      <c r="B72" s="18"/>
-    </row>
-    <row r="73" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A73" s="11" t="s">
-        <v>315</v>
-      </c>
-      <c r="B73" s="18"/>
+        <v>331</v>
+      </c>
+      <c r="B72" s="17"/>
+    </row>
+    <row r="73" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A73" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="B73" s="17"/>
     </row>
     <row r="74" spans="1:2" ht="24" x14ac:dyDescent="0.65">
       <c r="A74" s="15" t="s">
-        <v>345</v>
-      </c>
-      <c r="B74" s="18"/>
+        <v>329</v>
+      </c>
+      <c r="B74" s="17"/>
     </row>
     <row r="75" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A75" s="11" t="s">
+      <c r="A75" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="B75" s="17"/>
+    </row>
+    <row r="76" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A76" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="B76" s="17"/>
+    </row>
+    <row r="77" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A77" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="B77" s="17"/>
+    </row>
+    <row r="78" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A78" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="B78" s="17"/>
+    </row>
+    <row r="79" spans="1:2" ht="23.25" x14ac:dyDescent="0.65">
+      <c r="A79" s="20" t="s">
+        <v>308</v>
+      </c>
+      <c r="B79" s="17"/>
+    </row>
+    <row r="80" spans="1:2" ht="23.25" x14ac:dyDescent="0.65">
+      <c r="A80" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="B80" s="17"/>
+    </row>
+    <row r="81" spans="1:2" ht="23.25" x14ac:dyDescent="0.65">
+      <c r="A81" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="B81" s="17"/>
+    </row>
+    <row r="82" spans="1:2" ht="23.25" x14ac:dyDescent="0.65">
+      <c r="A82" s="22" t="s">
+        <v>329</v>
+      </c>
+      <c r="B82" s="17"/>
+    </row>
+    <row r="83" spans="1:2" ht="23.25" x14ac:dyDescent="0.75">
+      <c r="A83" s="23" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="23.25" x14ac:dyDescent="0.75">
+      <c r="A84" s="23" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="23.25" x14ac:dyDescent="0.75">
+      <c r="A85" s="23" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" ht="23.25" x14ac:dyDescent="0.75">
+      <c r="A86" s="23" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" ht="23.25" x14ac:dyDescent="0.75">
+      <c r="A87" s="23" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="23.25" x14ac:dyDescent="0.75">
+      <c r="A88" s="23" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" ht="23.25" x14ac:dyDescent="0.75">
+      <c r="A89" s="23" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" ht="23.25" x14ac:dyDescent="0.75">
+      <c r="A90" s="23" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" ht="23.25" x14ac:dyDescent="0.75">
+      <c r="A91" s="23" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="23.25" x14ac:dyDescent="0.75">
+      <c r="A92" s="23" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="23.25" x14ac:dyDescent="0.75">
+      <c r="A93" s="23" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="23.25" x14ac:dyDescent="0.75">
+      <c r="A94" s="23" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="23.25" x14ac:dyDescent="0.75">
+      <c r="A95" s="23" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" ht="23.25" x14ac:dyDescent="0.65">
+      <c r="A96" s="24" t="s">
+        <v>330</v>
+      </c>
+      <c r="B96" s="17"/>
+    </row>
+    <row r="97" spans="1:2" ht="23.25" x14ac:dyDescent="0.65">
+      <c r="A97" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="B97" s="17"/>
+    </row>
+    <row r="98" spans="1:2" ht="23.25" x14ac:dyDescent="0.65">
+      <c r="A98" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="B98" s="17"/>
+    </row>
+    <row r="99" spans="1:2" ht="23.25" x14ac:dyDescent="0.65">
+      <c r="A99" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="B99" s="17"/>
+    </row>
+    <row r="100" spans="1:2" ht="23.25" x14ac:dyDescent="0.65">
+      <c r="A100" s="20" t="s">
+        <v>313</v>
+      </c>
+      <c r="B100" s="17"/>
+    </row>
+    <row r="101" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A101" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="B101" s="17"/>
+    </row>
+    <row r="102" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A102" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="B102" s="17"/>
+    </row>
+    <row r="103" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A103" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="B103" s="17"/>
+    </row>
+    <row r="104" spans="1:2" ht="24" x14ac:dyDescent="0.65">
+      <c r="A104" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="B104" s="17"/>
+    </row>
+    <row r="105" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A105" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="B105" s="17"/>
+    </row>
+    <row r="106" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A106" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="B106" s="17"/>
+    </row>
+    <row r="107" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A107" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="B107" s="17"/>
+    </row>
+    <row r="108" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A108" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="B108" s="17"/>
+    </row>
+    <row r="109" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A109" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="B75" s="18"/>
-    </row>
-    <row r="76" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A76" s="13" t="s">
-        <v>341</v>
-      </c>
-      <c r="B76" s="18"/>
-    </row>
-    <row r="77" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A77" s="16" t="s">
-        <v>344</v>
-      </c>
-      <c r="B77" s="18"/>
-    </row>
-    <row r="78" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A78" s="11" t="s">
-        <v>316</v>
-      </c>
-      <c r="B78" s="18"/>
-    </row>
-    <row r="79" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A79" s="10" t="s">
-        <v>345</v>
-      </c>
-      <c r="B79" s="18"/>
-    </row>
-    <row r="80" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A80" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="B80" s="18"/>
-    </row>
-    <row r="81" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A81" s="13" t="s">
-        <v>349</v>
-      </c>
-      <c r="B81" s="18"/>
-    </row>
-    <row r="82" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A82" s="16" t="s">
-        <v>344</v>
-      </c>
-      <c r="B82" s="18"/>
-    </row>
-    <row r="83" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A83" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="B83" s="18"/>
-    </row>
-    <row r="84" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A84" s="15" t="s">
-        <v>345</v>
-      </c>
-      <c r="B84" s="18"/>
-    </row>
-    <row r="85" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A85" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="B85" s="18"/>
-    </row>
-    <row r="86" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A86" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="B86" s="18"/>
-    </row>
-    <row r="87" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A87" s="16" t="s">
-        <v>344</v>
-      </c>
-      <c r="B87" s="18"/>
-    </row>
-    <row r="88" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A88" s="11" t="s">
+      <c r="B109" s="17"/>
+    </row>
+    <row r="110" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A110" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="B88" s="18"/>
-    </row>
-    <row r="89" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A89" s="15" t="s">
-        <v>345</v>
-      </c>
-      <c r="B89" s="18"/>
-    </row>
-    <row r="90" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A90" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="B90" s="18"/>
-    </row>
-    <row r="91" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A91" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="B91" s="18"/>
-    </row>
-    <row r="92" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A92" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="B92" s="18"/>
-    </row>
-    <row r="93" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A93" s="11" t="s">
-        <v>324</v>
-      </c>
-      <c r="B93" s="18"/>
-    </row>
-    <row r="94" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A94" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="B94" s="18"/>
-    </row>
-    <row r="95" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A95" s="16" t="s">
-        <v>344</v>
-      </c>
-      <c r="B95" s="18"/>
-    </row>
-    <row r="96" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A96" s="18" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A97" s="18" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A98" s="18" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A99" s="18" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A100" s="18" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A101" s="18" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A102" s="18" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A103" s="18" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A104" s="18" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A105" s="18" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A106" s="18" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A107" s="18" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A108" s="18" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A109" s="15" t="s">
-        <v>345</v>
-      </c>
-      <c r="B109" s="18"/>
-    </row>
-    <row r="110" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A110" s="11" t="s">
-        <v>325</v>
-      </c>
-      <c r="B110" s="18"/>
-    </row>
-    <row r="111" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A111" s="11" t="s">
-        <v>326</v>
-      </c>
-      <c r="B111" s="18"/>
-    </row>
-    <row r="112" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A112" s="11" t="s">
-        <v>327</v>
-      </c>
-      <c r="B112" s="18"/>
-    </row>
-    <row r="113" spans="1:2" ht="41.25" x14ac:dyDescent="0.65">
-      <c r="A113" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="B113" s="18"/>
-    </row>
-    <row r="114" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A114" s="13" t="s">
-        <v>343</v>
-      </c>
-      <c r="B114" s="18"/>
-    </row>
-    <row r="115" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A115" s="16" t="s">
-        <v>344</v>
-      </c>
-      <c r="B115" s="18"/>
-    </row>
-    <row r="116" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A116" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="B116" s="18"/>
-    </row>
-    <row r="117" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A117" s="15" t="s">
-        <v>345</v>
-      </c>
-      <c r="B117" s="18"/>
-    </row>
-    <row r="118" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A118" s="11" t="s">
-        <v>329</v>
-      </c>
-      <c r="B118" s="18"/>
-    </row>
-    <row r="119" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A119" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="B119" s="18"/>
-    </row>
-    <row r="120" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A120" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="B120" s="18"/>
-    </row>
-    <row r="121" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A121" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="B121" s="18"/>
-    </row>
-    <row r="122" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A122" s="11" t="s">
-        <v>333</v>
-      </c>
-      <c r="B122" s="18"/>
-    </row>
-    <row r="123" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A123" s="11" t="s">
-        <v>334</v>
-      </c>
-      <c r="B123" s="18"/>
+      <c r="B110" s="17"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B44:B55">
-    <sortCondition ref="B44:B55"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/docs/DropDownAccessMethods.xlsx
+++ b/docs/DropDownAccessMethods.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robin\spCoin\SPCOIN-PROJECT-MODULES\spcoin-nextjs-front-end\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14EFC976-5E0E-46C1-96A3-A332C961AC48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2430359B-5B81-48E0-9362-A03FED92817B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1309" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="388">
   <si>
     <t>Panel</t>
   </si>
@@ -930,21 +930,6 @@
     <t>setAgentRateRange(uint256,uint256)</t>
   </si>
   <si>
-    <t>getRecipientRateList(address,address)</t>
-  </si>
-  <si>
-    <t>getRecipientRateAgentList(address,address,uint256)</t>
-  </si>
-  <si>
-    <t>getAgentTotalRecipient(address,address,uint256,address)</t>
-  </si>
-  <si>
-    <t>getAgentRateList(address,address,uint256,address)</t>
-  </si>
-  <si>
-    <t>addRecipient(address,address)</t>
-  </si>
-  <si>
     <t>calculateStakingRewards(uint256,uint256,uint256,uint256)</t>
   </si>
   <si>
@@ -963,15 +948,6 @@
     <t>updateRecipientAccountRewards(address)</t>
   </si>
   <si>
-    <t>addSponsorship(address,uint,address,uint,string,string)</t>
-  </si>
-  <si>
-    <t>addRecipientTransaction(address,address,uint,string,string)</t>
-  </si>
-  <si>
-    <t>addAgentTransaction(address,address,uint,address,uint,string,string)</t>
-  </si>
-  <si>
     <t>backDateTransaction(address,address,uint256,address,uint256,uint256,uint256)</t>
   </si>
   <si>
@@ -1041,95 +1017,191 @@
     <t>RewardsManager.sol</t>
   </si>
   <si>
-    <t>Exported On Chain Methods</t>
-  </si>
-  <si>
     <t>totalInitialSupply()</t>
   </si>
   <si>
-    <t xml:space="preserve">  getMasterAccountKeys()</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  getMasterAccountKeyAt(uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  getAccountKeyCount()</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  isAccountActive(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  getAccountRecord(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  getAccountLinks(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  getRecipientKeys(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  getAgentKeys(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  getRecipientKeyCount(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  getAgentKeyCount(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  getRecipientRateTransactionSetKey(address,address,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  getAgentRateTransactionSetKey(address,address,uint256,address,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  getAgentTransactionCount(address,address,uint256,address,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  getRecipientTransactionCount(address,address,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  getAgentTransactionAt(address,address,uint256,address,uint256,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  getRecipientTransactionAt(address,address,uint256,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  getTransactionRecord(uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  getRecipientTransactionIdKeys(address,address,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  getAgentTransactionIdKeys(address,address,uint256,address,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  getRecipientRateTransactionSetKeys(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  getAgentRateTransactionSetKeys(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  getRateTransactionSet(bytes32)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  getRateTransactionSetTransactionIds(bytes32)</t>
-  </si>
-  <si>
-    <t>getRecipientRecord(address,address)</t>
-  </si>
-  <si>
-    <t>getRecipientTransaction(address,address,uint256)</t>
-  </si>
-  <si>
     <t>getAgentTransaction(address,address,uint256,address,uint256)</t>
+  </si>
+  <si>
+    <t>addSponsorship(address,uint256,address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t>addRecipientTransaction(address,address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t>addAgentTransaction(address,address,uint256,address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> setAgentRateRange(uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> setAgentRateIncrement(uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getRecipientRateIncrement()</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAgentRateRange()</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAgentRateIncrement()</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getMasterAccountMetaData()</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getMasterAccountKeys()</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getMasterAccountKeysPage(uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getMasterAccountKeyAt(uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAccountCore(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAccountLinks(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAccountRecord(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getRecipientKeys(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getRecipientKeysPage(address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAgentKeys(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAgentKeysPage(address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getRecipientRecord(address,address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getRecipientRateList(address,address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getRecipientRateListPage(address,address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getRecipientTransaction(address,address,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getRecipientRateAgentList(address,address,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getRecipientRateAgentListPage(address,address,uint256,uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAgentTotalRecipient(address,address,uint256,address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAgentRateList(address,address,uint256,address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAgentRateListPage(address,address,uint256,address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getRecipientRateTransactionSetKey(address,address,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAgentRateTransactionSetKey(address,address,uint256,address,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAgentTransactionCount(address,address,uint256,address,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getRecipientTransactionCount(address,address,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAgentTransactionAt(address,address,uint256,address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getRecipientTransactionAt(address,address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getTransactionRecord(uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getRecipientTransactionIdKeys(address,address,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAgentTransactionIdKeys(address,address,uint256,address,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getRecipientRateTransactionSetKeys(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getRecipientRateTransactionSetKeysPage(address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAgentRateTransactionSetKeys(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getAgentRateTransactionSetKeysPage(address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getSponsorRecipientRateTransactionSetKeys(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getSponsorRecipientRateTransactionSetKeysPage(address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getSponsorAgentRateTransactionSetKeys(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getSponsorAgentRateTransactionSetKeysPage(address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getSponsorRateTransactionSetKeys(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getSponsorContainerRecipientKeys(address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getSponsorContainerRecipientKeysPage(address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getSponsorRecipientBoxRecipientRateTransactionSetKeys(address,address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getSponsorRecipientBoxRecipientRateTransactionSetKeysPage(address,address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getSponsorRecipientBoxAgentRateTransactionSetKeys(address,address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getSponsorRecipientBoxAgentRateTransactionSetKeysPage(address,address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getSponsorRecipientBoxRateTransactionSetKeys(address,address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getRateTransactionSet(bytes32)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getRateTransactionSetTransactionIds(bytes32)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> getRateTransactionSetTransactionIdsPage(bytes32,uint256,uint256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> isActiveAccount(address)</t>
+  </si>
+  <si>
+    <t>Expo+A1:A15rted On Chain Methods</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1186,6 +1258,11 @@
       <sz val="16"/>
       <name val="Cascadia Mono SemiLight"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1256,7 +1333,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1297,7 +1374,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -1308,10 +1384,13 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1646,650 +1725,841 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD098BC8-8253-4308-BB80-99C559D5DD3D}">
-  <dimension ref="A1:B110"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:B188"/>
+  <sheetFormatPr defaultRowHeight="20.65" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="131.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="82.1328125" customWidth="1"/>
+    <col min="2" max="2" width="82.1328125" style="24" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="96" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A1" s="8" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+      <c r="A2" s="12" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+      <c r="A3" s="15" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A4" s="16" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A5" s="16" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A6" s="16" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A7" s="16" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A8" s="16" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A9" s="16" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A10" s="16" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A11" s="16" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A12" s="16" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A13" s="16" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A14" s="16" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A15" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="B15" s="24"/>
+    </row>
+    <row r="16" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+      <c r="A16" s="14" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+      <c r="A17" s="11" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+      <c r="A18" s="12" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+      <c r="A19" s="15" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A20" s="24" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" s="18" customFormat="1" ht="24" x14ac:dyDescent="0.6">
+      <c r="A21" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="B21" s="24"/>
+    </row>
+    <row r="22" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A22" s="24" t="s">
+        <v>323</v>
+      </c>
+      <c r="B22" s="24"/>
+    </row>
+    <row r="23" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A23"/>
+      <c r="B23" s="24"/>
+    </row>
+    <row r="24" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+      <c r="A24" s="12" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+      <c r="A25" s="15" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+      <c r="A27" s="14" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A28" s="16" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A29" s="16" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A30" s="16" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+      <c r="A31" s="12" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+      <c r="A32" s="15" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A33" s="26" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A34" s="26" t="s">
         <v>336</v>
       </c>
-      <c r="B1" s="17"/>
-    </row>
-    <row r="2" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A2" s="12" t="s">
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A35" s="26" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A36" s="16" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A37" s="16" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A38" s="16" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A39" s="16" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A40" s="16" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A41" s="24"/>
+    </row>
+    <row r="42" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+      <c r="A42" s="14" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A43" s="26" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A44" s="26" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A45" s="16" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A46" s="16" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A47" s="16" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+      <c r="A49" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="B49" s="25"/>
+    </row>
+    <row r="50" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+      <c r="A50" s="15" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A51" s="24" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A52" s="24" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A53" s="24" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A54" s="24" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A55" s="24" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A56" s="24" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A57" s="24" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A58" s="24" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A59" s="24" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A60" s="24" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A61" s="24" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A62" s="24" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+      <c r="A63" s="14" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+      <c r="A64" s="11" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+      <c r="A66" s="12" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+      <c r="A67" s="13" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A68" s="24" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A69" s="24" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A70" s="24" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+      <c r="A72" s="14" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+      <c r="A74" s="12" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+      <c r="A75" s="15" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A76" s="24" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A77" s="17"/>
+    </row>
+    <row r="78" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+      <c r="A78" s="14" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+      <c r="A79" s="11" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+      <c r="A80" s="11"/>
+    </row>
+    <row r="81" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+      <c r="A81" s="12" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+      <c r="A82" s="15" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A83" s="24" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A84" s="24" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A85" s="24" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A86" s="24" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A87" s="24" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+      <c r="A88" s="14" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A89" s="24" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+      <c r="A91" s="12" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+      <c r="A92" s="15" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A93" s="10" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+      <c r="A94" s="14" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A95" s="24" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+      <c r="A97" s="12" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+      <c r="A98" s="15" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A99" s="10" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+      <c r="A100" s="14" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+      <c r="A101" s="11" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+      <c r="A103" s="12" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+      <c r="A104" s="15" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A105" s="10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+      <c r="A106" s="14" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A107" s="10" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" ht="23.25" x14ac:dyDescent="0.6">
+      <c r="A108" s="19" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" ht="23.25" x14ac:dyDescent="0.6">
+      <c r="A109" s="19" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A110" s="10" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" s="23" customFormat="1" ht="25.5" x14ac:dyDescent="0.75">
+      <c r="B111" s="24"/>
+    </row>
+    <row r="112" spans="1:2" ht="23.25" x14ac:dyDescent="0.6">
+      <c r="A112" s="20" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" ht="23.25" x14ac:dyDescent="0.6">
+      <c r="A113" s="21" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A114" s="24" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A115" s="24" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A116" s="24" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A117" s="24" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A118" s="24" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A119" s="24" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A120" s="24" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A121" s="24" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A122" s="24" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A123" s="24" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A124" s="24" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A125" s="24" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A126" s="24" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A127" s="24" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A128" s="24" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A129" s="24" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A130" s="24" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A131" s="24" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A132" s="24" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A133" s="24" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A134" s="24" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A135" s="24" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A136" s="24" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A137" s="24" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A138" s="24" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A139" s="24" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A140" s="24" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A141" s="24" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" ht="23.25" x14ac:dyDescent="0.6">
+      <c r="A142" s="22" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" ht="23.25" x14ac:dyDescent="0.6">
+      <c r="A143" s="19" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" ht="23.25" x14ac:dyDescent="0.6">
+      <c r="A144" s="19" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" ht="23.25" x14ac:dyDescent="0.6">
+      <c r="A145" s="19" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" ht="23.25" x14ac:dyDescent="0.6">
+      <c r="A146" s="19" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+      <c r="A148" s="12" t="s">
         <v>320</v>
       </c>
-      <c r="B2" s="17"/>
-    </row>
-    <row r="3" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A3" s="15" t="s">
-        <v>329</v>
-      </c>
-      <c r="B3" s="17"/>
-    </row>
-    <row r="4" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A4" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="B4" s="17"/>
-    </row>
-    <row r="5" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A5" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="B5" s="17"/>
-    </row>
-    <row r="6" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A6" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="B6" s="17"/>
-    </row>
-    <row r="7" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A7" s="16" t="s">
-        <v>257</v>
-      </c>
-      <c r="B7" s="17"/>
-    </row>
-    <row r="8" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A8" s="16" t="s">
-        <v>290</v>
-      </c>
-      <c r="B8" s="17"/>
-    </row>
-    <row r="9" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A9" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="B9" s="17"/>
-    </row>
-    <row r="10" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A10" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="B10" s="17"/>
-    </row>
-    <row r="11" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A11" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="B11" s="17"/>
-    </row>
-    <row r="12" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A12" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="B12" s="17"/>
-    </row>
-    <row r="13" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A13" s="16" t="s">
-        <v>261</v>
-      </c>
-      <c r="B13" s="17"/>
-    </row>
-    <row r="14" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A14" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="B14" s="17"/>
-    </row>
-    <row r="15" spans="1:2" s="9" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A15" s="16" t="s">
-        <v>263</v>
-      </c>
-      <c r="B15" s="17"/>
-    </row>
-    <row r="16" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A16" s="14" t="s">
-        <v>330</v>
-      </c>
-      <c r="B16" s="17"/>
-    </row>
-    <row r="17" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A17" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="B17" s="17"/>
-    </row>
-    <row r="18" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A18" s="12" t="s">
-        <v>332</v>
-      </c>
-      <c r="B18" s="17"/>
-    </row>
-    <row r="19" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A19" s="12" t="s">
-        <v>333</v>
-      </c>
-      <c r="B19" s="17"/>
-    </row>
-    <row r="20" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A20" s="14" t="s">
-        <v>330</v>
-      </c>
-      <c r="B20" s="17"/>
-    </row>
-    <row r="21" spans="1:2" s="19" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A21" s="16" t="s">
-        <v>264</v>
-      </c>
-      <c r="B21" s="18"/>
-    </row>
-    <row r="22" spans="1:2" s="19" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A22" s="16" t="s">
-        <v>265</v>
-      </c>
-      <c r="B22" s="18"/>
-    </row>
-    <row r="23" spans="1:2" s="19" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A23" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="B23" s="18"/>
-    </row>
-    <row r="24" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A24" s="12" t="s">
+    </row>
+    <row r="149" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+      <c r="A149" s="15" t="s">
         <v>321</v>
       </c>
-      <c r="B24" s="17"/>
-    </row>
-    <row r="25" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A25" s="15" t="s">
-        <v>329</v>
-      </c>
-      <c r="B25" s="17"/>
-    </row>
-    <row r="26" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A26" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="B26" s="17"/>
-    </row>
-    <row r="27" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A27" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="B27" s="17"/>
-    </row>
-    <row r="28" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A28" s="16" t="s">
-        <v>293</v>
-      </c>
-      <c r="B28" s="17"/>
-    </row>
-    <row r="29" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A29" s="16" t="s">
-        <v>295</v>
-      </c>
-      <c r="B29" s="17"/>
-    </row>
-    <row r="30" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A30" s="16" t="s">
-        <v>297</v>
-      </c>
-      <c r="B30" s="17"/>
-    </row>
-    <row r="31" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A31" s="14" t="s">
-        <v>330</v>
-      </c>
-      <c r="B31" s="17"/>
-    </row>
-    <row r="32" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A32" s="16" t="s">
-        <v>294</v>
-      </c>
-      <c r="B32" s="17"/>
-    </row>
-    <row r="33" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A33" s="16" t="s">
-        <v>296</v>
-      </c>
-      <c r="B33" s="17"/>
-    </row>
-    <row r="34" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A34" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="B34" s="17"/>
-    </row>
-    <row r="35" spans="1:2" ht="24" x14ac:dyDescent="0.45">
-      <c r="A35" s="12" t="s">
+    </row>
+    <row r="150" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+      <c r="A150" s="11" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+      <c r="A151" s="14" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="24" x14ac:dyDescent="0.45">
-      <c r="A36" s="15" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A37" s="17" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A38" s="17" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A39" s="17" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A40" s="17" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A41" s="17" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A42" s="17" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A43" s="17" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A44" s="17" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A45" s="17" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A46" s="17" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" ht="24" x14ac:dyDescent="0.45">
-      <c r="A47" s="14" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A48" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="B48" s="17"/>
-    </row>
-    <row r="49" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A49" s="12" t="s">
-        <v>323</v>
-      </c>
-      <c r="B49" s="17"/>
-    </row>
-    <row r="50" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A50" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="B50" s="17"/>
-    </row>
-    <row r="51" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A51" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="B51" s="17"/>
-    </row>
-    <row r="52" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A52" s="14" t="s">
-        <v>330</v>
-      </c>
-      <c r="B52" s="17"/>
-    </row>
-    <row r="53" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A53" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="B53" s="17"/>
-    </row>
-    <row r="54" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A54" s="12" t="s">
-        <v>324</v>
-      </c>
-      <c r="B54" s="17"/>
-    </row>
-    <row r="55" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A55" s="15" t="s">
-        <v>329</v>
-      </c>
-      <c r="B55" s="17"/>
-    </row>
-    <row r="56" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A56" s="17" t="s">
-        <v>361</v>
-      </c>
-      <c r="B56" s="17"/>
-    </row>
-    <row r="57" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A57" s="17" t="s">
-        <v>362</v>
-      </c>
-      <c r="B57" s="17"/>
-    </row>
-    <row r="58" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A58" s="14" t="s">
-        <v>330</v>
-      </c>
-      <c r="B58" s="17"/>
-    </row>
-    <row r="59" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A59" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="B59" s="17"/>
-    </row>
-    <row r="60" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A60" s="12" t="s">
-        <v>325</v>
-      </c>
-      <c r="B60" s="17"/>
-    </row>
-    <row r="61" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A61" s="15" t="s">
-        <v>329</v>
-      </c>
-      <c r="B61" s="17"/>
-    </row>
-    <row r="62" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A62" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="B62" s="17"/>
-    </row>
-    <row r="63" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A63" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="B63" s="17"/>
-    </row>
-    <row r="64" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A64" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="B64" s="17"/>
-    </row>
-    <row r="65" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A65" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="B65" s="17"/>
-    </row>
-    <row r="66" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A66" s="15" t="s">
-        <v>329</v>
-      </c>
-      <c r="B66" s="17"/>
-    </row>
-    <row r="67" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A67" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="B67" s="17"/>
-    </row>
-    <row r="68" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A68" s="12" t="s">
-        <v>334</v>
-      </c>
-      <c r="B68" s="17"/>
-    </row>
-    <row r="69" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A69" s="15" t="s">
-        <v>329</v>
-      </c>
-      <c r="B69" s="17"/>
-    </row>
-    <row r="70" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A70" s="10" t="s">
-        <v>305</v>
-      </c>
-      <c r="B70" s="17"/>
-    </row>
-    <row r="71" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A71" s="14" t="s">
-        <v>330</v>
-      </c>
-      <c r="B71" s="17"/>
-    </row>
-    <row r="72" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A72" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="B72" s="17"/>
-    </row>
-    <row r="73" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A73" s="12" t="s">
-        <v>335</v>
-      </c>
-      <c r="B73" s="17"/>
-    </row>
-    <row r="74" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A74" s="15" t="s">
-        <v>329</v>
-      </c>
-      <c r="B74" s="17"/>
-    </row>
-    <row r="75" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A75" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="B75" s="17"/>
-    </row>
-    <row r="76" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A76" s="14" t="s">
-        <v>330</v>
-      </c>
-      <c r="B76" s="17"/>
-    </row>
-    <row r="77" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A77" s="10" t="s">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A152" s="10" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A153" s="10" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A154" s="10" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A155" s="10" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A156" s="10" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A157" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="B77" s="17"/>
-    </row>
-    <row r="78" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A78" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="B78" s="17"/>
-    </row>
-    <row r="79" spans="1:2" ht="23.25" x14ac:dyDescent="0.65">
-      <c r="A79" s="20" t="s">
-        <v>308</v>
-      </c>
-      <c r="B79" s="17"/>
-    </row>
-    <row r="80" spans="1:2" ht="23.25" x14ac:dyDescent="0.65">
-      <c r="A80" s="20" t="s">
-        <v>309</v>
-      </c>
-      <c r="B80" s="17"/>
-    </row>
-    <row r="81" spans="1:2" ht="23.25" x14ac:dyDescent="0.65">
-      <c r="A81" s="21" t="s">
-        <v>327</v>
-      </c>
-      <c r="B81" s="17"/>
-    </row>
-    <row r="82" spans="1:2" ht="23.25" x14ac:dyDescent="0.65">
-      <c r="A82" s="22" t="s">
-        <v>329</v>
-      </c>
-      <c r="B82" s="17"/>
-    </row>
-    <row r="83" spans="1:2" ht="23.25" x14ac:dyDescent="0.75">
-      <c r="A83" s="23" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" ht="23.25" x14ac:dyDescent="0.75">
-      <c r="A84" s="23" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" ht="23.25" x14ac:dyDescent="0.75">
-      <c r="A85" s="23" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" ht="23.25" x14ac:dyDescent="0.75">
-      <c r="A86" s="23" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" ht="23.25" x14ac:dyDescent="0.75">
-      <c r="A87" s="23" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" ht="23.25" x14ac:dyDescent="0.75">
-      <c r="A88" s="23" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" ht="23.25" x14ac:dyDescent="0.75">
-      <c r="A89" s="23" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" ht="23.25" x14ac:dyDescent="0.75">
-      <c r="A90" s="23" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" ht="23.25" x14ac:dyDescent="0.75">
-      <c r="A91" s="23" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" ht="23.25" x14ac:dyDescent="0.75">
-      <c r="A92" s="23" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" ht="23.25" x14ac:dyDescent="0.75">
-      <c r="A93" s="23" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" ht="23.25" x14ac:dyDescent="0.75">
-      <c r="A94" s="23" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" ht="23.25" x14ac:dyDescent="0.75">
-      <c r="A95" s="23" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" ht="23.25" x14ac:dyDescent="0.65">
-      <c r="A96" s="24" t="s">
-        <v>330</v>
-      </c>
-      <c r="B96" s="17"/>
-    </row>
-    <row r="97" spans="1:2" ht="23.25" x14ac:dyDescent="0.65">
-      <c r="A97" s="20" t="s">
-        <v>310</v>
-      </c>
-      <c r="B97" s="17"/>
-    </row>
-    <row r="98" spans="1:2" ht="23.25" x14ac:dyDescent="0.65">
-      <c r="A98" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="B98" s="17"/>
-    </row>
-    <row r="99" spans="1:2" ht="23.25" x14ac:dyDescent="0.65">
-      <c r="A99" s="20" t="s">
-        <v>312</v>
-      </c>
-      <c r="B99" s="17"/>
-    </row>
-    <row r="100" spans="1:2" ht="23.25" x14ac:dyDescent="0.65">
-      <c r="A100" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="B100" s="17"/>
-    </row>
-    <row r="101" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A101" s="12" t="s">
-        <v>328</v>
-      </c>
-      <c r="B101" s="17"/>
-    </row>
-    <row r="102" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A102" s="15" t="s">
-        <v>329</v>
-      </c>
-      <c r="B102" s="17"/>
-    </row>
-    <row r="103" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A103" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="B103" s="17"/>
-    </row>
-    <row r="104" spans="1:2" ht="24" x14ac:dyDescent="0.65">
-      <c r="A104" s="14" t="s">
-        <v>330</v>
-      </c>
-      <c r="B104" s="17"/>
-    </row>
-    <row r="105" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A105" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="B105" s="17"/>
-    </row>
-    <row r="106" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A106" s="10" t="s">
-        <v>315</v>
-      </c>
-      <c r="B106" s="17"/>
-    </row>
-    <row r="107" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A107" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="B107" s="17"/>
-    </row>
-    <row r="108" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A108" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="B108" s="17"/>
-    </row>
-    <row r="109" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A109" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="B109" s="17"/>
-    </row>
-    <row r="110" spans="1:2" ht="21" x14ac:dyDescent="0.65">
-      <c r="A110" s="10" t="s">
-        <v>319</v>
-      </c>
-      <c r="B110" s="17"/>
+    </row>
+    <row r="160" spans="1:1" ht="25.5" x14ac:dyDescent="0.75">
+      <c r="A160" s="23"/>
+    </row>
+    <row r="161" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A161" s="17"/>
+    </row>
+    <row r="162" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A162" s="17"/>
+    </row>
+    <row r="163" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A163" s="17"/>
+    </row>
+    <row r="164" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A164" s="17"/>
+    </row>
+    <row r="165" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A165" s="17"/>
+    </row>
+    <row r="166" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A166" s="17"/>
+    </row>
+    <row r="167" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A167" s="17"/>
+    </row>
+    <row r="168" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A168" s="17"/>
+    </row>
+    <row r="169" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A169" s="17"/>
+    </row>
+    <row r="170" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A170" s="17"/>
+    </row>
+    <row r="171" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A171" s="17"/>
+    </row>
+    <row r="172" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A172" s="17"/>
+    </row>
+    <row r="173" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A173" s="17"/>
+    </row>
+    <row r="174" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A174" s="17"/>
+    </row>
+    <row r="175" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A175" s="17"/>
+    </row>
+    <row r="176" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A176" s="17"/>
+    </row>
+    <row r="177" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A177" s="17"/>
+    </row>
+    <row r="178" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A178" s="17"/>
+    </row>
+    <row r="179" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A179" s="17"/>
+    </row>
+    <row r="180" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A180" s="17"/>
+    </row>
+    <row r="181" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A181" s="17"/>
+    </row>
+    <row r="182" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A182" s="17"/>
+    </row>
+    <row r="183" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A183" s="17"/>
+    </row>
+    <row r="184" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A184" s="17"/>
+    </row>
+    <row r="185" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A185" s="17"/>
+    </row>
+    <row r="186" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A186" s="17"/>
+    </row>
+    <row r="187" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A187" s="17"/>
+    </row>
+    <row r="188" spans="1:1" ht="21" x14ac:dyDescent="0.65">
+      <c r="A188" s="17"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A152:A157">
+    <sortCondition ref="A152:A157"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/docs/DropDownAccessMethods.xlsx
+++ b/docs/DropDownAccessMethods.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robin\spCoin\SPCOIN-PROJECT-MODULES\spcoin-nextjs-front-end\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2430359B-5B81-48E0-9362-A03FED92817B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B987B636-5611-4C51-9D8B-C41CE8026185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="19395" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OnChainMethods" sheetId="13" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="389">
   <si>
     <t>Panel</t>
   </si>
@@ -1080,15 +1080,6 @@
     <t xml:space="preserve"> getAgentKeysPage(address,uint256,uint256)</t>
   </si>
   <si>
-    <t xml:space="preserve"> getRecipientRecord(address,address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getRecipientRateList(address,address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getRecipientRateListPage(address,address,uint256,uint256)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> getRecipientTransaction(address,address,uint256)</t>
   </si>
   <si>
@@ -1107,94 +1098,106 @@
     <t xml:space="preserve"> getAgentRateListPage(address,address,uint256,address,uint256,uint256)</t>
   </si>
   <si>
-    <t xml:space="preserve"> getRecipientRateTransactionSetKey(address,address,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getAgentRateTransactionSetKey(address,address,uint256,address,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getAgentTransactionCount(address,address,uint256,address,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getRecipientTransactionCount(address,address,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getAgentTransactionAt(address,address,uint256,address,uint256,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getRecipientTransactionAt(address,address,uint256,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getTransactionRecord(uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getRecipientTransactionIdKeys(address,address,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getAgentTransactionIdKeys(address,address,uint256,address,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getRecipientRateTransactionSetKeys(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getRecipientRateTransactionSetKeysPage(address,uint256,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getAgentRateTransactionSetKeys(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getAgentRateTransactionSetKeysPage(address,uint256,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getSponsorRecipientRateTransactionSetKeys(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getSponsorRecipientRateTransactionSetKeysPage(address,uint256,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getSponsorAgentRateTransactionSetKeys(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getSponsorAgentRateTransactionSetKeysPage(address,uint256,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getSponsorRateTransactionSetKeys(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getSponsorContainerRecipientKeys(address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getSponsorContainerRecipientKeysPage(address,uint256,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getSponsorRecipientBoxRecipientRateTransactionSetKeys(address,address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getSponsorRecipientBoxRecipientRateTransactionSetKeysPage(address,address,uint256,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getSponsorRecipientBoxAgentRateTransactionSetKeys(address,address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getSponsorRecipientBoxAgentRateTransactionSetKeysPage(address,address,uint256,uint256)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getSponsorRecipientBoxRateTransactionSetKeys(address,address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getRateTransactionSet(bytes32)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getRateTransactionSetTransactionIds(bytes32)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> getRateTransactionSetTransactionIdsPage(bytes32,uint256,uint256)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> isActiveAccount(address)</t>
   </si>
   <si>
-    <t>Expo+A1:A15rted On Chain Methods</t>
+    <t>getSponsorRecipientRecipientRateTransactionSetKeys(address,address)</t>
+  </si>
+  <si>
+    <t>getSponsorRecipientRecipientRateTransactionSetKeysPage(address,address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t>getSponsorRecipientAgentRateTransactionSetKeys(address,address)</t>
+  </si>
+  <si>
+    <t>getSponsorRecipientAgentRateTransactionSetKeysPage(address,address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t>getSponsorRecipientRateTransactionSetKeyGroups(address,address)</t>
+  </si>
+  <si>
+    <t>getSponsorRecipientRates(address,address)</t>
+  </si>
+  <si>
+    <t>getSponsorRecipientRatesPage(address,address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t>getSponsorAgentRateTransactionSetKeysPage(address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t>getSponsorContainerRecipientKeys(address)</t>
+  </si>
+  <si>
+    <t>getSponsorContainerRecipientKeysPage(address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t>getSponsorRateTransactionSetKeys(address)</t>
+  </si>
+  <si>
+    <t>getSponsorRecipientRateTransactionSetKeys(address)</t>
+  </si>
+  <si>
+    <t>getSponsorRecipientRateTransactionSetKeysPage(address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t>getTransactionRecord(uint256)</t>
+  </si>
+  <si>
+    <t>Inserted On Chain Methods</t>
+  </si>
+  <si>
+    <t>modified</t>
+  </si>
+  <si>
+    <t>getRecipientRecord(address,address)</t>
+  </si>
+  <si>
+    <t>getAgentRateTransactionSetKey(address,address,uint256,address,uint256)</t>
+  </si>
+  <si>
+    <t>getAgentRateTransactionSetKeys(address)</t>
+  </si>
+  <si>
+    <t>getAgentRateTransactionSetKeysPage(address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t>getAgentTransactionAt(address,address,uint256,address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t>getAgentTransactionCount(address,address,uint256,address,uint256)</t>
+  </si>
+  <si>
+    <t>getAgentTransactionIdKeys(address,address,uint256,address,uint256)</t>
+  </si>
+  <si>
+    <t>getRateTransactionSet(bytes32)</t>
+  </si>
+  <si>
+    <t>getRateTransactionSetTransactionIds(bytes32)</t>
+  </si>
+  <si>
+    <t>getRateTransactionSetTransactionIdsPage(bytes32,uint256,uint256)</t>
+  </si>
+  <si>
+    <t>getRecipientRateTransactionSetKey(address,address,uint256)</t>
+  </si>
+  <si>
+    <t>getRecipientRateTransactionSetKeys(address)</t>
+  </si>
+  <si>
+    <t>getRecipientRateTransactionSetKeysPage(address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t>getRecipientTransactionAt(address,address,uint256,uint256)</t>
+  </si>
+  <si>
+    <t>getRecipientTransactionCount(address,address,uint256)</t>
+  </si>
+  <si>
+    <t>getRecipientTransactionIdKeys(address,address,uint256)</t>
+  </si>
+  <si>
+    <t>getSponsorAgentRateTransactionSetKeys(address)</t>
   </si>
 </sst>
 </file>
@@ -1333,7 +1336,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1389,7 +1392,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1726,745 +1728,758 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD098BC8-8253-4308-BB80-99C559D5DD3D}">
   <dimension ref="A1:B188"/>
-  <sheetFormatPr defaultRowHeight="20.65" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="131.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="82.1328125" style="24" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="96" customWidth="1"/>
+    <col min="2" max="2" width="7.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:1" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A1" s="8" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="24" x14ac:dyDescent="0.45">
       <c r="A2" s="12" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:1" ht="24" x14ac:dyDescent="0.45">
       <c r="A3" s="15" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A4" s="16" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A5" s="16" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A6" s="16" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A7" s="16" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A8" s="16" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A9" s="16" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A10" s="16" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A11" s="16" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A12" s="16" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A13" s="16" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A14" s="16" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="15" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:1" s="9" customFormat="1" ht="20.65" x14ac:dyDescent="0.5">
       <c r="A15" s="16" t="s">
         <v>290</v>
       </c>
-      <c r="B15" s="24"/>
-    </row>
-    <row r="16" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+    </row>
+    <row r="16" spans="1:1" ht="24" x14ac:dyDescent="0.45">
       <c r="A16" s="14" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:1" ht="24" x14ac:dyDescent="0.45">
       <c r="A17" s="11" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="24" x14ac:dyDescent="0.6">
-      <c r="A18" s="12" t="s">
+    <row r="18" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A18" s="11"/>
+    </row>
+    <row r="19" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A19" s="12" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="24" x14ac:dyDescent="0.6">
-      <c r="A19" s="15" t="s">
+    <row r="20" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A20" s="15" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.6">
-      <c r="A20" s="24" t="s">
+    <row r="21" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A21" s="24" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="21" spans="1:2" s="18" customFormat="1" ht="24" x14ac:dyDescent="0.6">
-      <c r="A21" s="14" t="s">
+    <row r="22" spans="1:1" s="18" customFormat="1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A22" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B21" s="24"/>
-    </row>
-    <row r="22" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="24" t="s">
+    </row>
+    <row r="23" spans="1:1" s="18" customFormat="1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A23" s="24" t="s">
         <v>323</v>
       </c>
-      <c r="B22" s="24"/>
-    </row>
-    <row r="23" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.6">
-      <c r="A23"/>
-      <c r="B23" s="24"/>
-    </row>
-    <row r="24" spans="1:2" ht="24" x14ac:dyDescent="0.6">
-      <c r="A24" s="12" t="s">
+    </row>
+    <row r="24" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A24"/>
+    </row>
+    <row r="25" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A25" s="12" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="24" x14ac:dyDescent="0.6">
-      <c r="A25" s="15" t="s">
+    <row r="26" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A26" s="15" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="24" x14ac:dyDescent="0.6">
-      <c r="A27" s="14" t="s">
+    <row r="27" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A27" s="24" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A28" s="14" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.6">
-      <c r="A28" s="16" t="s">
+    <row r="29" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A29" s="16" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.6">
-      <c r="A29" s="16" t="s">
+    <row r="30" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A30" s="16" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.6">
-      <c r="A30" s="16" t="s">
+    <row r="31" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A31" s="16" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="24" x14ac:dyDescent="0.6">
-      <c r="A31" s="12" t="s">
+    <row r="32" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A32" s="24"/>
+    </row>
+    <row r="33" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A33" s="12" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="24" x14ac:dyDescent="0.6">
-      <c r="A32" s="15" t="s">
+    <row r="34" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A34" s="15" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A33" s="26" t="s">
+    <row r="35" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A35" s="25" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A34" s="26" t="s">
+    <row r="36" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A36" s="25" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A35" s="26" t="s">
+    <row r="37" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A37" s="25" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A36" s="16" t="s">
+    <row r="38" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A38" s="16" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A37" s="16" t="s">
+    <row r="39" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A39" s="16" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A38" s="16" t="s">
+    <row r="40" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A40" s="16" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A39" s="16" t="s">
+    <row r="41" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A41" s="16" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A40" s="16" t="s">
+    <row r="42" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A42" s="16" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A41" s="24"/>
-    </row>
-    <row r="42" spans="1:1" ht="24" x14ac:dyDescent="0.6">
-      <c r="A42" s="14" t="s">
+    <row r="43" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A43" s="14" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A43" s="26" t="s">
+    <row r="44" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A44" s="25" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A44" s="26" t="s">
+    <row r="45" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A45" s="25" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A45" s="16" t="s">
+    <row r="46" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A46" s="16" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A46" s="16" t="s">
+    <row r="47" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A47" s="16" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A47" s="16" t="s">
+    <row r="48" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
+      <c r="A48" s="16" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="24" x14ac:dyDescent="0.6">
-      <c r="A49" s="12" t="s">
+    <row r="50" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A50" s="12" t="s">
         <v>314</v>
       </c>
-      <c r="B49" s="25"/>
-    </row>
-    <row r="50" spans="1:2" ht="24" x14ac:dyDescent="0.6">
-      <c r="A50" s="15" t="s">
+    </row>
+    <row r="51" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A51" s="15" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.6">
-      <c r="A51" s="24" t="s">
+    <row r="52" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A52" s="24" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.6">
-      <c r="A52" s="24" t="s">
+    <row r="53" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A53" s="24" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.6">
-      <c r="A53" s="24" t="s">
+    <row r="54" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A54" s="24" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.6">
-      <c r="A54" s="24" t="s">
+    <row r="55" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A55" s="24" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.6">
-      <c r="A55" s="24" t="s">
+    <row r="56" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A56" s="24" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.6">
-      <c r="A56" s="24" t="s">
+    <row r="57" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A57" s="24" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.6">
-      <c r="A57" s="24" t="s">
+    <row r="58" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A58" s="24" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.6">
-      <c r="A58" s="24" t="s">
+    <row r="59" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A59" s="24" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.6">
-      <c r="A59" s="24" t="s">
+    <row r="60" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A60" s="24" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.6">
-      <c r="A60" s="24" t="s">
+    <row r="61" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A61" s="24" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.6">
-      <c r="A61" s="24" t="s">
+    <row r="62" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A62" s="24" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.6">
-      <c r="A62" s="24" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" ht="24" x14ac:dyDescent="0.6">
-      <c r="A63" s="14" t="s">
+    <row r="63" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A63" s="24" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A64" s="14" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="24" x14ac:dyDescent="0.6">
-      <c r="A64" s="11" t="s">
+    <row r="65" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A65" s="11" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="66" spans="1:1" ht="24" x14ac:dyDescent="0.6">
-      <c r="A66" s="12" t="s">
+    <row r="67" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A67" s="12" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="67" spans="1:1" ht="24" x14ac:dyDescent="0.6">
-      <c r="A67" s="13" t="s">
+    <row r="68" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A68" s="13" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A68" s="24" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="69" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
       <c r="A69" s="24" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.6">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
       <c r="A70" s="24" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A71" s="24" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" ht="24" x14ac:dyDescent="0.45">
       <c r="A72" s="14" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="74" spans="1:1" ht="24" x14ac:dyDescent="0.6">
-      <c r="A74" s="12" t="s">
+    <row r="75" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A75" s="12" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="75" spans="1:1" ht="24" x14ac:dyDescent="0.6">
-      <c r="A75" s="15" t="s">
+    <row r="76" spans="1:1" ht="24" x14ac:dyDescent="0.45">
+      <c r="A76" s="15" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A76" s="24" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A77" s="17"/>
-    </row>
-    <row r="78" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+    <row r="77" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A77" s="24" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" ht="24" x14ac:dyDescent="0.45">
       <c r="A78" s="14" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="79" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+    <row r="79" spans="1:1" ht="24" x14ac:dyDescent="0.45">
       <c r="A79" s="11" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="80" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+    <row r="80" spans="1:1" ht="24" x14ac:dyDescent="0.45">
       <c r="A80" s="11"/>
     </row>
-    <row r="81" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+    <row r="81" spans="1:1" ht="24" x14ac:dyDescent="0.45">
       <c r="A81" s="12" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="82" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+    <row r="82" spans="1:1" ht="24" x14ac:dyDescent="0.45">
       <c r="A82" s="15" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="83" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
       <c r="A83" s="24" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.6">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
       <c r="A84" s="24" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.6">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
       <c r="A85" s="24" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.6">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
       <c r="A86" s="24" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.6">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
       <c r="A87" s="24" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" ht="24" x14ac:dyDescent="0.45">
       <c r="A88" s="14" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="89" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
       <c r="A89" s="24" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="91" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+    <row r="91" spans="1:1" ht="24" x14ac:dyDescent="0.45">
       <c r="A91" s="12" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="92" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+    <row r="92" spans="1:1" ht="24" x14ac:dyDescent="0.45">
       <c r="A92" s="15" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="93" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A93" s="10" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="94" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+    <row r="94" spans="1:1" ht="24" x14ac:dyDescent="0.45">
       <c r="A94" s="14" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="95" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
       <c r="A95" s="24" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+    <row r="97" spans="1:1" ht="24" x14ac:dyDescent="0.45">
       <c r="A97" s="12" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+    <row r="98" spans="1:1" ht="24" x14ac:dyDescent="0.45">
       <c r="A98" s="15" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="99" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A99" s="10" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+    <row r="100" spans="1:1" ht="24" x14ac:dyDescent="0.45">
       <c r="A100" s="14" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+    <row r="101" spans="1:1" ht="24" x14ac:dyDescent="0.45">
       <c r="A101" s="11" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+    <row r="103" spans="1:1" ht="24" x14ac:dyDescent="0.45">
       <c r="A103" s="12" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+    <row r="104" spans="1:1" ht="24" x14ac:dyDescent="0.45">
       <c r="A104" s="15" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="105" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A105" s="10" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="106" spans="1:2" ht="24" x14ac:dyDescent="0.6">
+    <row r="106" spans="1:1" ht="24" x14ac:dyDescent="0.45">
       <c r="A106" s="14" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="107" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A107" s="10" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="108" spans="1:2" ht="23.25" x14ac:dyDescent="0.6">
+    <row r="108" spans="1:1" ht="23.25" x14ac:dyDescent="0.45">
       <c r="A108" s="19" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="109" spans="1:2" ht="23.25" x14ac:dyDescent="0.6">
+    <row r="109" spans="1:1" ht="23.25" x14ac:dyDescent="0.45">
       <c r="A109" s="19" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="110" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A110" s="10" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="111" spans="1:2" s="23" customFormat="1" ht="25.5" x14ac:dyDescent="0.75">
-      <c r="B111" s="24"/>
-    </row>
-    <row r="112" spans="1:2" ht="23.25" x14ac:dyDescent="0.6">
+    <row r="111" spans="1:1" ht="25.5" x14ac:dyDescent="0.75">
+      <c r="A111" s="23"/>
+    </row>
+    <row r="112" spans="1:1" ht="23.25" x14ac:dyDescent="0.45">
       <c r="A112" s="20" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="113" spans="1:1" ht="23.25" x14ac:dyDescent="0.6">
+    <row r="113" spans="1:1" ht="23.25" x14ac:dyDescent="0.45">
       <c r="A113" s="21" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="114" spans="1:1" s="23" customFormat="1" ht="25.5" x14ac:dyDescent="0.75">
       <c r="A114" s="24" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A115" s="24" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A116" s="24" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A117" s="24" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A118" s="24" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A119" s="24" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A120" s="24" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A121" s="24" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A122" s="24" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A123" s="24" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A124" s="24" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A125" s="24" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A126" s="24" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A127" s="24" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A128" s="24" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A129" s="24" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A130" s="24" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A131" s="24" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A132" s="24" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A133" s="24" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A134" s="24" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A135" s="24" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A115" s="24" t="s">
+    <row r="136" spans="1:2" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A136" s="24" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A137" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="B137" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A138" s="24" t="s">
+        <v>357</v>
+      </c>
+      <c r="B138" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A139" s="24" t="s">
+        <v>367</v>
+      </c>
+      <c r="B139" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A140" s="24" t="s">
+        <v>368</v>
+      </c>
+      <c r="B140" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" ht="20.65" x14ac:dyDescent="0.6">
+      <c r="A141" s="24" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A116" s="24" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A117" s="24" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A118" s="24" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A119" s="24" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A120" s="24" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A121" s="24" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A122" s="24" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A123" s="24" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A124" s="24" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A125" s="24" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A126" s="24" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A127" s="24" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A128" s="24" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A129" s="24" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A130" s="24" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A131" s="24" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A132" s="24" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A133" s="24" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A134" s="24" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A135" s="24" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A136" s="24" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A137" s="24" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A138" s="24" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A139" s="24" t="s">
+      <c r="B141" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A140" s="24" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A141" s="24" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1" ht="23.25" x14ac:dyDescent="0.6">
+    <row r="142" spans="1:2" ht="23.25" x14ac:dyDescent="0.45">
       <c r="A142" s="22" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="143" spans="1:1" ht="23.25" x14ac:dyDescent="0.6">
+    <row r="143" spans="1:2" ht="23.25" x14ac:dyDescent="0.45">
       <c r="A143" s="19" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="144" spans="1:1" ht="23.25" x14ac:dyDescent="0.6">
+    <row r="144" spans="1:2" ht="23.25" x14ac:dyDescent="0.45">
       <c r="A144" s="19" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="145" spans="1:1" ht="23.25" x14ac:dyDescent="0.6">
+    <row r="145" spans="1:1" ht="23.25" x14ac:dyDescent="0.45">
       <c r="A145" s="19" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="146" spans="1:1" ht="23.25" x14ac:dyDescent="0.6">
+    <row r="146" spans="1:1" ht="23.25" x14ac:dyDescent="0.45">
       <c r="A146" s="19" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="148" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+    <row r="148" spans="1:1" ht="24" x14ac:dyDescent="0.45">
       <c r="A148" s="12" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="149" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+    <row r="149" spans="1:1" ht="24" x14ac:dyDescent="0.45">
       <c r="A149" s="15" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="150" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+    <row r="150" spans="1:1" ht="24" x14ac:dyDescent="0.45">
       <c r="A150" s="11" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="151" spans="1:1" ht="24" x14ac:dyDescent="0.6">
+    <row r="151" spans="1:1" ht="24" x14ac:dyDescent="0.45">
       <c r="A151" s="14" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="152" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A152" s="10" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="153" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A153" s="10" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="154" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A154" s="10" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="155" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A155" s="10" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="156" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A156" s="10" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="157" spans="1:1" ht="20.65" x14ac:dyDescent="0.45">
       <c r="A157" s="10" t="s">
         <v>306</v>
       </c>
